--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9491AFE6-315B-F946-BA1B-C8F4D5DE62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1DBDB-281B-C842-AEF0-10D473CAE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="318">
   <si>
     <t>category</t>
   </si>
@@ -857,6 +857,123 @@
   </si>
   <si>
     <t>Dakshinaamoorthy_Stotram.pdf</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>Shasta_Suktam.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shastru_Panchaakshara_Stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Ayyappa_Dharmashasta_Trishati_Namavali.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Ashtottara_shata_Namavali.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Harihara_Sahasra_naama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Sahasranamavali.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashastuhu_Pancharatna.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Harihara_aatmaja_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>shri_Hariharaputra_shasta_shabarigirIsha_abhinna_puja _vidhi.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Shasta_keshadipadanta_Varnana_Stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Shastru_sha_varna sahasra_naama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Shastru_sha_varna_sahasra_naamaavalihi.pdf</t>
+  </si>
+  <si>
+    <t>Shasta_Suktam</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shastru_Panchaakshara_Stotram</t>
+  </si>
+  <si>
+    <t>Shri_Ayyappa_Dharmashasta_Trishati_Namavali</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Ashtottara_shata_Namavali</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Harihara_Sahasra_naama_stotram</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashasta_Sahasranamavali</t>
+  </si>
+  <si>
+    <t>Shri_Dharmashastuhu_Pancharatna</t>
+  </si>
+  <si>
+    <t>Shri_Harihara_aatmaja_ashtakam</t>
+  </si>
+  <si>
+    <t>shri_Hariharaputra_shasta_shabarigirIsha_abhinna_puja _vidhi</t>
+  </si>
+  <si>
+    <t>Shri_Shasta_keshadipadanta_Varnana_Stotram</t>
+  </si>
+  <si>
+    <t>Shri_Shastru_sha_varna sahasra_naama_stotram</t>
+  </si>
+  <si>
+    <t>Shri_Shastru_sha_varna_sahasra_naamaavalihi</t>
+  </si>
+  <si>
+    <t>Shri_Hariharaputra_Maalaa_mantraha</t>
+  </si>
+  <si>
+    <t>Shri_Hariharaputra_Maalaa_mantraha.pdf</t>
   </si>
 </sst>
 </file>
@@ -1228,14 +1345,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="40.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
@@ -3996,406 +4114,861 @@
         <v>147</v>
       </c>
       <c r="E77" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="F77" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="H77" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="2">
         <v>1</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>130</v>
+        <v>279</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="G78" t="s">
-        <v>97</v>
+        <v>305</v>
       </c>
       <c r="H78" t="s">
-        <v>97</v>
+        <v>293</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J78" t="s">
-        <v>97</v>
-      </c>
-      <c r="K78" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="F79" t="s">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="G79" t="s">
-        <v>257</v>
+        <v>306</v>
       </c>
       <c r="H79" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="F80" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="G80" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="H80" t="s">
-        <v>97</v>
+        <v>295</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J80" t="s">
-        <v>97</v>
-      </c>
-      <c r="K80" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80">
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E81" t="s">
-        <v>177</v>
+        <v>308</v>
       </c>
       <c r="F81" t="s">
-        <v>177</v>
+        <v>308</v>
       </c>
       <c r="G81" t="s">
-        <v>177</v>
+        <v>308</v>
       </c>
       <c r="H81" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J81" s="2">
-        <v>1</v>
-      </c>
-      <c r="K81" s="2">
-        <v>1</v>
-      </c>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
+        <v>5</v>
+      </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E82" t="s">
-        <v>175</v>
+        <v>309</v>
       </c>
       <c r="F82" t="s">
-        <v>175</v>
+        <v>309</v>
       </c>
       <c r="G82" t="s">
-        <v>175</v>
+        <v>309</v>
       </c>
       <c r="H82" t="s">
-        <v>176</v>
+        <v>297</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J82" s="2">
-        <v>2</v>
-      </c>
-      <c r="K82" s="2">
-        <v>2</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
+      <c r="J82">
+        <v>6</v>
+      </c>
+      <c r="K82">
+        <v>6</v>
+      </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="F83" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="G83" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="H83" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J83" s="2">
-        <v>3</v>
-      </c>
-      <c r="K83" s="2">
-        <v>3</v>
-      </c>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
+      <c r="J83">
+        <v>7</v>
+      </c>
+      <c r="K83">
+        <v>7</v>
+      </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>128</v>
+        <v>285</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E84" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="F84" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="G84" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="H84" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J84" t="s">
-        <v>97</v>
-      </c>
-      <c r="K84" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J84">
+        <v>8</v>
+      </c>
+      <c r="K84">
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E85" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="F85" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="G85" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="H85" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J85" s="2">
-        <v>1</v>
-      </c>
-      <c r="K85" s="2">
-        <v>1</v>
-      </c>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
+      <c r="J85">
+        <v>9</v>
+      </c>
+      <c r="K85">
+        <v>9</v>
+      </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>129</v>
+        <v>287</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="F86" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="G86" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="H86" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J86" t="s">
-        <v>97</v>
-      </c>
-      <c r="K86" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J86">
+        <v>10</v>
+      </c>
+      <c r="K86">
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E87" t="s">
+        <v>313</v>
+      </c>
+      <c r="F87" t="s">
+        <v>313</v>
+      </c>
+      <c r="G87" t="s">
+        <v>313</v>
+      </c>
+      <c r="H87" t="s">
+        <v>301</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J87">
+        <v>11</v>
+      </c>
+      <c r="K87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E88" t="s">
+        <v>314</v>
+      </c>
+      <c r="F88" t="s">
+        <v>314</v>
+      </c>
+      <c r="G88" t="s">
+        <v>314</v>
+      </c>
+      <c r="H88" t="s">
+        <v>302</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J88">
+        <v>12</v>
+      </c>
+      <c r="K88">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E89" t="s">
+        <v>315</v>
+      </c>
+      <c r="F89" t="s">
+        <v>315</v>
+      </c>
+      <c r="G89" t="s">
+        <v>315</v>
+      </c>
+      <c r="H89" t="s">
+        <v>303</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J89">
+        <v>13</v>
+      </c>
+      <c r="K89">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E90" t="s">
+        <v>316</v>
+      </c>
+      <c r="F90" t="s">
+        <v>316</v>
+      </c>
+      <c r="G90" t="s">
+        <v>316</v>
+      </c>
+      <c r="H90" t="s">
+        <v>317</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J90">
+        <v>14</v>
+      </c>
+      <c r="K90">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E91" t="s">
+        <v>97</v>
+      </c>
+      <c r="F91" t="s">
+        <v>97</v>
+      </c>
+      <c r="G91" t="s">
+        <v>97</v>
+      </c>
+      <c r="H91" t="s">
+        <v>97</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J91" t="s">
+        <v>97</v>
+      </c>
+      <c r="K91" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E92" t="s">
+        <v>257</v>
+      </c>
+      <c r="F92" t="s">
+        <v>257</v>
+      </c>
+      <c r="G92" t="s">
+        <v>257</v>
+      </c>
+      <c r="H92" t="s">
+        <v>258</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E93" t="s">
+        <v>97</v>
+      </c>
+      <c r="F93" t="s">
+        <v>97</v>
+      </c>
+      <c r="G93" t="s">
+        <v>97</v>
+      </c>
+      <c r="H93" t="s">
+        <v>97</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J93" t="s">
+        <v>97</v>
+      </c>
+      <c r="K93" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E94" t="s">
+        <v>177</v>
+      </c>
+      <c r="F94" t="s">
+        <v>177</v>
+      </c>
+      <c r="G94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" t="s">
+        <v>178</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J94" s="2">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="2"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E95" t="s">
+        <v>175</v>
+      </c>
+      <c r="F95" t="s">
+        <v>175</v>
+      </c>
+      <c r="G95" t="s">
+        <v>175</v>
+      </c>
+      <c r="H95" t="s">
+        <v>176</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J95" s="2">
+        <v>2</v>
+      </c>
+      <c r="K95" s="2">
+        <v>2</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="2"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E96" t="s">
+        <v>222</v>
+      </c>
+      <c r="F96" t="s">
+        <v>222</v>
+      </c>
+      <c r="G96" t="s">
+        <v>222</v>
+      </c>
+      <c r="H96" t="s">
+        <v>221</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J96" s="2">
+        <v>3</v>
+      </c>
+      <c r="K96" s="2">
+        <v>3</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="2"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E97" t="s">
+        <v>97</v>
+      </c>
+      <c r="F97" t="s">
+        <v>97</v>
+      </c>
+      <c r="G97" t="s">
+        <v>97</v>
+      </c>
+      <c r="H97" t="s">
+        <v>97</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J97" t="s">
+        <v>97</v>
+      </c>
+      <c r="K97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E98" t="s">
+        <v>216</v>
+      </c>
+      <c r="F98" t="s">
+        <v>216</v>
+      </c>
+      <c r="G98" t="s">
+        <v>216</v>
+      </c>
+      <c r="H98" t="s">
+        <v>217</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J98" s="2">
+        <v>1</v>
+      </c>
+      <c r="K98" s="2">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="2"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B99" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C99" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E99" t="s">
+        <v>97</v>
+      </c>
+      <c r="F99" t="s">
+        <v>97</v>
+      </c>
+      <c r="G99" t="s">
+        <v>97</v>
+      </c>
+      <c r="H99" t="s">
+        <v>97</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J99" t="s">
+        <v>97</v>
+      </c>
+      <c r="K99" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D100" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E100" t="s">
         <v>67</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F100" t="s">
         <v>67</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G100" t="s">
         <v>67</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H100" t="s">
         <v>68</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J87" s="2">
+      <c r="I100" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J100" s="2">
         <v>1</v>
       </c>
-      <c r="K87" s="2">
+      <c r="K100" s="2">
         <v>1</v>
       </c>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA1DBDB-281B-C842-AEF0-10D473CAE57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A765F6D-2828-2741-816F-5355C8737B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="367">
   <si>
     <t>category</t>
   </si>
@@ -974,6 +974,153 @@
   </si>
   <si>
     <t>Shri_Hariharaputra_Maalaa_mantraha.pdf</t>
+  </si>
+  <si>
+    <t>H002</t>
+  </si>
+  <si>
+    <t>H003</t>
+  </si>
+  <si>
+    <t>tamil</t>
+  </si>
+  <si>
+    <t>HH_Shri_Bodhendra_dwadasha_namaskara_stotram</t>
+  </si>
+  <si>
+    <t>HH_Shri_Bodhendra_dwadasha_namaskara_stotram.pdf</t>
+  </si>
+  <si>
+    <t>HH_Shri_Bodhendra_dwadasha_namaskara_stotram_tamil</t>
+  </si>
+  <si>
+    <t>HH_Shri_Bodhendra_dwadasha_namaskara_stotram_tamil.pdf</t>
+  </si>
+  <si>
+    <t>Q002</t>
+  </si>
+  <si>
+    <t>Q003</t>
+  </si>
+  <si>
+    <t>Q004</t>
+  </si>
+  <si>
+    <t>Q005</t>
+  </si>
+  <si>
+    <t>Q006</t>
+  </si>
+  <si>
+    <t>Q007</t>
+  </si>
+  <si>
+    <t>Q008</t>
+  </si>
+  <si>
+    <t>Q009</t>
+  </si>
+  <si>
+    <t>Q010</t>
+  </si>
+  <si>
+    <t>Q011</t>
+  </si>
+  <si>
+    <t>Q012</t>
+  </si>
+  <si>
+    <t>Q013</t>
+  </si>
+  <si>
+    <t>Q014</t>
+  </si>
+  <si>
+    <t>Adithya_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Brahma_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Chandra_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Dhanvanthri.pdf</t>
+  </si>
+  <si>
+    <t>Durga_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Ganapathy_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Garuda_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Lakshmi_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Rudra_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Subrahmanya_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Surya_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Vani_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Vishnu_Gayathri.pdf</t>
+  </si>
+  <si>
+    <t>Adithya_Gayathri</t>
+  </si>
+  <si>
+    <t>Brahma_Gayathri</t>
+  </si>
+  <si>
+    <t>Chandra_Gayathri</t>
+  </si>
+  <si>
+    <t>Dhanvanthri</t>
+  </si>
+  <si>
+    <t>Durga_Gayathri</t>
+  </si>
+  <si>
+    <t>Ganapathy_Gayathri</t>
+  </si>
+  <si>
+    <t>Garuda_Gayathri</t>
+  </si>
+  <si>
+    <t>Lakshmi_Gayathri</t>
+  </si>
+  <si>
+    <t>Rudra_Gayathri</t>
+  </si>
+  <si>
+    <t>Subrahmanya_Gayathri</t>
+  </si>
+  <si>
+    <t>Surya_Gayathri</t>
+  </si>
+  <si>
+    <t>Vani_Gayathri</t>
+  </si>
+  <si>
+    <t>Vishnu_Gayathri</t>
+  </si>
+  <si>
+    <t>K005</t>
+  </si>
+  <si>
+    <t>Adithya_hrudayam</t>
+  </si>
+  <si>
+    <t>Adithya_hrudayam.pdf</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1354,7 +1501,7 @@
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="40.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3136,72 +3283,78 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>119</v>
+        <v>318</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" t="s">
-        <v>97</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
-      </c>
-      <c r="H50" t="s">
-        <v>97</v>
+        <v>139</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J50" t="s">
-        <v>97</v>
-      </c>
-      <c r="K50" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J50" s="2">
+        <v>2</v>
+      </c>
+      <c r="K50" s="2">
+        <v>2</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>198</v>
+        <v>319</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>183</v>
+        <v>323</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>183</v>
+        <v>323</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>183</v>
+        <v>323</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="J51" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -3218,38 +3371,32 @@
         <v>197</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E52" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G52" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H52" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J52" s="2">
-        <v>2</v>
-      </c>
-      <c r="K52" s="2">
-        <v>2</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J52" t="s">
+        <v>97</v>
+      </c>
+      <c r="K52" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -3259,31 +3406,31 @@
         <v>197</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E53" t="s">
-        <v>237</v>
-      </c>
-      <c r="F53" t="s">
-        <v>237</v>
-      </c>
-      <c r="G53" t="s">
-        <v>237</v>
-      </c>
-      <c r="H53" t="s">
-        <v>238</v>
+      <c r="E53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J53" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -3300,31 +3447,31 @@
         <v>197</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="F54" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="G54" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="H54" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J54" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K54" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -3335,70 +3482,85 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>120</v>
+        <v>235</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E55" t="s">
+        <v>237</v>
       </c>
       <c r="F55" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="G55" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="H55" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K55" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J55" s="2">
+        <v>3</v>
+      </c>
+      <c r="K55" s="2">
+        <v>3</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F56" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G56" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="H56" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J56">
-        <v>1</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
+      <c r="J56" s="2">
+        <v>4</v>
+      </c>
+      <c r="K56" s="2">
+        <v>4</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
@@ -3408,31 +3570,28 @@
         <v>205</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E57" t="s">
-        <v>229</v>
-      </c>
       <c r="F57" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="H57" t="s">
-        <v>230</v>
+        <v>97</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J57">
-        <v>2</v>
-      </c>
-      <c r="K57">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J57" t="s">
+        <v>97</v>
+      </c>
+      <c r="K57" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
@@ -3443,31 +3602,31 @@
         <v>205</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E58" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F58" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G58" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H58" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
@@ -3478,101 +3637,101 @@
         <v>205</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F59" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G59" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H59" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K59">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E60" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="F60" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="G60" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="H60" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J60">
+        <v>3</v>
+      </c>
+      <c r="K60">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E61" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G61" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="H61" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
@@ -3583,31 +3742,31 @@
         <v>259</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E62" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="F62" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="G62" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J62">
-        <v>2</v>
-      </c>
-      <c r="K62">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J62" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
@@ -3618,31 +3777,31 @@
         <v>259</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F63" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G63" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H63" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -3653,346 +3812,346 @@
         <v>259</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F64" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G64" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H64" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K64">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="G65" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="H65" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J65" t="s">
-        <v>97</v>
-      </c>
-      <c r="K65" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E66" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="F66" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="G66" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="H66" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>123</v>
+        <v>364</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="F67" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="G67" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="H67" t="s">
-        <v>97</v>
+        <v>366</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J67" t="s">
-        <v>97</v>
-      </c>
-      <c r="K67" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>265</v>
+        <v>122</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="F68" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="G68" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="H68" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J68" t="s">
+        <v>97</v>
+      </c>
+      <c r="K68" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="F69" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="G69" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="H69" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J69" t="s">
-        <v>97</v>
-      </c>
-      <c r="K69" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>266</v>
+        <v>123</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E70" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="K70">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J70" t="s">
+        <v>97</v>
+      </c>
+      <c r="K70" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="G71" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="H71" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J71" t="s">
-        <v>97</v>
-      </c>
-      <c r="K71" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F72" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="G72" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="H72" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J72" t="s">
+        <v>97</v>
+      </c>
+      <c r="K72" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="F73" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="G73" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="H73" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -4003,31 +4162,31 @@
         <v>152</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E74" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G74" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H74" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J74">
-        <v>3</v>
-      </c>
-      <c r="K74">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J74" t="s">
+        <v>97</v>
+      </c>
+      <c r="K74" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -4038,136 +4197,136 @@
         <v>152</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F75" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G75" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H75" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E76" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="G76" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H76" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J76" t="s">
-        <v>97</v>
-      </c>
-      <c r="K76" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E77" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="F77" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="G77" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="H77" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J77" s="2">
-        <v>1</v>
-      </c>
-      <c r="K77" s="2">
-        <v>1</v>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E78" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="F78" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="G78" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="H78" t="s">
-        <v>293</v>
+        <v>196</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
@@ -4178,31 +4337,31 @@
         <v>209</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>280</v>
+        <v>126</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="G79" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="H79" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J79">
-        <v>3</v>
-      </c>
-      <c r="K79">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J79" t="s">
+        <v>97</v>
+      </c>
+      <c r="K79" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -4213,34 +4372,34 @@
         <v>209</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F80" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G80" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H80" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J80">
-        <v>4</v>
-      </c>
-      <c r="K80">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J80" s="2">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>112</v>
       </c>
@@ -4248,34 +4407,34 @@
         <v>209</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E81" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F81" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G81" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H81" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>112</v>
       </c>
@@ -4283,34 +4442,34 @@
         <v>209</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E82" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F82" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G82" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H82" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K82">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>112</v>
       </c>
@@ -4318,34 +4477,34 @@
         <v>209</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F83" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G83" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H83" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J83">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K83">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>112</v>
       </c>
@@ -4353,34 +4512,34 @@
         <v>209</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E84" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F84" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G84" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H84" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J84">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K84">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
         <v>112</v>
       </c>
@@ -4388,34 +4547,34 @@
         <v>209</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E85" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="F85" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="G85" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="H85" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J85">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K85">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>112</v>
       </c>
@@ -4423,34 +4582,34 @@
         <v>209</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F86" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G86" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H86" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J86">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K86">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>112</v>
       </c>
@@ -4458,34 +4617,34 @@
         <v>209</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H87" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J87">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K87">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>112</v>
       </c>
@@ -4493,34 +4652,34 @@
         <v>209</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="F88" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="G88" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H88" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J88">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K88">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>112</v>
       </c>
@@ -4528,34 +4687,34 @@
         <v>209</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E89" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F89" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G89" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H89" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J89">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K89">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>112</v>
       </c>
@@ -4563,412 +4722,972 @@
         <v>209</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E90" t="s">
+        <v>313</v>
+      </c>
+      <c r="F90" t="s">
+        <v>313</v>
+      </c>
+      <c r="G90" t="s">
+        <v>313</v>
+      </c>
+      <c r="H90" t="s">
+        <v>301</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J90">
+        <v>11</v>
+      </c>
+      <c r="K90">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" t="s">
+        <v>314</v>
+      </c>
+      <c r="F91" t="s">
+        <v>314</v>
+      </c>
+      <c r="G91" t="s">
+        <v>314</v>
+      </c>
+      <c r="H91" t="s">
+        <v>302</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J91">
+        <v>12</v>
+      </c>
+      <c r="K91">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E92" t="s">
+        <v>315</v>
+      </c>
+      <c r="F92" t="s">
+        <v>315</v>
+      </c>
+      <c r="G92" t="s">
+        <v>315</v>
+      </c>
+      <c r="H92" t="s">
+        <v>303</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92">
+        <v>13</v>
+      </c>
+      <c r="K92">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E93" t="s">
         <v>316</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F93" t="s">
         <v>316</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G93" t="s">
         <v>316</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H93" t="s">
         <v>317</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J90">
+      <c r="I93" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J93">
         <v>14</v>
       </c>
-      <c r="K90">
+      <c r="K93">
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E91" t="s">
-        <v>97</v>
-      </c>
-      <c r="F91" t="s">
-        <v>97</v>
-      </c>
-      <c r="G91" t="s">
-        <v>97</v>
-      </c>
-      <c r="H91" t="s">
-        <v>97</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J91" t="s">
-        <v>97</v>
-      </c>
-      <c r="K91" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
+      <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" t="s">
+        <v>97</v>
+      </c>
+      <c r="G94" t="s">
+        <v>97</v>
+      </c>
+      <c r="H94" t="s">
+        <v>97</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J94" t="s">
+        <v>97</v>
+      </c>
+      <c r="K94" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D95" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E92" t="s">
-        <v>257</v>
-      </c>
-      <c r="F92" t="s">
-        <v>257</v>
-      </c>
-      <c r="G92" t="s">
-        <v>257</v>
-      </c>
-      <c r="H92" t="s">
-        <v>258</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J92">
+      <c r="E95" t="s">
+        <v>351</v>
+      </c>
+      <c r="F95" t="s">
+        <v>351</v>
+      </c>
+      <c r="G95" t="s">
+        <v>351</v>
+      </c>
+      <c r="H95" t="s">
+        <v>338</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J95" s="2">
         <v>1</v>
       </c>
-      <c r="K92">
+      <c r="K95" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E93" t="s">
-        <v>97</v>
-      </c>
-      <c r="F93" t="s">
-        <v>97</v>
-      </c>
-      <c r="G93" t="s">
-        <v>97</v>
-      </c>
-      <c r="H93" t="s">
-        <v>97</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J93" t="s">
-        <v>97</v>
-      </c>
-      <c r="K93" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E94" t="s">
-        <v>177</v>
-      </c>
-      <c r="F94" t="s">
-        <v>177</v>
-      </c>
-      <c r="G94" t="s">
-        <v>177</v>
-      </c>
-      <c r="H94" t="s">
-        <v>178</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J94" s="2">
-        <v>1</v>
-      </c>
-      <c r="K94" s="2">
-        <v>1</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
-      <c r="Q94" s="2"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E95" t="s">
-        <v>175</v>
-      </c>
-      <c r="F95" t="s">
-        <v>175</v>
-      </c>
-      <c r="G95" t="s">
-        <v>175</v>
-      </c>
-      <c r="H95" t="s">
-        <v>176</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J95" s="2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E96" t="s">
+        <v>352</v>
+      </c>
+      <c r="F96" t="s">
+        <v>352</v>
+      </c>
+      <c r="G96" t="s">
+        <v>352</v>
+      </c>
+      <c r="H96" t="s">
+        <v>339</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J96">
         <v>2</v>
       </c>
-      <c r="K95" s="2">
+      <c r="K96">
         <v>2</v>
       </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
-      <c r="Q95" s="2"/>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E96" t="s">
-        <v>222</v>
-      </c>
-      <c r="F96" t="s">
-        <v>222</v>
-      </c>
-      <c r="G96" t="s">
-        <v>222</v>
-      </c>
-      <c r="H96" t="s">
-        <v>221</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J96" s="2">
-        <v>3</v>
-      </c>
-      <c r="K96" s="2">
-        <v>3</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" s="2"/>
-      <c r="Q96" s="2"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E97" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="F97" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="G97" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="H97" t="s">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J97" t="s">
-        <v>97</v>
-      </c>
-      <c r="K97" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J97">
+        <v>3</v>
+      </c>
+      <c r="K97">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>215</v>
+        <v>327</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E98" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="G98" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="H98" t="s">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J98" s="2">
-        <v>1</v>
-      </c>
-      <c r="K98" s="2">
-        <v>1</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" s="2"/>
-      <c r="Q98" s="2"/>
+      <c r="J98">
+        <v>4</v>
+      </c>
+      <c r="K98">
+        <v>4</v>
+      </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>129</v>
+        <v>328</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>355</v>
       </c>
       <c r="F99" t="s">
-        <v>97</v>
+        <v>355</v>
       </c>
       <c r="G99" t="s">
-        <v>97</v>
+        <v>355</v>
       </c>
       <c r="H99" t="s">
-        <v>97</v>
+        <v>342</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J99" t="s">
-        <v>97</v>
-      </c>
-      <c r="K99" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J99">
+        <v>5</v>
+      </c>
+      <c r="K99">
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" t="s">
+        <v>356</v>
+      </c>
+      <c r="F100" t="s">
+        <v>356</v>
+      </c>
+      <c r="G100" t="s">
+        <v>356</v>
+      </c>
+      <c r="H100" t="s">
+        <v>343</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J100">
+        <v>6</v>
+      </c>
+      <c r="K100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E101" t="s">
+        <v>357</v>
+      </c>
+      <c r="F101" t="s">
+        <v>357</v>
+      </c>
+      <c r="G101" t="s">
+        <v>357</v>
+      </c>
+      <c r="H101" t="s">
+        <v>344</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J101">
+        <v>7</v>
+      </c>
+      <c r="K101">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E102" t="s">
+        <v>358</v>
+      </c>
+      <c r="F102" t="s">
+        <v>358</v>
+      </c>
+      <c r="G102" t="s">
+        <v>358</v>
+      </c>
+      <c r="H102" t="s">
+        <v>345</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J102">
+        <v>8</v>
+      </c>
+      <c r="K102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E103" t="s">
+        <v>359</v>
+      </c>
+      <c r="F103" t="s">
+        <v>359</v>
+      </c>
+      <c r="G103" t="s">
+        <v>359</v>
+      </c>
+      <c r="H103" t="s">
+        <v>346</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J103">
+        <v>9</v>
+      </c>
+      <c r="K103">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E104" t="s">
+        <v>257</v>
+      </c>
+      <c r="F104" t="s">
+        <v>257</v>
+      </c>
+      <c r="G104" t="s">
+        <v>257</v>
+      </c>
+      <c r="H104" t="s">
+        <v>258</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J104">
+        <v>10</v>
+      </c>
+      <c r="K104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E105" t="s">
+        <v>360</v>
+      </c>
+      <c r="F105" t="s">
+        <v>360</v>
+      </c>
+      <c r="G105" t="s">
+        <v>360</v>
+      </c>
+      <c r="H105" t="s">
+        <v>347</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J105">
+        <v>11</v>
+      </c>
+      <c r="K105">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E106" t="s">
+        <v>361</v>
+      </c>
+      <c r="F106" t="s">
+        <v>361</v>
+      </c>
+      <c r="G106" t="s">
+        <v>361</v>
+      </c>
+      <c r="H106" t="s">
+        <v>348</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J106">
+        <v>12</v>
+      </c>
+      <c r="K106">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E107" t="s">
+        <v>362</v>
+      </c>
+      <c r="F107" t="s">
+        <v>362</v>
+      </c>
+      <c r="G107" t="s">
+        <v>362</v>
+      </c>
+      <c r="H107" t="s">
+        <v>349</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J107">
+        <v>13</v>
+      </c>
+      <c r="K107">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A108" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E108" t="s">
+        <v>363</v>
+      </c>
+      <c r="F108" t="s">
+        <v>363</v>
+      </c>
+      <c r="G108" t="s">
+        <v>363</v>
+      </c>
+      <c r="H108" t="s">
+        <v>350</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J108">
+        <v>14</v>
+      </c>
+      <c r="K108">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E109" t="s">
+        <v>97</v>
+      </c>
+      <c r="F109" t="s">
+        <v>97</v>
+      </c>
+      <c r="G109" t="s">
+        <v>97</v>
+      </c>
+      <c r="H109" t="s">
+        <v>97</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J109" t="s">
+        <v>97</v>
+      </c>
+      <c r="K109" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E110" t="s">
+        <v>177</v>
+      </c>
+      <c r="F110" t="s">
+        <v>177</v>
+      </c>
+      <c r="G110" t="s">
+        <v>177</v>
+      </c>
+      <c r="H110" t="s">
+        <v>178</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J110" s="2">
+        <v>1</v>
+      </c>
+      <c r="K110" s="2">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="2"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A111" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E111" t="s">
+        <v>175</v>
+      </c>
+      <c r="F111" t="s">
+        <v>175</v>
+      </c>
+      <c r="G111" t="s">
+        <v>175</v>
+      </c>
+      <c r="H111" t="s">
+        <v>176</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J111" s="2">
+        <v>2</v>
+      </c>
+      <c r="K111" s="2">
+        <v>2</v>
+      </c>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" s="2"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A112" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E112" t="s">
+        <v>222</v>
+      </c>
+      <c r="F112" t="s">
+        <v>222</v>
+      </c>
+      <c r="G112" t="s">
+        <v>222</v>
+      </c>
+      <c r="H112" t="s">
+        <v>221</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J112" s="2">
+        <v>3</v>
+      </c>
+      <c r="K112" s="2">
+        <v>3</v>
+      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="2"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A113" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E113" t="s">
+        <v>97</v>
+      </c>
+      <c r="F113" t="s">
+        <v>97</v>
+      </c>
+      <c r="G113" t="s">
+        <v>97</v>
+      </c>
+      <c r="H113" t="s">
+        <v>97</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J113" t="s">
+        <v>97</v>
+      </c>
+      <c r="K113" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A114" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E114" t="s">
+        <v>216</v>
+      </c>
+      <c r="F114" t="s">
+        <v>216</v>
+      </c>
+      <c r="G114" t="s">
+        <v>216</v>
+      </c>
+      <c r="H114" t="s">
+        <v>217</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J114" s="2">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="2"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A115" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B115" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C115" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E115" t="s">
+        <v>97</v>
+      </c>
+      <c r="F115" t="s">
+        <v>97</v>
+      </c>
+      <c r="G115" t="s">
+        <v>97</v>
+      </c>
+      <c r="H115" t="s">
+        <v>97</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J115" t="s">
+        <v>97</v>
+      </c>
+      <c r="K115" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A116" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E116" t="s">
         <v>67</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F116" t="s">
         <v>67</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G116" t="s">
         <v>67</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H116" t="s">
         <v>68</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J100" s="2">
+      <c r="I116" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J116" s="2">
         <v>1</v>
       </c>
-      <c r="K100" s="2">
+      <c r="K116" s="2">
         <v>1</v>
       </c>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" s="2"/>
-      <c r="Q100" s="2"/>
+      <c r="L116" s="2"/>
+      <c r="M116" s="2"/>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A765F6D-2828-2741-816F-5355C8737B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FD59F0-E1EF-C349-AE24-66485BFD7C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="370">
   <si>
     <t>category</t>
   </si>
@@ -1121,6 +1121,15 @@
   </si>
   <si>
     <t>Adithya_hrudayam.pdf</t>
+  </si>
+  <si>
+    <t>H004</t>
+  </si>
+  <si>
+    <t>Gurvashtakam</t>
+  </si>
+  <si>
+    <t>Gurvashtakam.pdf</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q116"/>
+  <dimension ref="A1:Q117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3365,38 +3374,44 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>119</v>
+        <v>367</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" t="s">
-        <v>97</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
-      </c>
-      <c r="H52" t="s">
-        <v>97</v>
+        <v>139</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J52" t="s">
-        <v>97</v>
-      </c>
-      <c r="K52" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J52" s="2">
+        <v>4</v>
+      </c>
+      <c r="K52" s="2">
+        <v>4</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -3406,38 +3421,32 @@
         <v>197</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>184</v>
+      <c r="E53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" t="s">
+        <v>97</v>
+      </c>
+      <c r="H53" t="s">
+        <v>97</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J53" s="2">
-        <v>1</v>
-      </c>
-      <c r="K53" s="2">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J53" t="s">
+        <v>97</v>
+      </c>
+      <c r="K53" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
@@ -3447,31 +3456,31 @@
         <v>197</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E54" t="s">
-        <v>202</v>
-      </c>
-      <c r="F54" t="s">
-        <v>202</v>
-      </c>
-      <c r="G54" t="s">
-        <v>202</v>
-      </c>
-      <c r="H54" t="s">
-        <v>204</v>
+      <c r="E54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -3488,31 +3497,31 @@
         <v>197</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="G55" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="H55" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -3529,31 +3538,31 @@
         <v>197</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F56" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G56" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H56" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J56" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -3564,35 +3573,44 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>120</v>
+        <v>236</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>239</v>
       </c>
       <c r="F57" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>239</v>
       </c>
       <c r="H57" t="s">
-        <v>97</v>
+        <v>240</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J57" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J57" s="2">
+        <v>4</v>
+      </c>
+      <c r="K57" s="2">
+        <v>4</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
@@ -3602,31 +3620,28 @@
         <v>205</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E58" t="s">
-        <v>224</v>
-      </c>
       <c r="F58" t="s">
-        <v>224</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
-        <v>224</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s">
-        <v>225</v>
+        <v>97</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J58" t="s">
+        <v>97</v>
+      </c>
+      <c r="K58" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
@@ -3637,31 +3652,31 @@
         <v>205</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E59" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F59" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G59" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H59" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
@@ -3672,31 +3687,31 @@
         <v>205</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
@@ -3707,66 +3722,66 @@
         <v>205</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H61" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>121</v>
+        <v>228</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="H62" t="s">
-        <v>97</v>
+        <v>234</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J62" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
+      <c r="K62">
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
@@ -3777,31 +3792,31 @@
         <v>259</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s">
-        <v>245</v>
+        <v>97</v>
       </c>
       <c r="H63" t="s">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
-      </c>
-      <c r="K63">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J63" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -3812,31 +3827,31 @@
         <v>259</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -3847,31 +3862,31 @@
         <v>259</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H65" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -3882,31 +3897,31 @@
         <v>259</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E66" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G66" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H66" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -3917,66 +3932,66 @@
         <v>259</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>364</v>
+        <v>244</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>365</v>
+        <v>251</v>
       </c>
       <c r="F67" t="s">
-        <v>365</v>
+        <v>251</v>
       </c>
       <c r="G67" t="s">
-        <v>365</v>
+        <v>251</v>
       </c>
       <c r="H67" t="s">
-        <v>366</v>
+        <v>252</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>122</v>
+        <v>364</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E68" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="F68" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="H68" t="s">
-        <v>97</v>
+        <v>366</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J68" t="s">
-        <v>97</v>
-      </c>
-      <c r="K68" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -3987,66 +4002,66 @@
         <v>208</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>264</v>
+        <v>122</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>143</v>
       </c>
       <c r="E69" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s">
-        <v>267</v>
+        <v>97</v>
       </c>
       <c r="H69" t="s">
-        <v>268</v>
+        <v>97</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J69" t="s">
+        <v>97</v>
+      </c>
+      <c r="K69" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="F70" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="G70" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="H70" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J70" t="s">
-        <v>97</v>
-      </c>
-      <c r="K70" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4057,66 +4072,66 @@
         <v>262</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E71" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="F71" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="G71" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="H71" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J71" t="s">
+        <v>97</v>
+      </c>
+      <c r="K71" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>124</v>
+        <v>265</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E72" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="F72" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="G72" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="H72" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J72" t="s">
-        <v>97</v>
-      </c>
-      <c r="K72" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -4127,66 +4142,66 @@
         <v>263</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>266</v>
+        <v>124</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="F73" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="G73" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="H73" t="s">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J73" t="s">
+        <v>97</v>
+      </c>
+      <c r="K73" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>125</v>
+        <v>266</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="F74" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="G74" t="s">
-        <v>97</v>
+        <v>271</v>
       </c>
       <c r="H74" t="s">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J74" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -4197,31 +4212,31 @@
         <v>152</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E75" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F75" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="G75" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="H75" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J75" t="s">
+        <v>97</v>
+      </c>
+      <c r="K75" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -4232,31 +4247,31 @@
         <v>152</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E76" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F76" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G76" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H76" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
@@ -4267,31 +4282,31 @@
         <v>152</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E77" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F77" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G77" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H77" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
@@ -4302,66 +4317,66 @@
         <v>152</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E78" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F78" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G78" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H78" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="F79" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="G79" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="H79" t="s">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J79" t="s">
-        <v>97</v>
-      </c>
-      <c r="K79" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J79">
+        <v>4</v>
+      </c>
+      <c r="K79">
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -4372,31 +4387,31 @@
         <v>209</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>253</v>
+        <v>126</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="F80" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="G80" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="H80" t="s">
-        <v>292</v>
+        <v>97</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J80" s="2">
-        <v>1</v>
-      </c>
-      <c r="K80" s="2">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J80" t="s">
+        <v>97</v>
+      </c>
+      <c r="K80" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -4407,31 +4422,31 @@
         <v>209</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E81" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F81" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G81" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H81" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J81">
-        <v>2</v>
-      </c>
-      <c r="K81">
-        <v>2</v>
+      <c r="J81" s="2">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
@@ -4442,31 +4457,31 @@
         <v>209</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H82" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -4477,31 +4492,31 @@
         <v>209</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H83" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K83">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
@@ -4512,31 +4527,31 @@
         <v>209</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H84" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K84">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
@@ -4547,31 +4562,31 @@
         <v>209</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H85" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -4582,31 +4597,31 @@
         <v>209</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H86" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J86">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K86">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -4617,31 +4632,31 @@
         <v>209</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H87" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J87">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K87">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -4652,31 +4667,31 @@
         <v>209</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="F88" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G88" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="H88" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J88">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K88">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -4687,31 +4702,31 @@
         <v>209</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E89" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="F89" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="G89" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="H89" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J89">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K89">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -4722,31 +4737,31 @@
         <v>209</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H90" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J90">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K90">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
@@ -4757,31 +4772,31 @@
         <v>209</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H91" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J91">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K91">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
@@ -4792,31 +4807,31 @@
         <v>209</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E92" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F92" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G92" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H92" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J92">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K92">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
@@ -4827,66 +4842,66 @@
         <v>209</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E93" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F93" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G93" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H93" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J93">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K93">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E94" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="F94" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="G94" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="H94" t="s">
-        <v>97</v>
+        <v>317</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J94" t="s">
-        <v>97</v>
-      </c>
-      <c r="K94" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J94">
+        <v>14</v>
+      </c>
+      <c r="K94">
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
@@ -4897,31 +4912,31 @@
         <v>210</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E95" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="F95" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="G95" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="H95" t="s">
-        <v>338</v>
+        <v>97</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J95" s="2">
-        <v>1</v>
-      </c>
-      <c r="K95" s="2">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J95" t="s">
+        <v>97</v>
+      </c>
+      <c r="K95" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
@@ -4932,31 +4947,31 @@
         <v>210</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H96" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J96">
-        <v>2</v>
-      </c>
-      <c r="K96">
-        <v>2</v>
+      <c r="J96" s="2">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
@@ -4967,31 +4982,31 @@
         <v>210</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E97" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F97" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G97" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H97" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
@@ -5002,31 +5017,31 @@
         <v>210</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G98" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H98" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
@@ -5037,31 +5052,31 @@
         <v>210</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E99" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F99" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G99" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H99" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K99">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
@@ -5072,31 +5087,31 @@
         <v>210</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E100" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F100" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G100" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H100" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J100">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K100">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
@@ -5107,31 +5122,31 @@
         <v>210</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E101" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F101" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G101" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H101" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K101">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
@@ -5142,31 +5157,31 @@
         <v>210</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E102" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F102" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G102" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H102" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K102">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
@@ -5177,31 +5192,31 @@
         <v>210</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E103" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F103" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G103" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H103" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K103">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
@@ -5212,31 +5227,31 @@
         <v>210</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E104" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="F104" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="G104" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="H104" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K104">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
@@ -5247,31 +5262,31 @@
         <v>210</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E105" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="F105" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="G105" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="H105" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J105">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K105">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
@@ -5282,31 +5297,31 @@
         <v>210</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H106" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J106">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K106">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
@@ -5317,31 +5332,31 @@
         <v>210</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J107">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K107">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
@@ -5352,66 +5367,66 @@
         <v>210</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E108" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F108" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G108" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H108" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J108">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K108">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E109" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="F109" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="G109" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="H109" t="s">
-        <v>97</v>
+        <v>350</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J109" t="s">
-        <v>97</v>
-      </c>
-      <c r="K109" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J109">
+        <v>14</v>
+      </c>
+      <c r="K109">
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
@@ -5422,38 +5437,32 @@
         <v>211</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E110" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="F110" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="G110" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="H110" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J110" s="2">
-        <v>1</v>
-      </c>
-      <c r="K110" s="2">
-        <v>1</v>
-      </c>
-      <c r="L110" s="2"/>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" s="2"/>
-      <c r="Q110" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J110" t="s">
+        <v>97</v>
+      </c>
+      <c r="K110" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
@@ -5463,31 +5472,31 @@
         <v>211</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E111" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F111" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G111" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H111" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -5504,31 +5513,31 @@
         <v>211</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E112" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="F112" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="G112" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="H112" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -5539,38 +5548,44 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E113" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F113" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G113" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="H113" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J113" t="s">
-        <v>97</v>
-      </c>
-      <c r="K113" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J113" s="2">
+        <v>3</v>
+      </c>
+      <c r="K113" s="2">
+        <v>3</v>
+      </c>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2"/>
+      <c r="Q113" s="2"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
@@ -5580,73 +5595,73 @@
         <v>212</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>150</v>
       </c>
       <c r="E114" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="F114" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="G114" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="H114" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J114" s="2">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" s="2"/>
-      <c r="Q114" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J114" t="s">
+        <v>97</v>
+      </c>
+      <c r="K114" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E115" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="F115" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="G115" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="H115" t="s">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J115" t="s">
-        <v>97</v>
-      </c>
-      <c r="K115" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J115" s="2">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="2"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
@@ -5656,38 +5671,73 @@
         <v>213</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E116" t="s">
+        <v>97</v>
+      </c>
+      <c r="F116" t="s">
+        <v>97</v>
+      </c>
+      <c r="G116" t="s">
+        <v>97</v>
+      </c>
+      <c r="H116" t="s">
+        <v>97</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J116" t="s">
+        <v>97</v>
+      </c>
+      <c r="K116" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A117" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E117" t="s">
         <v>67</v>
       </c>
-      <c r="F116" t="s">
+      <c r="F117" t="s">
         <v>67</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G117" t="s">
         <v>67</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H117" t="s">
         <v>68</v>
       </c>
-      <c r="I116" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J116" s="2">
+      <c r="I117" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J117" s="2">
         <v>1</v>
       </c>
-      <c r="K116" s="2">
+      <c r="K117" s="2">
         <v>1</v>
       </c>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2"/>
-      <c r="Q116" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FD59F0-E1EF-C349-AE24-66485BFD7C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA011A32-730A-684C-86CA-1652E207AD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="403">
   <si>
     <t>category</t>
   </si>
@@ -1130,6 +1130,105 @@
   </si>
   <si>
     <t>Gurvashtakam.pdf</t>
+  </si>
+  <si>
+    <t>I005</t>
+  </si>
+  <si>
+    <t>I006</t>
+  </si>
+  <si>
+    <t>I007</t>
+  </si>
+  <si>
+    <t>I008</t>
+  </si>
+  <si>
+    <t>I009</t>
+  </si>
+  <si>
+    <t>I010</t>
+  </si>
+  <si>
+    <t>I011</t>
+  </si>
+  <si>
+    <t>I012</t>
+  </si>
+  <si>
+    <t>I013</t>
+  </si>
+  <si>
+    <t>I014</t>
+  </si>
+  <si>
+    <t>I015</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtotthara_shata_naama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtotthara_shata_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_bhagavati_puraatana_pureshwari_stava.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_kavacham.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_sahasra_naama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_sahasra_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_stava.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_stotram_shankaracharya_virachitam.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_upanishad.pdf</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtakam</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtotthara_shata_naama_stotram</t>
+  </si>
+  <si>
+    <t>Annapoorna_ashtotthara_shata_naamaavali</t>
+  </si>
+  <si>
+    <t>Annapoorna_bhagavati_puraatana_pureshwari_stava</t>
+  </si>
+  <si>
+    <t>Annapoorna_kavacham</t>
+  </si>
+  <si>
+    <t>Annapoorna_sahasra_naama_stotram</t>
+  </si>
+  <si>
+    <t>Annapoorna_sahasra_naamaavali</t>
+  </si>
+  <si>
+    <t>Annapoorna_stava</t>
+  </si>
+  <si>
+    <t>Annapoorna_stotram</t>
+  </si>
+  <si>
+    <t>Annapoorna_stotram_shankaracharya_virachitam</t>
+  </si>
+  <si>
+    <t>Annapoorna_upanishad</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q117"/>
+  <dimension ref="A1:Q128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3614,401 +3713,467 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E58" t="s">
+        <v>392</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>392</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>392</v>
       </c>
       <c r="H58" t="s">
-        <v>97</v>
+        <v>381</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J58" t="s">
-        <v>97</v>
-      </c>
-      <c r="K58" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J58" s="2">
+        <v>5</v>
+      </c>
+      <c r="K58" s="2">
+        <v>5</v>
+      </c>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>223</v>
+        <v>371</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E59" t="s">
-        <v>224</v>
+        <v>393</v>
       </c>
       <c r="F59" t="s">
-        <v>224</v>
+        <v>393</v>
       </c>
       <c r="G59" t="s">
-        <v>224</v>
+        <v>393</v>
       </c>
       <c r="H59" t="s">
-        <v>225</v>
+        <v>382</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
+      <c r="J59" s="2">
+        <v>6</v>
+      </c>
+      <c r="K59" s="2">
+        <v>6</v>
+      </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>226</v>
+        <v>372</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E60" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="F60" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="G60" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="H60" t="s">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J60">
-        <v>2</v>
-      </c>
-      <c r="K60">
-        <v>2</v>
-      </c>
+      <c r="J60" s="2">
+        <v>7</v>
+      </c>
+      <c r="K60" s="2">
+        <v>7</v>
+      </c>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>227</v>
+        <v>373</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>231</v>
+        <v>395</v>
       </c>
       <c r="F61" t="s">
-        <v>231</v>
+        <v>395</v>
       </c>
       <c r="G61" t="s">
-        <v>231</v>
+        <v>395</v>
       </c>
       <c r="H61" t="s">
-        <v>232</v>
+        <v>384</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J61">
-        <v>3</v>
-      </c>
-      <c r="K61">
-        <v>3</v>
-      </c>
+      <c r="J61" s="2">
+        <v>8</v>
+      </c>
+      <c r="K61" s="2">
+        <v>8</v>
+      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>228</v>
+        <v>374</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="F62" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="G62" t="s">
-        <v>233</v>
+        <v>396</v>
       </c>
       <c r="H62" t="s">
-        <v>234</v>
+        <v>385</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J62">
-        <v>4</v>
-      </c>
-      <c r="K62">
-        <v>4</v>
-      </c>
+      <c r="J62" s="2">
+        <v>9</v>
+      </c>
+      <c r="K62" s="2">
+        <v>9</v>
+      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>121</v>
+        <v>375</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="G63" t="s">
-        <v>97</v>
+        <v>397</v>
       </c>
       <c r="H63" t="s">
-        <v>97</v>
+        <v>386</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J63" t="s">
-        <v>97</v>
-      </c>
-      <c r="K63" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J63" s="2">
+        <v>10</v>
+      </c>
+      <c r="K63" s="2">
+        <v>10</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>241</v>
+        <v>376</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E64" t="s">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="F64" t="s">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="G64" t="s">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="H64" t="s">
-        <v>246</v>
+        <v>387</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J64">
-        <v>1</v>
-      </c>
-      <c r="K64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J64" s="2">
+        <v>11</v>
+      </c>
+      <c r="K64" s="2">
+        <v>11</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>242</v>
+        <v>377</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E65" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="F65" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="G65" t="s">
-        <v>247</v>
+        <v>399</v>
       </c>
       <c r="H65" t="s">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J65">
-        <v>2</v>
-      </c>
-      <c r="K65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J65" s="2">
+        <v>12</v>
+      </c>
+      <c r="K65" s="2">
+        <v>12</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>243</v>
+        <v>378</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="F66" t="s">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="G66" t="s">
-        <v>249</v>
+        <v>400</v>
       </c>
       <c r="H66" t="s">
-        <v>250</v>
+        <v>389</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J66">
-        <v>3</v>
-      </c>
-      <c r="K66">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J66" s="2">
+        <v>13</v>
+      </c>
+      <c r="K66" s="2">
+        <v>13</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>244</v>
+        <v>379</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E67" t="s">
-        <v>251</v>
+        <v>401</v>
       </c>
       <c r="F67" t="s">
-        <v>251</v>
+        <v>401</v>
       </c>
       <c r="G67" t="s">
-        <v>251</v>
+        <v>401</v>
       </c>
       <c r="H67" t="s">
-        <v>252</v>
+        <v>390</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J67">
-        <v>4</v>
-      </c>
-      <c r="K67">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J67" s="2">
+        <v>14</v>
+      </c>
+      <c r="K67" s="2">
+        <v>14</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="F68" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="G68" t="s">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="H68" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J68">
-        <v>5</v>
-      </c>
-      <c r="K68">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J68" s="2">
+        <v>15</v>
+      </c>
+      <c r="K68" s="2">
+        <v>15</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E69" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="F69" t="s">
         <v>97</v>
@@ -4016,9 +4181,6 @@
       <c r="G69" t="s">
         <v>97</v>
       </c>
-      <c r="H69" t="s">
-        <v>97</v>
-      </c>
       <c r="I69" s="2" t="s">
         <v>97</v>
       </c>
@@ -4029,30 +4191,30 @@
         <v>97</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E70" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="F70" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G70" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="H70" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>70</v>
@@ -4064,333 +4226,333 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="G71" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="H71" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J71" t="s">
-        <v>97</v>
-      </c>
-      <c r="K71" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>262</v>
+        <v>205</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E72" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="G72" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="H72" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J72">
+        <v>3</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E73" t="s">
+        <v>233</v>
+      </c>
+      <c r="F73" t="s">
+        <v>233</v>
+      </c>
+      <c r="G73" t="s">
+        <v>233</v>
+      </c>
+      <c r="H73" t="s">
+        <v>234</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E74" t="s">
+        <v>97</v>
+      </c>
+      <c r="F74" t="s">
+        <v>97</v>
+      </c>
+      <c r="G74" t="s">
+        <v>97</v>
+      </c>
+      <c r="H74" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J74" t="s">
+        <v>97</v>
+      </c>
+      <c r="K74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E75" t="s">
+        <v>245</v>
+      </c>
+      <c r="F75" t="s">
+        <v>245</v>
+      </c>
+      <c r="G75" t="s">
+        <v>245</v>
+      </c>
+      <c r="H75" t="s">
+        <v>246</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J75">
         <v>1</v>
       </c>
-      <c r="K72">
+      <c r="K75">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" t="s">
-        <v>97</v>
-      </c>
-      <c r="F73" t="s">
-        <v>97</v>
-      </c>
-      <c r="G73" t="s">
-        <v>97</v>
-      </c>
-      <c r="H73" t="s">
-        <v>97</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E74" t="s">
-        <v>271</v>
-      </c>
-      <c r="F74" t="s">
-        <v>271</v>
-      </c>
-      <c r="G74" t="s">
-        <v>271</v>
-      </c>
-      <c r="H74" t="s">
-        <v>272</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="K74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E75" t="s">
-        <v>97</v>
-      </c>
-      <c r="F75" t="s">
-        <v>97</v>
-      </c>
-      <c r="G75" t="s">
-        <v>97</v>
-      </c>
-      <c r="H75" t="s">
-        <v>97</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J75" t="s">
-        <v>97</v>
-      </c>
-      <c r="K75" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="F76" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="G76" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="H76" t="s">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E77" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="F77" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="G77" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="H77" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E78" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="F78" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="G78" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="H78" t="s">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E79" t="s">
-        <v>195</v>
+        <v>365</v>
       </c>
       <c r="F79" t="s">
-        <v>195</v>
+        <v>365</v>
       </c>
       <c r="G79" t="s">
-        <v>195</v>
+        <v>365</v>
       </c>
       <c r="H79" t="s">
-        <v>196</v>
+        <v>366</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J79">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K79">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E80" t="s">
         <v>97</v>
@@ -4416,352 +4578,352 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E81" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="F81" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="G81" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="H81" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81">
         <v>1</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E82" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="F82" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G82" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="H82" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J82">
-        <v>2</v>
-      </c>
-      <c r="K82">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J82" t="s">
+        <v>97</v>
+      </c>
+      <c r="K82" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="F83" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="G83" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="H83" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K83">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>281</v>
+        <v>124</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E84" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="F84" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="G84" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="H84" t="s">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J84">
-        <v>4</v>
-      </c>
-      <c r="K84">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J84" t="s">
+        <v>97</v>
+      </c>
+      <c r="K84" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E85" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="F85" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="G85" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="H85" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K85">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>283</v>
+        <v>125</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E86" t="s">
-        <v>309</v>
+        <v>97</v>
       </c>
       <c r="F86" t="s">
-        <v>309</v>
+        <v>97</v>
       </c>
       <c r="G86" t="s">
-        <v>309</v>
+        <v>97</v>
       </c>
       <c r="H86" t="s">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J86">
-        <v>6</v>
-      </c>
-      <c r="K86">
-        <v>6</v>
+        <v>97</v>
+      </c>
+      <c r="J86" t="s">
+        <v>97</v>
+      </c>
+      <c r="K86" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E87" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="F87" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="G87" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="H87" t="s">
-        <v>298</v>
+        <v>187</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J87">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K87">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>285</v>
+        <v>190</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E88" t="s">
-        <v>311</v>
+        <v>188</v>
       </c>
       <c r="F88" t="s">
-        <v>311</v>
+        <v>188</v>
       </c>
       <c r="G88" t="s">
-        <v>311</v>
+        <v>188</v>
       </c>
       <c r="H88" t="s">
-        <v>299</v>
+        <v>189</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J88">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K88">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>286</v>
+        <v>191</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E89" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="F89" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="G89" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="H89" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J89">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K89">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="F90" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="G90" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="H90" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J90">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K90">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
@@ -4772,31 +4934,31 @@
         <v>209</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>288</v>
+        <v>126</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>313</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s">
-        <v>313</v>
+        <v>97</v>
       </c>
       <c r="G91" t="s">
-        <v>313</v>
+        <v>97</v>
       </c>
       <c r="H91" t="s">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J91">
-        <v>11</v>
-      </c>
-      <c r="K91">
-        <v>11</v>
+        <v>97</v>
+      </c>
+      <c r="J91" t="s">
+        <v>97</v>
+      </c>
+      <c r="K91" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
@@ -4807,31 +4969,31 @@
         <v>209</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E92" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F92" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="G92" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="H92" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J92">
-        <v>12</v>
-      </c>
-      <c r="K92">
-        <v>12</v>
+      <c r="J92" s="2">
+        <v>1</v>
+      </c>
+      <c r="K92" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
@@ -4842,31 +5004,31 @@
         <v>209</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E93" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F93" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G93" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="H93" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J93">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K93">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
@@ -4877,419 +5039,419 @@
         <v>209</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E94" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="F94" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G94" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="H94" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J94">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K94">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="F95" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="G95" t="s">
-        <v>97</v>
+        <v>307</v>
       </c>
       <c r="H95" t="s">
-        <v>97</v>
+        <v>295</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J95" t="s">
-        <v>97</v>
-      </c>
-      <c r="K95" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J95">
+        <v>4</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E96" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="F96" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="G96" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="H96" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J96" s="2">
-        <v>1</v>
-      </c>
-      <c r="K96" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J96">
+        <v>5</v>
+      </c>
+      <c r="K96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E97" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="F97" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="G97" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="H97" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J97">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E98" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F98" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="G98" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="H98" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J98">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K98">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E99" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="F99" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="G99" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="H99" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J99">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K99">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E100" t="s">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="F100" t="s">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="G100" t="s">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="H100" t="s">
-        <v>342</v>
+        <v>256</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J100">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K100">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="F101" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="G101" t="s">
-        <v>356</v>
+        <v>312</v>
       </c>
       <c r="H101" t="s">
-        <v>343</v>
+        <v>300</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K101">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E102" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="F102" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="G102" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="H102" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K102">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E103" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
       <c r="F103" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
       <c r="G103" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
       <c r="H103" t="s">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K103">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E104" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="F104" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="G104" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="H104" t="s">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K104">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="F105" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="G105" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="H105" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J105">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K105">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>113</v>
       </c>
@@ -5297,34 +5459,34 @@
         <v>210</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>334</v>
+        <v>130</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E106" t="s">
-        <v>360</v>
+        <v>97</v>
       </c>
       <c r="F106" t="s">
-        <v>360</v>
+        <v>97</v>
       </c>
       <c r="G106" t="s">
-        <v>360</v>
+        <v>97</v>
       </c>
       <c r="H106" t="s">
-        <v>347</v>
+        <v>97</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J106">
-        <v>11</v>
-      </c>
-      <c r="K106">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="J106" t="s">
+        <v>97</v>
+      </c>
+      <c r="K106" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>113</v>
       </c>
@@ -5332,34 +5494,34 @@
         <v>210</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>335</v>
+        <v>254</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E107" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F107" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="G107" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="H107" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J107">
-        <v>12</v>
-      </c>
-      <c r="K107">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J107" s="2">
+        <v>1</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>113</v>
       </c>
@@ -5367,34 +5529,34 @@
         <v>210</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E108" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F108" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G108" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="H108" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J108">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K108">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>113</v>
       </c>
@@ -5402,342 +5564,727 @@
         <v>210</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E109" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F109" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="G109" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="H109" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J109">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K109">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>127</v>
+        <v>327</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E110" t="s">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="F110" t="s">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="G110" t="s">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="H110" t="s">
-        <v>97</v>
+        <v>341</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J110" t="s">
-        <v>97</v>
-      </c>
-      <c r="K110" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="J110">
+        <v>4</v>
+      </c>
+      <c r="K110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>218</v>
+        <v>328</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E111" t="s">
-        <v>177</v>
+        <v>355</v>
       </c>
       <c r="F111" t="s">
-        <v>177</v>
+        <v>355</v>
       </c>
       <c r="G111" t="s">
-        <v>177</v>
+        <v>355</v>
       </c>
       <c r="H111" t="s">
-        <v>178</v>
+        <v>342</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J111" s="2">
-        <v>1</v>
-      </c>
-      <c r="K111" s="2">
-        <v>1</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" s="2"/>
-      <c r="Q111" s="2"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J111">
+        <v>5</v>
+      </c>
+      <c r="K111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>219</v>
+        <v>329</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E112" t="s">
-        <v>175</v>
+        <v>356</v>
       </c>
       <c r="F112" t="s">
-        <v>175</v>
+        <v>356</v>
       </c>
       <c r="G112" t="s">
-        <v>175</v>
+        <v>356</v>
       </c>
       <c r="H112" t="s">
-        <v>176</v>
+        <v>343</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J112" s="2">
-        <v>2</v>
-      </c>
-      <c r="K112" s="2">
-        <v>2</v>
-      </c>
-      <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" s="2"/>
-      <c r="Q112" s="2"/>
+      <c r="J112">
+        <v>6</v>
+      </c>
+      <c r="K112">
+        <v>6</v>
+      </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E113" t="s">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="F113" t="s">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="G113" t="s">
-        <v>222</v>
+        <v>357</v>
       </c>
       <c r="H113" t="s">
-        <v>221</v>
+        <v>344</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J113" s="2">
-        <v>3</v>
-      </c>
-      <c r="K113" s="2">
-        <v>3</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" s="2"/>
-      <c r="Q113" s="2"/>
+      <c r="J113">
+        <v>7</v>
+      </c>
+      <c r="K113">
+        <v>7</v>
+      </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>128</v>
+        <v>331</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="F114" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="G114" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="H114" t="s">
-        <v>97</v>
+        <v>345</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J114" t="s">
-        <v>97</v>
-      </c>
-      <c r="K114" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J114">
+        <v>8</v>
+      </c>
+      <c r="K114">
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>216</v>
+        <v>359</v>
       </c>
       <c r="F115" t="s">
-        <v>216</v>
+        <v>359</v>
       </c>
       <c r="G115" t="s">
-        <v>216</v>
+        <v>359</v>
       </c>
       <c r="H115" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J115" s="2">
-        <v>1</v>
-      </c>
-      <c r="K115" s="2">
-        <v>1</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" s="2"/>
-      <c r="Q115" s="2"/>
+      <c r="J115">
+        <v>9</v>
+      </c>
+      <c r="K115">
+        <v>9</v>
+      </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>129</v>
+        <v>333</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E116" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="F116" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="G116" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="H116" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J116" t="s">
-        <v>97</v>
-      </c>
-      <c r="K116" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J116">
+        <v>10</v>
+      </c>
+      <c r="K116">
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E117" t="s">
+        <v>360</v>
+      </c>
+      <c r="F117" t="s">
+        <v>360</v>
+      </c>
+      <c r="G117" t="s">
+        <v>360</v>
+      </c>
+      <c r="H117" t="s">
+        <v>347</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J117">
+        <v>11</v>
+      </c>
+      <c r="K117">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A118" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E118" t="s">
+        <v>361</v>
+      </c>
+      <c r="F118" t="s">
+        <v>361</v>
+      </c>
+      <c r="G118" t="s">
+        <v>361</v>
+      </c>
+      <c r="H118" t="s">
+        <v>348</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J118">
+        <v>12</v>
+      </c>
+      <c r="K118">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A119" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E119" t="s">
+        <v>362</v>
+      </c>
+      <c r="F119" t="s">
+        <v>362</v>
+      </c>
+      <c r="G119" t="s">
+        <v>362</v>
+      </c>
+      <c r="H119" t="s">
+        <v>349</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J119">
+        <v>13</v>
+      </c>
+      <c r="K119">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A120" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E120" t="s">
+        <v>363</v>
+      </c>
+      <c r="F120" t="s">
+        <v>363</v>
+      </c>
+      <c r="G120" t="s">
+        <v>363</v>
+      </c>
+      <c r="H120" t="s">
+        <v>350</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J120">
+        <v>14</v>
+      </c>
+      <c r="K120">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A121" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E121" t="s">
+        <v>97</v>
+      </c>
+      <c r="F121" t="s">
+        <v>97</v>
+      </c>
+      <c r="G121" t="s">
+        <v>97</v>
+      </c>
+      <c r="H121" t="s">
+        <v>97</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J121" t="s">
+        <v>97</v>
+      </c>
+      <c r="K121" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A122" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E122" t="s">
+        <v>177</v>
+      </c>
+      <c r="F122" t="s">
+        <v>177</v>
+      </c>
+      <c r="G122" t="s">
+        <v>177</v>
+      </c>
+      <c r="H122" t="s">
+        <v>178</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J122" s="2">
+        <v>1</v>
+      </c>
+      <c r="K122" s="2">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E123" t="s">
+        <v>175</v>
+      </c>
+      <c r="F123" t="s">
+        <v>175</v>
+      </c>
+      <c r="G123" t="s">
+        <v>175</v>
+      </c>
+      <c r="H123" t="s">
+        <v>176</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J123" s="2">
+        <v>2</v>
+      </c>
+      <c r="K123" s="2">
+        <v>2</v>
+      </c>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" s="2"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E124" t="s">
+        <v>222</v>
+      </c>
+      <c r="F124" t="s">
+        <v>222</v>
+      </c>
+      <c r="G124" t="s">
+        <v>222</v>
+      </c>
+      <c r="H124" t="s">
+        <v>221</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J124" s="2">
+        <v>3</v>
+      </c>
+      <c r="K124" s="2">
+        <v>3</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" s="2"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E125" t="s">
+        <v>97</v>
+      </c>
+      <c r="F125" t="s">
+        <v>97</v>
+      </c>
+      <c r="G125" t="s">
+        <v>97</v>
+      </c>
+      <c r="H125" t="s">
+        <v>97</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J125" t="s">
+        <v>97</v>
+      </c>
+      <c r="K125" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E126" t="s">
+        <v>216</v>
+      </c>
+      <c r="F126" t="s">
+        <v>216</v>
+      </c>
+      <c r="G126" t="s">
+        <v>216</v>
+      </c>
+      <c r="H126" t="s">
+        <v>217</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J126" s="2">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2"/>
+      <c r="M126" s="2"/>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" s="2"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B127" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C127" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E127" t="s">
+        <v>97</v>
+      </c>
+      <c r="F127" t="s">
+        <v>97</v>
+      </c>
+      <c r="G127" t="s">
+        <v>97</v>
+      </c>
+      <c r="H127" t="s">
+        <v>97</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J127" t="s">
+        <v>97</v>
+      </c>
+      <c r="K127" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E128" t="s">
         <v>67</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F128" t="s">
         <v>67</v>
       </c>
-      <c r="G117" t="s">
+      <c r="G128" t="s">
         <v>67</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H128" t="s">
         <v>68</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J117" s="2">
+      <c r="I128" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J128" s="2">
         <v>1</v>
       </c>
-      <c r="K117" s="2">
+      <c r="K128" s="2">
         <v>1</v>
       </c>
-      <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
-      <c r="P117" s="2"/>
-      <c r="Q117" s="2"/>
+      <c r="L128" s="2"/>
+      <c r="M128" s="2"/>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/Already backed up sangrahaalaya on 10202026 9.30 pm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA011A32-730A-684C-86CA-1652E207AD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD61464-6ED4-DA49-AB89-7BFEFEC1D4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="409">
   <si>
     <t>category</t>
   </si>
@@ -1229,6 +1229,24 @@
   </si>
   <si>
     <t>Annapoorna_upanishad</t>
+  </si>
+  <si>
+    <t>H005</t>
+  </si>
+  <si>
+    <t>H006</t>
+  </si>
+  <si>
+    <t>Guru_geetha</t>
+  </si>
+  <si>
+    <t>Guru_geetha.pdf</t>
+  </si>
+  <si>
+    <t>Guru_paaduka_panchakam</t>
+  </si>
+  <si>
+    <t>Guru_paaduka_panchakam.pdf</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q128"/>
+  <dimension ref="A1:Q130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3514,72 +3532,78 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>119</v>
+        <v>403</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E53" t="s">
-        <v>97</v>
-      </c>
-      <c r="F53" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" t="s">
-        <v>97</v>
-      </c>
-      <c r="H53" t="s">
-        <v>97</v>
+        <v>139</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>406</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J53" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J53" s="2">
+        <v>5</v>
+      </c>
+      <c r="K53" s="2">
+        <v>5</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>198</v>
+        <v>404</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>183</v>
+        <v>407</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>183</v>
+        <v>407</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>183</v>
+        <v>407</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>184</v>
+        <v>408</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J54" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K54" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -3596,38 +3620,32 @@
         <v>197</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="F55" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H55" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J55" s="2">
-        <v>2</v>
-      </c>
-      <c r="K55" s="2">
-        <v>2</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="2"/>
-      <c r="Q55" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J55" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
@@ -3637,31 +3655,31 @@
         <v>197</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E56" t="s">
-        <v>237</v>
-      </c>
-      <c r="F56" t="s">
-        <v>237</v>
-      </c>
-      <c r="G56" t="s">
-        <v>237</v>
-      </c>
-      <c r="H56" t="s">
-        <v>238</v>
+      <c r="E56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J56" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -3678,31 +3696,31 @@
         <v>197</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>236</v>
+        <v>203</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E57" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="G57" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="H57" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J57" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K57" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -3719,31 +3737,31 @@
         <v>197</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>370</v>
+        <v>235</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E58" t="s">
-        <v>392</v>
+        <v>237</v>
       </c>
       <c r="F58" t="s">
-        <v>392</v>
+        <v>237</v>
       </c>
       <c r="G58" t="s">
-        <v>392</v>
+        <v>237</v>
       </c>
       <c r="H58" t="s">
-        <v>381</v>
+        <v>238</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J58" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -3760,31 +3778,31 @@
         <v>197</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>371</v>
+        <v>236</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E59" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
       <c r="F59" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
       <c r="G59" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
       <c r="H59" t="s">
-        <v>382</v>
+        <v>240</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J59" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -3801,31 +3819,31 @@
         <v>197</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E60" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F60" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G60" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H60" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J60" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K60" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -3842,31 +3860,31 @@
         <v>197</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H61" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J61" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K61" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -3883,31 +3901,31 @@
         <v>197</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E62" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F62" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G62" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H62" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J62" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K62" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -3924,31 +3942,31 @@
         <v>197</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E63" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F63" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G63" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H63" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J63" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K63" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -3965,31 +3983,31 @@
         <v>197</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E64" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F64" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G64" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H64" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J64" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K64" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -4006,31 +4024,31 @@
         <v>197</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E65" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F65" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G65" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H65" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J65" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K65" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -4047,31 +4065,31 @@
         <v>197</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H66" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J66" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K66" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -4088,31 +4106,31 @@
         <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E67" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F67" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G67" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H67" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J67" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K67" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -4129,31 +4147,31 @@
         <v>197</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F68" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G68" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H68" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J68" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K68" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -4164,67 +4182,85 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>120</v>
+        <v>379</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E69" t="s">
+        <v>401</v>
       </c>
       <c r="F69" t="s">
-        <v>97</v>
+        <v>401</v>
       </c>
       <c r="G69" t="s">
-        <v>97</v>
+        <v>401</v>
+      </c>
+      <c r="H69" t="s">
+        <v>390</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J69" t="s">
-        <v>97</v>
-      </c>
-      <c r="K69" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J69" s="2">
+        <v>14</v>
+      </c>
+      <c r="K69" s="2">
+        <v>14</v>
+      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>223</v>
+        <v>380</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>224</v>
+        <v>402</v>
       </c>
       <c r="F70" t="s">
-        <v>224</v>
+        <v>402</v>
       </c>
       <c r="G70" t="s">
-        <v>224</v>
+        <v>402</v>
       </c>
       <c r="H70" t="s">
-        <v>225</v>
+        <v>391</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="K70">
-        <v>1</v>
-      </c>
+      <c r="J70" s="2">
+        <v>15</v>
+      </c>
+      <c r="K70" s="2">
+        <v>15</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
@@ -4234,31 +4270,25 @@
         <v>205</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E71" t="s">
-        <v>229</v>
-      </c>
       <c r="F71" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
-      </c>
-      <c r="H71" t="s">
-        <v>230</v>
+        <v>97</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J71">
-        <v>2</v>
-      </c>
-      <c r="K71">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J71" t="s">
+        <v>97</v>
+      </c>
+      <c r="K71" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
@@ -4269,31 +4299,31 @@
         <v>205</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E72" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F72" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G72" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="H72" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
@@ -4304,101 +4334,101 @@
         <v>205</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E73" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F73" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G73" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H73" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K73">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="F74" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="G74" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="H74" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J74" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E75" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F75" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G75" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="H75" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
@@ -4409,31 +4439,31 @@
         <v>259</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E76" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="F76" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s">
-        <v>247</v>
+        <v>97</v>
       </c>
       <c r="H76" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J76">
-        <v>2</v>
-      </c>
-      <c r="K76">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J76" t="s">
+        <v>97</v>
+      </c>
+      <c r="K76" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
@@ -4444,31 +4474,31 @@
         <v>259</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E77" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F77" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G77" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H77" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
@@ -4479,31 +4509,31 @@
         <v>259</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E78" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F78" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G78" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H78" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
@@ -4514,115 +4544,115 @@
         <v>259</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>364</v>
+        <v>243</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E79" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="F79" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="G79" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="H79" t="s">
-        <v>366</v>
+        <v>250</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="F80" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="G80" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="H80" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J80" t="s">
-        <v>97</v>
-      </c>
-      <c r="K80" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
+      <c r="K80">
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>264</v>
+        <v>364</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="F81" t="s">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="G81" t="s">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="H81" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E82" t="s">
         <v>97</v>
@@ -4648,28 +4678,28 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F83" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G83" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H83" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
@@ -4683,16 +4713,16 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E84" t="s">
         <v>97</v>
@@ -4718,28 +4748,28 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H85" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
@@ -4753,16 +4783,16 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" t="s">
         <v>97</v>
@@ -4788,28 +4818,28 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E87" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="F87" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="G87" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="H87" t="s">
-        <v>187</v>
+        <v>272</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>70</v>
@@ -4829,31 +4859,31 @@
         <v>152</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E88" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F88" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="G88" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="H88" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J88">
-        <v>2</v>
-      </c>
-      <c r="K88">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J88" t="s">
+        <v>97</v>
+      </c>
+      <c r="K88" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -4864,31 +4894,31 @@
         <v>152</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H89" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K89">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -4899,101 +4929,101 @@
         <v>152</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F90" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G90" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H90" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K90">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E91" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="F91" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="G91" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="H91" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J91" t="s">
-        <v>97</v>
-      </c>
-      <c r="K91" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J91">
+        <v>3</v>
+      </c>
+      <c r="K91">
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E92" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="G92" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="H92" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J92" s="2">
-        <v>1</v>
-      </c>
-      <c r="K92" s="2">
-        <v>1</v>
+      <c r="J92">
+        <v>4</v>
+      </c>
+      <c r="K92">
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
@@ -5004,31 +5034,31 @@
         <v>209</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E93" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="F93" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G93" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="H93" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J93">
-        <v>2</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J93" t="s">
+        <v>97</v>
+      </c>
+      <c r="K93" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
@@ -5039,31 +5069,31 @@
         <v>209</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E94" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F94" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G94" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H94" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J94">
-        <v>3</v>
-      </c>
-      <c r="K94">
-        <v>3</v>
+      <c r="J94" s="2">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
@@ -5074,31 +5104,31 @@
         <v>209</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F95" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G95" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H95" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K95">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
@@ -5109,31 +5139,31 @@
         <v>209</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E96" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F96" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G96" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H96" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K96">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
@@ -5144,31 +5174,31 @@
         <v>209</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E97" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F97" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G97" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H97" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J97">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K97">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
@@ -5179,31 +5209,31 @@
         <v>209</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E98" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F98" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G98" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H98" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J98">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K98">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -5214,31 +5244,31 @@
         <v>209</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H99" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K99">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
@@ -5249,31 +5279,31 @@
         <v>209</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E100" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="F100" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="G100" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="H100" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J100">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K100">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
@@ -5284,31 +5314,31 @@
         <v>209</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F101" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G101" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H101" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K101">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
@@ -5319,31 +5349,31 @@
         <v>209</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E102" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="F102" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="G102" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="H102" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K102">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
@@ -5354,31 +5384,31 @@
         <v>209</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G103" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K103">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
@@ -5389,31 +5419,31 @@
         <v>209</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G104" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H104" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K104">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
@@ -5424,101 +5454,101 @@
         <v>209</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H105" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J105">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K105">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E106" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="F106" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="G106" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="H106" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J106" t="s">
-        <v>97</v>
-      </c>
-      <c r="K106" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J106">
+        <v>13</v>
+      </c>
+      <c r="K106">
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="F107" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="G107" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="H107" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J107" s="2">
-        <v>1</v>
-      </c>
-      <c r="K107" s="2">
-        <v>1</v>
+      <c r="J107">
+        <v>14</v>
+      </c>
+      <c r="K107">
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
@@ -5529,31 +5559,31 @@
         <v>210</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E108" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="F108" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="G108" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="H108" t="s">
-        <v>339</v>
+        <v>97</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J108">
-        <v>2</v>
-      </c>
-      <c r="K108">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J108" t="s">
+        <v>97</v>
+      </c>
+      <c r="K108" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -5564,31 +5594,31 @@
         <v>210</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E109" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F109" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G109" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H109" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J109">
-        <v>3</v>
-      </c>
-      <c r="K109">
-        <v>3</v>
+      <c r="J109" s="2">
+        <v>1</v>
+      </c>
+      <c r="K109" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
@@ -5599,31 +5629,31 @@
         <v>210</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E110" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F110" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G110" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H110" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K110">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -5634,31 +5664,31 @@
         <v>210</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E111" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F111" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G111" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H111" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K111">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5669,31 +5699,31 @@
         <v>210</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E112" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F112" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G112" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H112" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J112">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K112">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
@@ -5704,31 +5734,31 @@
         <v>210</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E113" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F113" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G113" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H113" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J113">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K113">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
@@ -5739,31 +5769,31 @@
         <v>210</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F114" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G114" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H114" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J114">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K114">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
@@ -5774,31 +5804,31 @@
         <v>210</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F115" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G115" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H115" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K115">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
@@ -5809,31 +5839,31 @@
         <v>210</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E116" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="F116" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="G116" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="H116" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K116">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
@@ -5844,31 +5874,31 @@
         <v>210</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E117" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F117" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G117" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H117" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K117">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
@@ -5879,31 +5909,31 @@
         <v>210</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E118" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F118" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="G118" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="H118" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K118">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
@@ -5914,31 +5944,31 @@
         <v>210</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E119" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F119" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G119" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H119" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K119">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
@@ -5949,108 +5979,102 @@
         <v>210</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E120" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F120" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G120" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H120" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J120">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K120">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="F121" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="G121" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="H121" t="s">
-        <v>97</v>
+        <v>349</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J121" t="s">
-        <v>97</v>
-      </c>
-      <c r="K121" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J121">
+        <v>13</v>
+      </c>
+      <c r="K121">
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E122" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="F122" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="G122" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="H122" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J122" s="2">
-        <v>1</v>
-      </c>
-      <c r="K122" s="2">
-        <v>1</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" s="2"/>
-      <c r="Q122" s="2"/>
+      <c r="J122">
+        <v>14</v>
+      </c>
+      <c r="K122">
+        <v>14</v>
+      </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
@@ -6060,38 +6084,32 @@
         <v>211</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E123" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="F123" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="G123" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H123" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J123" s="2">
-        <v>2</v>
-      </c>
-      <c r="K123" s="2">
-        <v>2</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" s="2"/>
-      <c r="Q123" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J123" t="s">
+        <v>97</v>
+      </c>
+      <c r="K123" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
@@ -6101,31 +6119,31 @@
         <v>211</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E124" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="F124" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="G124" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="H124" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K124" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -6136,72 +6154,78 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>128</v>
+        <v>219</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E125" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F125" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H125" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J125" t="s">
-        <v>97</v>
-      </c>
-      <c r="K125" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J125" s="2">
+        <v>2</v>
+      </c>
+      <c r="K125" s="2">
+        <v>2</v>
+      </c>
+      <c r="L125" s="2"/>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" s="2"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E126" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F126" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G126" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H126" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J126" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K126" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -6212,16 +6236,16 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E127" t="s">
         <v>97</v>
@@ -6247,28 +6271,28 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E128" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F128" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="G128" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="H128" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
@@ -6286,6 +6310,82 @@
       <c r="P128" s="2"/>
       <c r="Q128" s="2"/>
     </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E129" t="s">
+        <v>97</v>
+      </c>
+      <c r="F129" t="s">
+        <v>97</v>
+      </c>
+      <c r="G129" t="s">
+        <v>97</v>
+      </c>
+      <c r="H129" t="s">
+        <v>97</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J129" t="s">
+        <v>97</v>
+      </c>
+      <c r="K129" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A130" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E130" t="s">
+        <v>67</v>
+      </c>
+      <c r="F130" t="s">
+        <v>67</v>
+      </c>
+      <c r="G130" t="s">
+        <v>67</v>
+      </c>
+      <c r="H130" t="s">
+        <v>68</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J130" s="2">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1</v>
+      </c>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" s="2"/>
+      <c r="Q130" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/Already backed up sangrahaalaya on 10202026 9.30 pm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD61464-6ED4-DA49-AB89-7BFEFEC1D4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD45396-E3E7-2541-9DC8-82410D815AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="424">
   <si>
     <t>category</t>
   </si>
@@ -1247,6 +1247,51 @@
   </si>
   <si>
     <t>Guru_paaduka_panchakam.pdf</t>
+  </si>
+  <si>
+    <t>I016</t>
+  </si>
+  <si>
+    <t>I017</t>
+  </si>
+  <si>
+    <t>I018</t>
+  </si>
+  <si>
+    <t>I019</t>
+  </si>
+  <si>
+    <t>I020</t>
+  </si>
+  <si>
+    <t>Shri_Thrylokyavijayaa_Aparaajitha_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Thrylokyavijayaa_Aparaajitha_stotram</t>
+  </si>
+  <si>
+    <t>Durga_devi_Aparaadha_kshamaapana_stotram</t>
+  </si>
+  <si>
+    <t>Durga_devi_Aparaadha_kshamaapana_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Ambika_ashtotthara_shata_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Ambika_ashtotthara_shata_naamaavali</t>
+  </si>
+  <si>
+    <t>Argalaa_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Argalaa_stotram</t>
+  </si>
+  <si>
+    <t>aaryaa_durga_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>aaryaa_durga_ashtakam</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q130"/>
+  <dimension ref="A1:Q135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -4264,196 +4309,226 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>120</v>
+        <v>409</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E71" t="s">
+        <v>415</v>
       </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>415</v>
       </c>
       <c r="G71" t="s">
-        <v>97</v>
+        <v>415</v>
+      </c>
+      <c r="H71" t="s">
+        <v>414</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J71" t="s">
-        <v>97</v>
-      </c>
-      <c r="K71" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J71" s="2">
+        <v>16</v>
+      </c>
+      <c r="K71" s="2">
+        <v>16</v>
+      </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>223</v>
+        <v>410</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
-        <v>224</v>
+        <v>416</v>
       </c>
       <c r="F72" t="s">
-        <v>224</v>
+        <v>416</v>
       </c>
       <c r="G72" t="s">
-        <v>224</v>
+        <v>416</v>
       </c>
       <c r="H72" t="s">
-        <v>225</v>
+        <v>417</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
-      </c>
+      <c r="J72" s="2">
+        <v>17</v>
+      </c>
+      <c r="K72" s="2">
+        <v>17</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>226</v>
+        <v>411</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
-        <v>229</v>
+        <v>419</v>
       </c>
       <c r="F73" t="s">
-        <v>229</v>
+        <v>419</v>
       </c>
       <c r="G73" t="s">
-        <v>229</v>
+        <v>419</v>
       </c>
       <c r="H73" t="s">
-        <v>230</v>
+        <v>418</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J73">
-        <v>2</v>
-      </c>
-      <c r="K73">
-        <v>2</v>
-      </c>
+      <c r="J73" s="2">
+        <v>18</v>
+      </c>
+      <c r="K73" s="2">
+        <v>18</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>227</v>
+        <v>412</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E74" t="s">
-        <v>231</v>
+        <v>421</v>
       </c>
       <c r="F74" t="s">
-        <v>231</v>
+        <v>421</v>
       </c>
       <c r="G74" t="s">
-        <v>231</v>
+        <v>421</v>
       </c>
       <c r="H74" t="s">
-        <v>232</v>
+        <v>420</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J74">
-        <v>3</v>
-      </c>
-      <c r="K74">
-        <v>3</v>
-      </c>
+      <c r="J74" s="2">
+        <v>19</v>
+      </c>
+      <c r="K74" s="2">
+        <v>19</v>
+      </c>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>228</v>
+        <v>413</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E75" t="s">
-        <v>233</v>
+        <v>423</v>
       </c>
       <c r="F75" t="s">
-        <v>233</v>
+        <v>423</v>
       </c>
       <c r="G75" t="s">
-        <v>233</v>
+        <v>423</v>
       </c>
       <c r="H75" t="s">
-        <v>234</v>
+        <v>422</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J75">
-        <v>4</v>
-      </c>
-      <c r="K75">
-        <v>4</v>
-      </c>
+      <c r="J75" s="2">
+        <v>20</v>
+      </c>
+      <c r="K75" s="2">
+        <v>20</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E76" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="F76" t="s">
         <v>97</v>
       </c>
       <c r="G76" t="s">
-        <v>97</v>
-      </c>
-      <c r="H76" t="s">
         <v>97</v>
       </c>
       <c r="I76" s="2" t="s">
@@ -4468,28 +4543,28 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E77" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="F77" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G77" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="H77" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
@@ -4503,28 +4578,28 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E78" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="F78" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="G78" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="H78" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
@@ -4538,28 +4613,28 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E79" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="F79" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="G79" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="H79" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
@@ -4573,28 +4648,28 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E80" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="F80" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="G80" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="H80" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>70</v>
@@ -4614,430 +4689,430 @@
         <v>259</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>364</v>
+        <v>121</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E81" t="s">
-        <v>365</v>
+        <v>97</v>
       </c>
       <c r="F81" t="s">
-        <v>365</v>
+        <v>97</v>
       </c>
       <c r="G81" t="s">
-        <v>365</v>
+        <v>97</v>
       </c>
       <c r="H81" t="s">
-        <v>366</v>
+        <v>97</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J81">
-        <v>5</v>
-      </c>
-      <c r="K81">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="J81" t="s">
+        <v>97</v>
+      </c>
+      <c r="K81" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="F82" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="G82" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="H82" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J82" t="s">
-        <v>97</v>
-      </c>
-      <c r="K82" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E83" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="G83" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="H83" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E84" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="F84" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="G84" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="H84" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J84" t="s">
-        <v>97</v>
-      </c>
-      <c r="K84" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+      <c r="K84">
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E85" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F85" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="H85" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>124</v>
+        <v>364</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E86" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="F86" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="G86" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="H86" t="s">
-        <v>97</v>
+        <v>366</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J86" t="s">
-        <v>97</v>
-      </c>
-      <c r="K86" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J86">
+        <v>5</v>
+      </c>
+      <c r="K86">
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>266</v>
+        <v>122</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E87" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="F87" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="G87" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="H87" t="s">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J87">
-        <v>1</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J87" t="s">
+        <v>97</v>
+      </c>
+      <c r="K87" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="F88" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="G88" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="H88" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J88" t="s">
-        <v>97</v>
-      </c>
-      <c r="K88" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F89" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="G89" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="H89" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J89">
-        <v>1</v>
-      </c>
-      <c r="K89">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J89" t="s">
+        <v>97</v>
+      </c>
+      <c r="K89" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="F90" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="G90" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="H90" t="s">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E91" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G91" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H91" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J91">
-        <v>3</v>
-      </c>
-      <c r="K91">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J91" t="s">
+        <v>97</v>
+      </c>
+      <c r="K91" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E92" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="F92" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="G92" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="H92" t="s">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K92">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s">
         <v>97</v>
@@ -5063,63 +5138,63 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="F94" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="G94" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="H94" t="s">
-        <v>292</v>
+        <v>187</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94">
         <v>1</v>
       </c>
-      <c r="K94" s="2">
+      <c r="K94">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>279</v>
+        <v>190</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E95" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="F95" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="G95" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="H95" t="s">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>70</v>
@@ -5133,28 +5208,28 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="F96" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="G96" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="H96" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>70</v>
@@ -5168,28 +5243,28 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="F97" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="G97" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="H97" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>70</v>
@@ -5209,31 +5284,31 @@
         <v>209</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>282</v>
+        <v>126</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E98" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="F98" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="G98" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="H98" t="s">
-        <v>296</v>
+        <v>97</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J98">
-        <v>5</v>
-      </c>
-      <c r="K98">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="J98" t="s">
+        <v>97</v>
+      </c>
+      <c r="K98" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -5244,31 +5319,31 @@
         <v>209</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E99" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F99" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G99" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H99" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J99">
-        <v>6</v>
-      </c>
-      <c r="K99">
-        <v>6</v>
+      <c r="J99" s="2">
+        <v>1</v>
+      </c>
+      <c r="K99" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
@@ -5279,31 +5354,31 @@
         <v>209</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E100" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F100" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="G100" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H100" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J100">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K100">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
@@ -5314,31 +5389,31 @@
         <v>209</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F101" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="G101" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H101" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K101">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
@@ -5349,31 +5424,31 @@
         <v>209</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E102" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="F102" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="G102" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="H102" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K102">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
@@ -5384,31 +5459,31 @@
         <v>209</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E103" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F103" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G103" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H103" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K103">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
@@ -5419,31 +5494,31 @@
         <v>209</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E104" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F104" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G104" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H104" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K104">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
@@ -5454,31 +5529,31 @@
         <v>209</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F105" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G105" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H105" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J105">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K105">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
@@ -5489,31 +5564,31 @@
         <v>209</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H106" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J106">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K106">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
@@ -5524,209 +5599,209 @@
         <v>209</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="F107" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="G107" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="H107" t="s">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J107">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K107">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>130</v>
+        <v>287</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E108" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="F108" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="G108" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="H108" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J108" t="s">
-        <v>97</v>
-      </c>
-      <c r="K108" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J108">
+        <v>10</v>
+      </c>
+      <c r="K108">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E109" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="F109" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="G109" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="H109" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J109" s="2">
-        <v>1</v>
-      </c>
-      <c r="K109" s="2">
-        <v>1</v>
+      <c r="J109">
+        <v>11</v>
+      </c>
+      <c r="K109">
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E110" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="F110" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="G110" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="H110" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J110">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E111" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="F111" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="G111" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="H111" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J111">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="F112" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="G112" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="H112" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J112">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K112">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>113</v>
       </c>
@@ -5734,34 +5809,34 @@
         <v>210</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>328</v>
+        <v>130</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E113" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="F113" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="G113" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="H113" t="s">
-        <v>342</v>
+        <v>97</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J113">
-        <v>5</v>
-      </c>
-      <c r="K113">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="J113" t="s">
+        <v>97</v>
+      </c>
+      <c r="K113" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>113</v>
       </c>
@@ -5769,34 +5844,34 @@
         <v>210</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>329</v>
+        <v>254</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F114" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G114" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H114" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J114">
-        <v>6</v>
-      </c>
-      <c r="K114">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J114" s="2">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>113</v>
       </c>
@@ -5804,34 +5879,34 @@
         <v>210</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E115" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F115" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G115" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="H115" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K115">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>113</v>
       </c>
@@ -5839,34 +5914,34 @@
         <v>210</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E116" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F116" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G116" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H116" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K116">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>113</v>
       </c>
@@ -5874,34 +5949,34 @@
         <v>210</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E117" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F117" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="G117" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H117" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K117">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>113</v>
       </c>
@@ -5909,34 +5984,34 @@
         <v>210</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E118" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="F118" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="G118" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="H118" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K118">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>113</v>
       </c>
@@ -5944,34 +6019,34 @@
         <v>210</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E119" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F119" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G119" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H119" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K119">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>113</v>
       </c>
@@ -5979,34 +6054,34 @@
         <v>210</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E120" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F120" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G120" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H120" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J120">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K120">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>113</v>
       </c>
@@ -6014,34 +6089,34 @@
         <v>210</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F121" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G121" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H121" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J121">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K121">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>113</v>
       </c>
@@ -6049,335 +6124,317 @@
         <v>210</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E122" t="s">
+        <v>359</v>
+      </c>
+      <c r="F122" t="s">
+        <v>359</v>
+      </c>
+      <c r="G122" t="s">
+        <v>359</v>
+      </c>
+      <c r="H122" t="s">
+        <v>346</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J122">
+        <v>9</v>
+      </c>
+      <c r="K122">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A123" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E123" t="s">
+        <v>257</v>
+      </c>
+      <c r="F123" t="s">
+        <v>257</v>
+      </c>
+      <c r="G123" t="s">
+        <v>257</v>
+      </c>
+      <c r="H123" t="s">
+        <v>258</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J123">
+        <v>10</v>
+      </c>
+      <c r="K123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A124" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E124" t="s">
+        <v>360</v>
+      </c>
+      <c r="F124" t="s">
+        <v>360</v>
+      </c>
+      <c r="G124" t="s">
+        <v>360</v>
+      </c>
+      <c r="H124" t="s">
+        <v>347</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J124">
+        <v>11</v>
+      </c>
+      <c r="K124">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A125" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E125" t="s">
+        <v>361</v>
+      </c>
+      <c r="F125" t="s">
+        <v>361</v>
+      </c>
+      <c r="G125" t="s">
+        <v>361</v>
+      </c>
+      <c r="H125" t="s">
+        <v>348</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J125">
+        <v>12</v>
+      </c>
+      <c r="K125">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A126" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E126" t="s">
+        <v>362</v>
+      </c>
+      <c r="F126" t="s">
+        <v>362</v>
+      </c>
+      <c r="G126" t="s">
+        <v>362</v>
+      </c>
+      <c r="H126" t="s">
+        <v>349</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J126">
+        <v>13</v>
+      </c>
+      <c r="K126">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A127" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E127" t="s">
         <v>363</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F127" t="s">
         <v>363</v>
       </c>
-      <c r="G122" t="s">
+      <c r="G127" t="s">
         <v>363</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H127" t="s">
         <v>350</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J122">
+      <c r="I127" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J127">
         <v>14</v>
       </c>
-      <c r="K122">
+      <c r="K127">
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A123" s="2" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D128" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E123" t="s">
-        <v>97</v>
-      </c>
-      <c r="F123" t="s">
-        <v>97</v>
-      </c>
-      <c r="G123" t="s">
-        <v>97</v>
-      </c>
-      <c r="H123" t="s">
-        <v>97</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J123" t="s">
-        <v>97</v>
-      </c>
-      <c r="K123" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A124" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E124" t="s">
-        <v>177</v>
-      </c>
-      <c r="F124" t="s">
-        <v>177</v>
-      </c>
-      <c r="G124" t="s">
-        <v>177</v>
-      </c>
-      <c r="H124" t="s">
-        <v>178</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J124" s="2">
-        <v>1</v>
-      </c>
-      <c r="K124" s="2">
-        <v>1</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" s="2"/>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" s="2"/>
-      <c r="Q124" s="2"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A125" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E125" t="s">
-        <v>175</v>
-      </c>
-      <c r="F125" t="s">
-        <v>175</v>
-      </c>
-      <c r="G125" t="s">
-        <v>175</v>
-      </c>
-      <c r="H125" t="s">
-        <v>176</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J125" s="2">
-        <v>2</v>
-      </c>
-      <c r="K125" s="2">
-        <v>2</v>
-      </c>
-      <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" s="2"/>
-      <c r="Q125" s="2"/>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A126" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E126" t="s">
-        <v>222</v>
-      </c>
-      <c r="F126" t="s">
-        <v>222</v>
-      </c>
-      <c r="G126" t="s">
-        <v>222</v>
-      </c>
-      <c r="H126" t="s">
-        <v>221</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J126" s="2">
-        <v>3</v>
-      </c>
-      <c r="K126" s="2">
-        <v>3</v>
-      </c>
-      <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" s="2"/>
-      <c r="Q126" s="2"/>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A127" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E127" t="s">
-        <v>97</v>
-      </c>
-      <c r="F127" t="s">
-        <v>97</v>
-      </c>
-      <c r="G127" t="s">
-        <v>97</v>
-      </c>
-      <c r="H127" t="s">
-        <v>97</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J127" t="s">
-        <v>97</v>
-      </c>
-      <c r="K127" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="E128" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="F128" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="G128" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="H128" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J128" s="2">
-        <v>1</v>
-      </c>
-      <c r="K128" s="2">
-        <v>1</v>
-      </c>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" s="2"/>
-      <c r="Q128" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K128" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E129" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F129" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G129" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H129" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J129" t="s">
-        <v>97</v>
-      </c>
-      <c r="K129" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J129" s="2">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
+      </c>
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2"/>
+      <c r="Q129" s="2"/>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E130" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="F130" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="G130" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="H130" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -6386,6 +6443,199 @@
       <c r="P130" s="2"/>
       <c r="Q130" s="2"/>
     </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A131" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E131" t="s">
+        <v>222</v>
+      </c>
+      <c r="F131" t="s">
+        <v>222</v>
+      </c>
+      <c r="G131" t="s">
+        <v>222</v>
+      </c>
+      <c r="H131" t="s">
+        <v>221</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J131" s="2">
+        <v>3</v>
+      </c>
+      <c r="K131" s="2">
+        <v>3</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" s="2"/>
+      <c r="Q131" s="2"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E132" t="s">
+        <v>97</v>
+      </c>
+      <c r="F132" t="s">
+        <v>97</v>
+      </c>
+      <c r="G132" t="s">
+        <v>97</v>
+      </c>
+      <c r="H132" t="s">
+        <v>97</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J132" t="s">
+        <v>97</v>
+      </c>
+      <c r="K132" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A133" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E133" t="s">
+        <v>216</v>
+      </c>
+      <c r="F133" t="s">
+        <v>216</v>
+      </c>
+      <c r="G133" t="s">
+        <v>216</v>
+      </c>
+      <c r="H133" t="s">
+        <v>217</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J133" s="2">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="2"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A134" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E134" t="s">
+        <v>97</v>
+      </c>
+      <c r="F134" t="s">
+        <v>97</v>
+      </c>
+      <c r="G134" t="s">
+        <v>97</v>
+      </c>
+      <c r="H134" t="s">
+        <v>97</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J134" t="s">
+        <v>97</v>
+      </c>
+      <c r="K134" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A135" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E135" t="s">
+        <v>67</v>
+      </c>
+      <c r="F135" t="s">
+        <v>67</v>
+      </c>
+      <c r="G135" t="s">
+        <v>67</v>
+      </c>
+      <c r="H135" t="s">
+        <v>68</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J135" s="2">
+        <v>1</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L135" s="2"/>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" s="2"/>
+      <c r="Q135" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD45396-E3E7-2541-9DC8-82410D815AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75D7D36-F5BF-F945-B24D-504D8F9AA308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="445">
   <si>
     <t>category</t>
   </si>
@@ -1288,10 +1288,73 @@
     <t>Argalaa_stotram</t>
   </si>
   <si>
-    <t>aaryaa_durga_ashtakam.pdf</t>
-  </si>
-  <si>
-    <t>aaryaa_durga_ashtakam</t>
+    <t>Aaryaa_durga_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Aaryaa_durga_ashtakam</t>
+  </si>
+  <si>
+    <t>Keelaka_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Kunchuka_siddha_kunchika_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Mahishaasura_ashtotthara_shata_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Naaraayani_stuti_or_Naaraayani_suktham.pdf</t>
+  </si>
+  <si>
+    <t>Navadurgaa_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Chandikaa_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Chandikaa_pratah_smaranam.pdf</t>
+  </si>
+  <si>
+    <t>I021</t>
+  </si>
+  <si>
+    <t>I022</t>
+  </si>
+  <si>
+    <t>I023</t>
+  </si>
+  <si>
+    <t>I024</t>
+  </si>
+  <si>
+    <t>I025</t>
+  </si>
+  <si>
+    <t>I026</t>
+  </si>
+  <si>
+    <t>I027</t>
+  </si>
+  <si>
+    <t>Keelaka_stotram</t>
+  </si>
+  <si>
+    <t>Kunchuka_siddha_kunchika_stotram</t>
+  </si>
+  <si>
+    <t>Mahishaasura_ashtotthara_shata_naamaavali</t>
+  </si>
+  <si>
+    <t>Naaraayani_stuti_or_Naaraayani_suktham</t>
+  </si>
+  <si>
+    <t>Navadurgaa_stotram</t>
+  </si>
+  <si>
+    <t>Chandikaa_ashtakam</t>
+  </si>
+  <si>
+    <t>Chandikaa_pratah_smaranam</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q135"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -4514,780 +4577,822 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>120</v>
+        <v>431</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E76" t="s">
+        <v>438</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>438</v>
       </c>
       <c r="G76" t="s">
-        <v>97</v>
+        <v>438</v>
+      </c>
+      <c r="H76" t="s">
+        <v>424</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J76" t="s">
-        <v>97</v>
-      </c>
-      <c r="K76" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J76" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" s="2">
+        <v>21</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>223</v>
+        <v>432</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E77" t="s">
-        <v>224</v>
+        <v>439</v>
       </c>
       <c r="F77" t="s">
-        <v>224</v>
+        <v>439</v>
       </c>
       <c r="G77" t="s">
-        <v>224</v>
+        <v>439</v>
       </c>
       <c r="H77" t="s">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77">
-        <v>1</v>
-      </c>
+      <c r="J77" s="2">
+        <v>22</v>
+      </c>
+      <c r="K77" s="2">
+        <v>22</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>226</v>
+        <v>433</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E78" t="s">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="F78" t="s">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="G78" t="s">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="H78" t="s">
-        <v>230</v>
+        <v>426</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J78">
-        <v>2</v>
-      </c>
-      <c r="K78">
-        <v>2</v>
-      </c>
+      <c r="J78" s="2">
+        <v>23</v>
+      </c>
+      <c r="K78" s="2">
+        <v>23</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>227</v>
+        <v>434</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>231</v>
+        <v>441</v>
       </c>
       <c r="F79" t="s">
-        <v>231</v>
+        <v>441</v>
       </c>
       <c r="G79" t="s">
-        <v>231</v>
+        <v>441</v>
       </c>
       <c r="H79" t="s">
-        <v>232</v>
+        <v>427</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J79">
-        <v>3</v>
-      </c>
-      <c r="K79">
-        <v>3</v>
-      </c>
+      <c r="J79" s="2">
+        <v>24</v>
+      </c>
+      <c r="K79" s="2">
+        <v>24</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E80" t="s">
+        <v>442</v>
+      </c>
+      <c r="F80" t="s">
+        <v>442</v>
+      </c>
+      <c r="G80" t="s">
+        <v>442</v>
+      </c>
+      <c r="H80" t="s">
+        <v>428</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J80" s="2">
+        <v>25</v>
+      </c>
+      <c r="K80" s="2">
+        <v>25</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E81" t="s">
+        <v>443</v>
+      </c>
+      <c r="F81" t="s">
+        <v>443</v>
+      </c>
+      <c r="G81" t="s">
+        <v>443</v>
+      </c>
+      <c r="H81" t="s">
+        <v>429</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J81" s="2">
+        <v>26</v>
+      </c>
+      <c r="K81" s="2">
+        <v>26</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E82" t="s">
+        <v>444</v>
+      </c>
+      <c r="F82" t="s">
+        <v>444</v>
+      </c>
+      <c r="G82" t="s">
+        <v>444</v>
+      </c>
+      <c r="H82" t="s">
+        <v>430</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J82" s="2">
+        <v>27</v>
+      </c>
+      <c r="K82" s="2">
+        <v>27</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C83" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" t="s">
+        <v>97</v>
+      </c>
+      <c r="G83" t="s">
+        <v>97</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J83" t="s">
+        <v>97</v>
+      </c>
+      <c r="K83" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E84" t="s">
+        <v>224</v>
+      </c>
+      <c r="F84" t="s">
+        <v>224</v>
+      </c>
+      <c r="G84" t="s">
+        <v>224</v>
+      </c>
+      <c r="H84" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E85" t="s">
+        <v>229</v>
+      </c>
+      <c r="F85" t="s">
+        <v>229</v>
+      </c>
+      <c r="G85" t="s">
+        <v>229</v>
+      </c>
+      <c r="H85" t="s">
+        <v>230</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" t="s">
+        <v>231</v>
+      </c>
+      <c r="F86" t="s">
+        <v>231</v>
+      </c>
+      <c r="G86" t="s">
+        <v>231</v>
+      </c>
+      <c r="H86" t="s">
+        <v>232</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E87" t="s">
         <v>233</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F87" t="s">
         <v>233</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G87" t="s">
         <v>233</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H87" t="s">
         <v>234</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J80">
+      <c r="I87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J87">
         <v>4</v>
       </c>
-      <c r="K80">
+      <c r="K87">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A81" s="2" t="s">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B88" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E81" t="s">
-        <v>97</v>
-      </c>
-      <c r="F81" t="s">
-        <v>97</v>
-      </c>
-      <c r="G81" t="s">
-        <v>97</v>
-      </c>
-      <c r="H81" t="s">
-        <v>97</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J81" t="s">
-        <v>97</v>
-      </c>
-      <c r="K81" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="2" t="s">
+      <c r="E88" t="s">
+        <v>97</v>
+      </c>
+      <c r="F88" t="s">
+        <v>97</v>
+      </c>
+      <c r="G88" t="s">
+        <v>97</v>
+      </c>
+      <c r="H88" t="s">
+        <v>97</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J88" t="s">
+        <v>97</v>
+      </c>
+      <c r="K88" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E89" t="s">
         <v>245</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F89" t="s">
         <v>245</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G89" t="s">
         <v>245</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H89" t="s">
         <v>246</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J82">
+      <c r="I89" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J89">
         <v>1</v>
       </c>
-      <c r="K82">
+      <c r="K89">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A83" s="2" t="s">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E90" t="s">
         <v>247</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F90" t="s">
         <v>247</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G90" t="s">
         <v>247</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H90" t="s">
         <v>248</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J83">
+      <c r="I90" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J90">
         <v>2</v>
       </c>
-      <c r="K83">
+      <c r="K90">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A84" s="2" t="s">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B91" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E91" t="s">
         <v>249</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F91" t="s">
         <v>249</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G91" t="s">
         <v>249</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H91" t="s">
         <v>250</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J84">
+      <c r="I91" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J91">
         <v>3</v>
       </c>
-      <c r="K84">
+      <c r="K91">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A85" s="2" t="s">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B92" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C92" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D92" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E92" t="s">
         <v>251</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F92" t="s">
         <v>251</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G92" t="s">
         <v>251</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H92" t="s">
         <v>252</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J85">
+      <c r="I92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J92">
         <v>4</v>
       </c>
-      <c r="K85">
+      <c r="K92">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A86" s="2" t="s">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E93" t="s">
         <v>365</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F93" t="s">
         <v>365</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G93" t="s">
         <v>365</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H93" t="s">
         <v>366</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J86">
+      <c r="I93" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J93">
         <v>5</v>
       </c>
-      <c r="K86">
+      <c r="K93">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A87" s="2" t="s">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E87" t="s">
-        <v>97</v>
-      </c>
-      <c r="F87" t="s">
-        <v>97</v>
-      </c>
-      <c r="G87" t="s">
-        <v>97</v>
-      </c>
-      <c r="H87" t="s">
-        <v>97</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J87" t="s">
-        <v>97</v>
-      </c>
-      <c r="K87" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="2" t="s">
+      <c r="E94" t="s">
+        <v>97</v>
+      </c>
+      <c r="F94" t="s">
+        <v>97</v>
+      </c>
+      <c r="G94" t="s">
+        <v>97</v>
+      </c>
+      <c r="H94" t="s">
+        <v>97</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J94" t="s">
+        <v>97</v>
+      </c>
+      <c r="K94" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D95" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E95" t="s">
         <v>267</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F95" t="s">
         <v>267</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G95" t="s">
         <v>267</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H95" t="s">
         <v>268</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J88">
+      <c r="I95" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J95">
         <v>1</v>
       </c>
-      <c r="K88">
+      <c r="K95">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="2" t="s">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B96" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D96" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E89" t="s">
-        <v>97</v>
-      </c>
-      <c r="F89" t="s">
-        <v>97</v>
-      </c>
-      <c r="G89" t="s">
-        <v>97</v>
-      </c>
-      <c r="H89" t="s">
-        <v>97</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J89" t="s">
-        <v>97</v>
-      </c>
-      <c r="K89" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E90" t="s">
-        <v>269</v>
-      </c>
-      <c r="F90" t="s">
-        <v>269</v>
-      </c>
-      <c r="G90" t="s">
-        <v>269</v>
-      </c>
-      <c r="H90" t="s">
-        <v>270</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J90">
-        <v>1</v>
-      </c>
-      <c r="K90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A91" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E91" t="s">
-        <v>97</v>
-      </c>
-      <c r="F91" t="s">
-        <v>97</v>
-      </c>
-      <c r="G91" t="s">
-        <v>97</v>
-      </c>
-      <c r="H91" t="s">
-        <v>97</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J91" t="s">
-        <v>97</v>
-      </c>
-      <c r="K91" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E92" t="s">
-        <v>271</v>
-      </c>
-      <c r="F92" t="s">
-        <v>271</v>
-      </c>
-      <c r="G92" t="s">
-        <v>271</v>
-      </c>
-      <c r="H92" t="s">
-        <v>272</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J92">
-        <v>1</v>
-      </c>
-      <c r="K92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E93" t="s">
-        <v>97</v>
-      </c>
-      <c r="F93" t="s">
-        <v>97</v>
-      </c>
-      <c r="G93" t="s">
-        <v>97</v>
-      </c>
-      <c r="H93" t="s">
-        <v>97</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J93" t="s">
-        <v>97</v>
-      </c>
-      <c r="K93" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E94" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" t="s">
-        <v>186</v>
-      </c>
-      <c r="G94" t="s">
-        <v>186</v>
-      </c>
-      <c r="H94" t="s">
-        <v>187</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J94">
-        <v>1</v>
-      </c>
-      <c r="K94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A95" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E95" t="s">
-        <v>188</v>
-      </c>
-      <c r="F95" t="s">
-        <v>188</v>
-      </c>
-      <c r="G95" t="s">
-        <v>188</v>
-      </c>
-      <c r="H95" t="s">
-        <v>189</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J95">
-        <v>2</v>
-      </c>
-      <c r="K95">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="E96" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F96" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G96" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H96" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J96">
-        <v>3</v>
-      </c>
-      <c r="K96">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J96" t="s">
+        <v>97</v>
+      </c>
+      <c r="K96" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E97" t="s">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="F97" t="s">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="G97" t="s">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="H97" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J97">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K97">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
         <v>97</v>
@@ -5313,212 +5418,212 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E99" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="F99" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="G99" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="H99" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99">
         <v>1</v>
       </c>
-      <c r="K99" s="2">
+      <c r="K99">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>279</v>
+        <v>125</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E100" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="F100" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G100" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="H100" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J100">
-        <v>2</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J100" t="s">
+        <v>97</v>
+      </c>
+      <c r="K100" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>280</v>
+        <v>185</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E101" t="s">
-        <v>306</v>
+        <v>186</v>
       </c>
       <c r="F101" t="s">
-        <v>306</v>
+        <v>186</v>
       </c>
       <c r="G101" t="s">
-        <v>306</v>
+        <v>186</v>
       </c>
       <c r="H101" t="s">
-        <v>294</v>
+        <v>187</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K101">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>281</v>
+        <v>190</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E102" t="s">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="F102" t="s">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="G102" t="s">
-        <v>307</v>
+        <v>188</v>
       </c>
       <c r="H102" t="s">
-        <v>295</v>
+        <v>189</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K102">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E103" t="s">
-        <v>308</v>
+        <v>193</v>
       </c>
       <c r="F103" t="s">
-        <v>308</v>
+        <v>193</v>
       </c>
       <c r="G103" t="s">
-        <v>308</v>
+        <v>193</v>
       </c>
       <c r="H103" t="s">
-        <v>296</v>
+        <v>194</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K103">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E104" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="F104" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="G104" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="H104" t="s">
-        <v>297</v>
+        <v>196</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K104">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
@@ -5529,31 +5634,31 @@
         <v>209</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>284</v>
+        <v>126</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>310</v>
+        <v>97</v>
       </c>
       <c r="F105" t="s">
-        <v>310</v>
+        <v>97</v>
       </c>
       <c r="G105" t="s">
-        <v>310</v>
+        <v>97</v>
       </c>
       <c r="H105" t="s">
-        <v>298</v>
+        <v>97</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J105">
-        <v>7</v>
-      </c>
-      <c r="K105">
-        <v>7</v>
+        <v>97</v>
+      </c>
+      <c r="J105" t="s">
+        <v>97</v>
+      </c>
+      <c r="K105" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
@@ -5564,31 +5669,31 @@
         <v>209</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E106" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="F106" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G106" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H106" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J106">
-        <v>8</v>
-      </c>
-      <c r="K106">
-        <v>8</v>
+      <c r="J106" s="2">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
@@ -5599,31 +5704,31 @@
         <v>209</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E107" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="F107" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="G107" t="s">
-        <v>255</v>
+        <v>305</v>
       </c>
       <c r="H107" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J107">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K107">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
@@ -5634,31 +5739,31 @@
         <v>209</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E108" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F108" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="G108" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H108" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J108">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K108">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -5669,31 +5774,31 @@
         <v>209</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E109" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="F109" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G109" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="H109" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J109">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K109">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
@@ -5704,31 +5809,31 @@
         <v>209</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E110" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F110" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G110" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="H110" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J110">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K110">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -5739,31 +5844,31 @@
         <v>209</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E111" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F111" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G111" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H111" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J111">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K111">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5774,276 +5879,276 @@
         <v>209</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H112" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J112">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K112">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="F113" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="G113" t="s">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="H113" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J113" t="s">
-        <v>97</v>
-      </c>
-      <c r="K113" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J113">
+        <v>8</v>
+      </c>
+      <c r="K113">
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>351</v>
+        <v>255</v>
       </c>
       <c r="F114" t="s">
-        <v>351</v>
+        <v>255</v>
       </c>
       <c r="G114" t="s">
-        <v>351</v>
+        <v>255</v>
       </c>
       <c r="H114" t="s">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J114" s="2">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
+      <c r="J114">
+        <v>9</v>
+      </c>
+      <c r="K114">
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E115" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="F115" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="G115" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="H115" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E116" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="F116" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="G116" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="H116" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K116">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="F117" t="s">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="G117" t="s">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="H117" t="s">
-        <v>341</v>
+        <v>302</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K117">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="F118" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="G118" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="H118" t="s">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K118">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>329</v>
+        <v>291</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E119" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="F119" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="G119" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="H119" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K119">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6054,31 +6159,31 @@
         <v>210</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E120" t="s">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="G120" t="s">
-        <v>357</v>
+        <v>97</v>
       </c>
       <c r="H120" t="s">
-        <v>344</v>
+        <v>97</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J120">
-        <v>7</v>
-      </c>
-      <c r="K120">
-        <v>7</v>
+        <v>97</v>
+      </c>
+      <c r="J120" t="s">
+        <v>97</v>
+      </c>
+      <c r="K120" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6089,31 +6194,31 @@
         <v>210</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="F121" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G121" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H121" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J121">
-        <v>8</v>
-      </c>
-      <c r="K121">
-        <v>8</v>
+      <c r="J121" s="2">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6124,31 +6229,31 @@
         <v>210</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E122" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="F122" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G122" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="H122" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K122">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6159,31 +6264,31 @@
         <v>210</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E123" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="F123" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="G123" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="H123" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K123">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6194,31 +6299,31 @@
         <v>210</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E124" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="F124" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="G124" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H124" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K124">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6229,31 +6334,31 @@
         <v>210</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E125" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="F125" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G125" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="H125" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J125">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K125">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6264,31 +6369,31 @@
         <v>210</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E126" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F126" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G126" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="H126" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J126">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K126">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6299,342 +6404,587 @@
         <v>210</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E127" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="F127" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G127" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="H127" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K127">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>127</v>
+        <v>331</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E128" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="F128" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="G128" t="s">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="H128" t="s">
-        <v>97</v>
+        <v>345</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J128" t="s">
-        <v>97</v>
-      </c>
-      <c r="K128" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J128">
+        <v>8</v>
+      </c>
+      <c r="K128">
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>218</v>
+        <v>332</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E129" t="s">
-        <v>177</v>
+        <v>359</v>
       </c>
       <c r="F129" t="s">
-        <v>177</v>
+        <v>359</v>
       </c>
       <c r="G129" t="s">
-        <v>177</v>
+        <v>359</v>
       </c>
       <c r="H129" t="s">
-        <v>178</v>
+        <v>346</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J129" s="2">
-        <v>1</v>
-      </c>
-      <c r="K129" s="2">
-        <v>1</v>
-      </c>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" s="2"/>
-      <c r="Q129" s="2"/>
+      <c r="J129">
+        <v>9</v>
+      </c>
+      <c r="K129">
+        <v>9</v>
+      </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E130" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="F130" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="G130" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="H130" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J130" s="2">
-        <v>2</v>
-      </c>
-      <c r="K130" s="2">
-        <v>2</v>
-      </c>
-      <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" s="2"/>
-      <c r="Q130" s="2"/>
+      <c r="J130">
+        <v>10</v>
+      </c>
+      <c r="K130">
+        <v>10</v>
+      </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E131" t="s">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="F131" t="s">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="G131" t="s">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="H131" t="s">
-        <v>221</v>
+        <v>347</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J131" s="2">
-        <v>3</v>
-      </c>
-      <c r="K131" s="2">
-        <v>3</v>
-      </c>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2"/>
-      <c r="Q131" s="2"/>
+      <c r="J131">
+        <v>11</v>
+      </c>
+      <c r="K131">
+        <v>11</v>
+      </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>128</v>
+        <v>335</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="F132" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="G132" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="H132" t="s">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J132" t="s">
-        <v>97</v>
-      </c>
-      <c r="K132" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J132">
+        <v>12</v>
+      </c>
+      <c r="K132">
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>215</v>
+        <v>336</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E133" t="s">
-        <v>216</v>
+        <v>362</v>
       </c>
       <c r="F133" t="s">
-        <v>216</v>
+        <v>362</v>
       </c>
       <c r="G133" t="s">
-        <v>216</v>
+        <v>362</v>
       </c>
       <c r="H133" t="s">
-        <v>217</v>
+        <v>349</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J133" s="2">
-        <v>1</v>
-      </c>
-      <c r="K133" s="2">
-        <v>1</v>
-      </c>
-      <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" s="2"/>
-      <c r="Q133" s="2"/>
+      <c r="J133">
+        <v>13</v>
+      </c>
+      <c r="K133">
+        <v>13</v>
+      </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>129</v>
+        <v>337</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E134" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="F134" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="G134" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="H134" t="s">
-        <v>97</v>
+        <v>350</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J134" t="s">
-        <v>97</v>
-      </c>
-      <c r="K134" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J134">
+        <v>14</v>
+      </c>
+      <c r="K134">
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E135" t="s">
+        <v>97</v>
+      </c>
+      <c r="F135" t="s">
+        <v>97</v>
+      </c>
+      <c r="G135" t="s">
+        <v>97</v>
+      </c>
+      <c r="H135" t="s">
+        <v>97</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J135" t="s">
+        <v>97</v>
+      </c>
+      <c r="K135" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A136" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E136" t="s">
+        <v>177</v>
+      </c>
+      <c r="F136" t="s">
+        <v>177</v>
+      </c>
+      <c r="G136" t="s">
+        <v>177</v>
+      </c>
+      <c r="H136" t="s">
+        <v>178</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J136" s="2">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2">
+        <v>1</v>
+      </c>
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" s="2"/>
+      <c r="Q136" s="2"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" t="s">
+        <v>175</v>
+      </c>
+      <c r="F137" t="s">
+        <v>175</v>
+      </c>
+      <c r="G137" t="s">
+        <v>175</v>
+      </c>
+      <c r="H137" t="s">
+        <v>176</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J137" s="2">
+        <v>2</v>
+      </c>
+      <c r="K137" s="2">
+        <v>2</v>
+      </c>
+      <c r="L137" s="2"/>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="2"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A138" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E138" t="s">
+        <v>222</v>
+      </c>
+      <c r="F138" t="s">
+        <v>222</v>
+      </c>
+      <c r="G138" t="s">
+        <v>222</v>
+      </c>
+      <c r="H138" t="s">
+        <v>221</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J138" s="2">
+        <v>3</v>
+      </c>
+      <c r="K138" s="2">
+        <v>3</v>
+      </c>
+      <c r="L138" s="2"/>
+      <c r="M138" s="2"/>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" s="2"/>
+      <c r="Q138" s="2"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A139" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E139" t="s">
+        <v>97</v>
+      </c>
+      <c r="F139" t="s">
+        <v>97</v>
+      </c>
+      <c r="G139" t="s">
+        <v>97</v>
+      </c>
+      <c r="H139" t="s">
+        <v>97</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J139" t="s">
+        <v>97</v>
+      </c>
+      <c r="K139" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A140" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E140" t="s">
+        <v>216</v>
+      </c>
+      <c r="F140" t="s">
+        <v>216</v>
+      </c>
+      <c r="G140" t="s">
+        <v>216</v>
+      </c>
+      <c r="H140" t="s">
+        <v>217</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J140" s="2">
+        <v>1</v>
+      </c>
+      <c r="K140" s="2">
+        <v>1</v>
+      </c>
+      <c r="L140" s="2"/>
+      <c r="M140" s="2"/>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" s="2"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A141" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B141" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C135" s="2" t="s">
+      <c r="C141" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E141" t="s">
+        <v>97</v>
+      </c>
+      <c r="F141" t="s">
+        <v>97</v>
+      </c>
+      <c r="G141" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" t="s">
+        <v>97</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J141" t="s">
+        <v>97</v>
+      </c>
+      <c r="K141" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A142" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D142" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E142" t="s">
         <v>67</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F142" t="s">
         <v>67</v>
       </c>
-      <c r="G135" t="s">
+      <c r="G142" t="s">
         <v>67</v>
       </c>
-      <c r="H135" t="s">
+      <c r="H142" t="s">
         <v>68</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J135" s="2">
+      <c r="I142" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J142" s="2">
         <v>1</v>
       </c>
-      <c r="K135" s="2">
+      <c r="K142" s="2">
         <v>1</v>
       </c>
-      <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" s="2"/>
-      <c r="Q135" s="2"/>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75D7D36-F5BF-F945-B24D-504D8F9AA308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846C20A0-0E8D-0F44-8E51-EDBBAD5FAAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1297,9 +1297,6 @@
     <t>Keelaka_stotram.pdf</t>
   </si>
   <si>
-    <t>Kunchuka_siddha_kunchika_stotram.pdf</t>
-  </si>
-  <si>
     <t>Mahishaasura_ashtotthara_shata_naamaavali.pdf</t>
   </si>
   <si>
@@ -1339,9 +1336,6 @@
     <t>Keelaka_stotram</t>
   </si>
   <si>
-    <t>Kunchuka_siddha_kunchika_stotram</t>
-  </si>
-  <si>
     <t>Mahishaasura_ashtotthara_shata_naamaavali</t>
   </si>
   <si>
@@ -1355,6 +1349,12 @@
   </si>
   <si>
     <t>Chandikaa_pratah_smaranam</t>
+  </si>
+  <si>
+    <t>Kunchika_siddha_kunchika_stotram</t>
+  </si>
+  <si>
+    <t>Kunchika_siddha_kunchika_stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -4583,19 +4583,19 @@
         <v>197</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E76" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F76" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G76" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H76" t="s">
         <v>424</v>
@@ -4624,22 +4624,22 @@
         <v>197</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E77" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F77" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G77" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H77" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>70</v>
@@ -4665,22 +4665,22 @@
         <v>197</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E78" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F78" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G78" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H78" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
@@ -4706,22 +4706,22 @@
         <v>197</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F79" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G79" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H79" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>70</v>
@@ -4747,22 +4747,22 @@
         <v>197</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E80" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F80" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G80" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H80" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>70</v>
@@ -4788,22 +4788,22 @@
         <v>197</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E81" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F81" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G81" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H81" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
@@ -4829,22 +4829,22 @@
         <v>197</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E82" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F82" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G82" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H82" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>70</v>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846C20A0-0E8D-0F44-8E51-EDBBAD5FAAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9409FB20-C785-AB48-97F7-91E33A7D9B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="460">
   <si>
     <t>category</t>
   </si>
@@ -1355,6 +1355,51 @@
   </si>
   <si>
     <t>Kunchika_siddha_kunchika_stotram.pdf</t>
+  </si>
+  <si>
+    <t>N002</t>
+  </si>
+  <si>
+    <t>N003</t>
+  </si>
+  <si>
+    <t>N004</t>
+  </si>
+  <si>
+    <t>N006</t>
+  </si>
+  <si>
+    <t>N005</t>
+  </si>
+  <si>
+    <t>Maheshwaraproktha_Ujjayini_Mahaakaalamahima.pdf</t>
+  </si>
+  <si>
+    <t>Omkaareshwara_maahaatmyam.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Agastesha_lingaashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Ahoramoorthy_kavacham.pdf</t>
+  </si>
+  <si>
+    <t>Shrimad_akhilaanda_devi_jambhukeshwara_stuti_dringeri.pdf</t>
+  </si>
+  <si>
+    <t>Maheshwaraproktha_Ujjayini_Mahaakaalamahima</t>
+  </si>
+  <si>
+    <t>Omkaareshwara_maahaatmyam</t>
+  </si>
+  <si>
+    <t>Shri_Agastesha_lingaashtakam</t>
+  </si>
+  <si>
+    <t>Shri_Ahoramoorthy_kavacham</t>
+  </si>
+  <si>
+    <t>Shrimad_akhilaanda_devi_jambhukeshwara_stuti_dringeri</t>
   </si>
 </sst>
 </file>
@@ -1726,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q142"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1734,7 +1779,8 @@
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="52.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
@@ -5453,202 +5499,196 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>125</v>
+        <v>445</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E100" t="s">
-        <v>97</v>
+        <v>455</v>
       </c>
       <c r="F100" t="s">
-        <v>97</v>
+        <v>455</v>
       </c>
       <c r="G100" t="s">
-        <v>97</v>
+        <v>455</v>
       </c>
       <c r="H100" t="s">
-        <v>97</v>
+        <v>450</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J100" t="s">
-        <v>97</v>
-      </c>
-      <c r="K100" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>185</v>
+        <v>446</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E101" t="s">
-        <v>186</v>
+        <v>456</v>
       </c>
       <c r="F101" t="s">
-        <v>186</v>
+        <v>456</v>
       </c>
       <c r="G101" t="s">
-        <v>186</v>
+        <v>456</v>
       </c>
       <c r="H101" t="s">
-        <v>187</v>
+        <v>451</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>190</v>
+        <v>447</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E102" t="s">
-        <v>188</v>
+        <v>457</v>
       </c>
       <c r="F102" t="s">
-        <v>188</v>
+        <v>457</v>
       </c>
       <c r="G102" t="s">
-        <v>188</v>
+        <v>457</v>
       </c>
       <c r="H102" t="s">
-        <v>189</v>
+        <v>452</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J102">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K102">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>191</v>
+        <v>449</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E103" t="s">
-        <v>193</v>
+        <v>458</v>
       </c>
       <c r="F103" t="s">
-        <v>193</v>
+        <v>458</v>
       </c>
       <c r="G103" t="s">
-        <v>193</v>
+        <v>458</v>
       </c>
       <c r="H103" t="s">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J103">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K103">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>192</v>
+        <v>448</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E104" t="s">
-        <v>195</v>
+        <v>459</v>
       </c>
       <c r="F104" t="s">
-        <v>195</v>
+        <v>459</v>
       </c>
       <c r="G104" t="s">
-        <v>195</v>
+        <v>459</v>
       </c>
       <c r="H104" t="s">
-        <v>196</v>
+        <v>454</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J104">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K104">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E105" t="s">
         <v>97</v>
       </c>
       <c r="F105" t="s">
-        <v>97</v>
-      </c>
-      <c r="G105" t="s">
-        <v>97</v>
-      </c>
-      <c r="H105" t="s">
         <v>97</v>
       </c>
       <c r="I105" s="2" t="s">
@@ -5663,63 +5703,63 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E106" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="F106" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="G106" t="s">
-        <v>304</v>
+        <v>186</v>
       </c>
       <c r="H106" t="s">
-        <v>292</v>
+        <v>187</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106">
         <v>1</v>
       </c>
-      <c r="K106" s="2">
+      <c r="K106">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>279</v>
+        <v>190</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="F107" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="G107" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="H107" t="s">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
@@ -5733,28 +5773,28 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E108" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="F108" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="G108" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="H108" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
@@ -5768,28 +5808,28 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E109" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="F109" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="G109" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="H109" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
@@ -5809,31 +5849,31 @@
         <v>209</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>282</v>
+        <v>126</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E110" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="F110" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="G110" t="s">
-        <v>308</v>
+        <v>97</v>
       </c>
       <c r="H110" t="s">
-        <v>296</v>
+        <v>97</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J110">
-        <v>5</v>
-      </c>
-      <c r="K110">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="J110" t="s">
+        <v>97</v>
+      </c>
+      <c r="K110" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -5844,31 +5884,31 @@
         <v>209</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E111" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F111" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G111" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H111" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J111">
-        <v>6</v>
-      </c>
-      <c r="K111">
-        <v>6</v>
+      <c r="J111" s="2">
+        <v>1</v>
+      </c>
+      <c r="K111" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5879,31 +5919,31 @@
         <v>209</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F112" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="G112" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H112" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J112">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K112">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -5914,31 +5954,31 @@
         <v>209</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F113" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="G113" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H113" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J113">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K113">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -5949,31 +5989,31 @@
         <v>209</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="F114" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="G114" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="H114" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J114">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K114">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -5984,31 +6024,31 @@
         <v>209</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E115" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F115" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G115" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H115" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K115">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -6019,31 +6059,31 @@
         <v>209</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E116" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F116" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G116" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H116" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K116">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -6054,31 +6094,31 @@
         <v>209</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F117" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G117" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H117" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K117">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -6089,31 +6129,31 @@
         <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F118" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G118" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H118" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K118">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -6124,206 +6164,206 @@
         <v>209</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E119" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="F119" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="G119" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="H119" t="s">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K119">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>130</v>
+        <v>287</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="F120" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="G120" t="s">
-        <v>97</v>
+        <v>312</v>
       </c>
       <c r="H120" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J120" t="s">
-        <v>97</v>
-      </c>
-      <c r="K120" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J120">
+        <v>10</v>
+      </c>
+      <c r="K120">
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="F121" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="G121" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="H121" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J121" s="2">
-        <v>1</v>
-      </c>
-      <c r="K121" s="2">
-        <v>1</v>
+      <c r="J121">
+        <v>11</v>
+      </c>
+      <c r="K121">
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="F122" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="G122" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="H122" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K122">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="F123" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="G123" t="s">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="H123" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K123">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="F124" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="G124" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="H124" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K124">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6334,31 +6374,31 @@
         <v>210</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>328</v>
+        <v>130</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E125" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="F125" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="G125" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="H125" t="s">
-        <v>342</v>
+        <v>97</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J125">
-        <v>5</v>
-      </c>
-      <c r="K125">
-        <v>5</v>
+        <v>97</v>
+      </c>
+      <c r="J125" t="s">
+        <v>97</v>
+      </c>
+      <c r="K125" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6369,31 +6409,31 @@
         <v>210</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>329</v>
+        <v>254</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E126" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F126" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G126" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H126" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J126">
-        <v>6</v>
-      </c>
-      <c r="K126">
-        <v>6</v>
+      <c r="J126" s="2">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6404,31 +6444,31 @@
         <v>210</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E127" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F127" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G127" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="H127" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K127">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6439,31 +6479,31 @@
         <v>210</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E128" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F128" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G128" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H128" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J128">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K128">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
@@ -6474,31 +6514,31 @@
         <v>210</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E129" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F129" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="G129" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H129" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J129">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K129">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
@@ -6509,31 +6549,31 @@
         <v>210</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E130" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="F130" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="G130" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="H130" t="s">
-        <v>258</v>
+        <v>342</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K130">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
@@ -6544,31 +6584,31 @@
         <v>210</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E131" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F131" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G131" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H131" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K131">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
@@ -6579,31 +6619,31 @@
         <v>210</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F132" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G132" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H132" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J132">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K132">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
@@ -6614,31 +6654,31 @@
         <v>210</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E133" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F133" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G133" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H133" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J133">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K133">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
@@ -6649,335 +6689,317 @@
         <v>210</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E134" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F134" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G134" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H134" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K134">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>127</v>
+        <v>333</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="F135" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="G135" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="H135" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J135" t="s">
-        <v>97</v>
-      </c>
-      <c r="K135" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J135">
+        <v>10</v>
+      </c>
+      <c r="K135">
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="F136" t="s">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="G136" t="s">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="H136" t="s">
-        <v>178</v>
+        <v>347</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J136" s="2">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2">
-        <v>1</v>
-      </c>
-      <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" s="2"/>
-      <c r="Q136" s="2"/>
+      <c r="J136">
+        <v>11</v>
+      </c>
+      <c r="K136">
+        <v>11</v>
+      </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>219</v>
+        <v>335</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>175</v>
+        <v>361</v>
       </c>
       <c r="F137" t="s">
-        <v>175</v>
+        <v>361</v>
       </c>
       <c r="G137" t="s">
-        <v>175</v>
+        <v>361</v>
       </c>
       <c r="H137" t="s">
-        <v>176</v>
+        <v>348</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J137" s="2">
-        <v>2</v>
-      </c>
-      <c r="K137" s="2">
-        <v>2</v>
-      </c>
-      <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" s="2"/>
-      <c r="Q137" s="2"/>
+      <c r="J137">
+        <v>12</v>
+      </c>
+      <c r="K137">
+        <v>12</v>
+      </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>220</v>
+        <v>336</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="F138" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="G138" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="H138" t="s">
-        <v>221</v>
+        <v>349</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J138" s="2">
-        <v>3</v>
-      </c>
-      <c r="K138" s="2">
-        <v>3</v>
-      </c>
-      <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" s="2"/>
-      <c r="Q138" s="2"/>
+      <c r="J138">
+        <v>13</v>
+      </c>
+      <c r="K138">
+        <v>13</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>128</v>
+        <v>337</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="F139" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="G139" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="H139" t="s">
-        <v>97</v>
+        <v>350</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J139" t="s">
-        <v>97</v>
-      </c>
-      <c r="K139" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J139">
+        <v>14</v>
+      </c>
+      <c r="K139">
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E140" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="F140" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="G140" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="H140" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J140" s="2">
-        <v>1</v>
-      </c>
-      <c r="K140" s="2">
-        <v>1</v>
-      </c>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" s="2"/>
-      <c r="Q140" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J140" t="s">
+        <v>97</v>
+      </c>
+      <c r="K140" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E141" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F141" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G141" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H141" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J141" t="s">
-        <v>97</v>
-      </c>
-      <c r="K141" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J141" s="2">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
+        <v>1</v>
+      </c>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" s="2"/>
+      <c r="Q141" s="2"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E142" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="F142" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="G142" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="H142" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K142" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -6986,6 +7008,199 @@
       <c r="P142" s="2"/>
       <c r="Q142" s="2"/>
     </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A143" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E143" t="s">
+        <v>222</v>
+      </c>
+      <c r="F143" t="s">
+        <v>222</v>
+      </c>
+      <c r="G143" t="s">
+        <v>222</v>
+      </c>
+      <c r="H143" t="s">
+        <v>221</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J143" s="2">
+        <v>3</v>
+      </c>
+      <c r="K143" s="2">
+        <v>3</v>
+      </c>
+      <c r="L143" s="2"/>
+      <c r="M143" s="2"/>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" s="2"/>
+      <c r="Q143" s="2"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A144" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E144" t="s">
+        <v>97</v>
+      </c>
+      <c r="F144" t="s">
+        <v>97</v>
+      </c>
+      <c r="G144" t="s">
+        <v>97</v>
+      </c>
+      <c r="H144" t="s">
+        <v>97</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J144" t="s">
+        <v>97</v>
+      </c>
+      <c r="K144" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A145" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E145" t="s">
+        <v>216</v>
+      </c>
+      <c r="F145" t="s">
+        <v>216</v>
+      </c>
+      <c r="G145" t="s">
+        <v>216</v>
+      </c>
+      <c r="H145" t="s">
+        <v>217</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J145" s="2">
+        <v>1</v>
+      </c>
+      <c r="K145" s="2">
+        <v>1</v>
+      </c>
+      <c r="L145" s="2"/>
+      <c r="M145" s="2"/>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" s="2"/>
+      <c r="Q145" s="2"/>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A146" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E146" t="s">
+        <v>97</v>
+      </c>
+      <c r="F146" t="s">
+        <v>97</v>
+      </c>
+      <c r="G146" t="s">
+        <v>97</v>
+      </c>
+      <c r="H146" t="s">
+        <v>97</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J146" t="s">
+        <v>97</v>
+      </c>
+      <c r="K146" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A147" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E147" t="s">
+        <v>67</v>
+      </c>
+      <c r="F147" t="s">
+        <v>67</v>
+      </c>
+      <c r="G147" t="s">
+        <v>67</v>
+      </c>
+      <c r="H147" t="s">
+        <v>68</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J147" s="2">
+        <v>1</v>
+      </c>
+      <c r="K147" s="2">
+        <v>1</v>
+      </c>
+      <c r="L147" s="2"/>
+      <c r="M147" s="2"/>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
+      <c r="P147" s="2"/>
+      <c r="Q147" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9409FB20-C785-AB48-97F7-91E33A7D9B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90526B38-DBC8-1346-9672-72F65125A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="463">
   <si>
     <t>category</t>
   </si>
@@ -1400,6 +1400,15 @@
   </si>
   <si>
     <t>Shrimad_akhilaanda_devi_jambhukeshwara_stuti_dringeri</t>
+  </si>
+  <si>
+    <t>N007</t>
+  </si>
+  <si>
+    <t>Aghoramoorthy_sahasranaama_stotram_naamaavali_1_and_2.pdf</t>
+  </si>
+  <si>
+    <t>Aghoramoorthy_sahasranaama_stotram_naamaavali_1_and_2</t>
   </si>
 </sst>
 </file>
@@ -1771,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q147"/>
+  <dimension ref="A1:Q148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5674,31 +5683,37 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>125</v>
+        <v>460</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E105" t="s">
-        <v>97</v>
+        <v>462</v>
       </c>
       <c r="F105" t="s">
-        <v>97</v>
+        <v>462</v>
+      </c>
+      <c r="G105" t="s">
+        <v>462</v>
+      </c>
+      <c r="H105" t="s">
+        <v>461</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J105" t="s">
-        <v>97</v>
-      </c>
-      <c r="K105" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J105">
+        <v>7</v>
+      </c>
+      <c r="K105">
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
@@ -5709,31 +5724,25 @@
         <v>152</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E106" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F106" t="s">
-        <v>186</v>
-      </c>
-      <c r="G106" t="s">
-        <v>186</v>
-      </c>
-      <c r="H106" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J106">
-        <v>1</v>
-      </c>
-      <c r="K106">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J106" t="s">
+        <v>97</v>
+      </c>
+      <c r="K106" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
@@ -5744,31 +5753,31 @@
         <v>152</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H107" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
@@ -5779,31 +5788,31 @@
         <v>152</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E108" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F108" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G108" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H108" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K108">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -5814,66 +5823,66 @@
         <v>152</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E109" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F109" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G109" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H109" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K109">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E110" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="F110" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="G110" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="H110" t="s">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J110" t="s">
-        <v>97</v>
-      </c>
-      <c r="K110" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J110">
+        <v>4</v>
+      </c>
+      <c r="K110">
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -5884,31 +5893,31 @@
         <v>209</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>253</v>
+        <v>126</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E111" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="G111" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="H111" t="s">
-        <v>292</v>
+        <v>97</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J111" s="2">
-        <v>1</v>
-      </c>
-      <c r="K111" s="2">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J111" t="s">
+        <v>97</v>
+      </c>
+      <c r="K111" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5919,31 +5928,31 @@
         <v>209</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E112" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F112" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G112" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H112" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J112">
-        <v>2</v>
-      </c>
-      <c r="K112">
-        <v>2</v>
+      <c r="J112" s="2">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -5954,31 +5963,31 @@
         <v>209</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F113" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G113" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H113" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K113">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -5989,31 +5998,31 @@
         <v>209</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H114" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K114">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -6024,31 +6033,31 @@
         <v>209</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E115" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F115" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G115" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H115" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K115">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -6059,31 +6068,31 @@
         <v>209</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E116" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F116" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G116" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H116" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K116">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -6094,31 +6103,31 @@
         <v>209</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H117" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K117">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -6129,31 +6138,31 @@
         <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F118" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G118" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H118" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K118">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -6164,31 +6173,31 @@
         <v>209</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E119" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="F119" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="G119" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="H119" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K119">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6199,31 +6208,31 @@
         <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="F120" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="G120" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="H120" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J120">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K120">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6234,31 +6243,31 @@
         <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H121" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J121">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K121">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6269,31 +6278,31 @@
         <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F122" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G122" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H122" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K122">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6304,31 +6313,31 @@
         <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F123" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G123" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H123" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K123">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6339,66 +6348,66 @@
         <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F124" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G124" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H124" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K124">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>130</v>
+        <v>291</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="F125" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="H125" t="s">
-        <v>97</v>
+        <v>317</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J125" t="s">
-        <v>97</v>
-      </c>
-      <c r="K125" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J125">
+        <v>14</v>
+      </c>
+      <c r="K125">
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6409,31 +6418,31 @@
         <v>210</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E126" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="F126" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="G126" t="s">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="H126" t="s">
-        <v>338</v>
+        <v>97</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J126" s="2">
-        <v>1</v>
-      </c>
-      <c r="K126" s="2">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J126" t="s">
+        <v>97</v>
+      </c>
+      <c r="K126" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6444,31 +6453,31 @@
         <v>210</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E127" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F127" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G127" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H127" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J127">
-        <v>2</v>
-      </c>
-      <c r="K127">
-        <v>2</v>
+      <c r="J127" s="2">
+        <v>1</v>
+      </c>
+      <c r="K127" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6479,31 +6488,31 @@
         <v>210</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E128" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F128" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G128" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H128" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K128">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
@@ -6514,31 +6523,31 @@
         <v>210</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E129" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F129" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G129" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H129" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K129">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
@@ -6549,31 +6558,31 @@
         <v>210</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E130" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F130" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G130" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H130" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K130">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
@@ -6584,31 +6593,31 @@
         <v>210</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E131" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F131" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G131" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H131" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K131">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
@@ -6619,31 +6628,31 @@
         <v>210</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F132" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G132" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H132" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J132">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K132">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
@@ -6654,31 +6663,31 @@
         <v>210</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E133" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F133" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G133" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H133" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J133">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K133">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
@@ -6689,31 +6698,31 @@
         <v>210</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E134" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F134" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G134" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H134" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K134">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
@@ -6724,31 +6733,31 @@
         <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="F135" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="G135" t="s">
-        <v>257</v>
+        <v>359</v>
       </c>
       <c r="H135" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J135">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K135">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.2">
@@ -6759,31 +6768,31 @@
         <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="F136" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="G136" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="H136" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J136">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K136">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.2">
@@ -6794,31 +6803,31 @@
         <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F137" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G137" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H137" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J137">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K137">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.2">
@@ -6829,31 +6838,31 @@
         <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F138" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G138" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H138" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J138">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K138">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.2">
@@ -6864,66 +6873,66 @@
         <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F139" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G139" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H139" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K139">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="F140" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="G140" t="s">
-        <v>97</v>
+        <v>363</v>
       </c>
       <c r="H140" t="s">
-        <v>97</v>
+        <v>350</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J140" t="s">
-        <v>97</v>
-      </c>
-      <c r="K140" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J140">
+        <v>14</v>
+      </c>
+      <c r="K140">
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.2">
@@ -6934,38 +6943,32 @@
         <v>211</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>218</v>
+        <v>127</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E141" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="F141" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="G141" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="H141" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J141" s="2">
-        <v>1</v>
-      </c>
-      <c r="K141" s="2">
-        <v>1</v>
-      </c>
-      <c r="L141" s="2"/>
-      <c r="M141" s="2"/>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" s="2"/>
-      <c r="Q141" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J141" t="s">
+        <v>97</v>
+      </c>
+      <c r="K141" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
@@ -6975,31 +6978,31 @@
         <v>211</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E142" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F142" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G142" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H142" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -7016,31 +7019,31 @@
         <v>211</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E143" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="F143" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="G143" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="H143" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -7051,38 +7054,44 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E144" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F144" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G144" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="H144" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J144" t="s">
-        <v>97</v>
-      </c>
-      <c r="K144" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J144" s="2">
+        <v>3</v>
+      </c>
+      <c r="K144" s="2">
+        <v>3</v>
+      </c>
+      <c r="L144" s="2"/>
+      <c r="M144" s="2"/>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" s="2"/>
+      <c r="Q144" s="2"/>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
@@ -7092,73 +7101,73 @@
         <v>212</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>150</v>
       </c>
       <c r="E145" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="F145" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="G145" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="H145" t="s">
-        <v>217</v>
+        <v>97</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J145" s="2">
-        <v>1</v>
-      </c>
-      <c r="K145" s="2">
-        <v>1</v>
-      </c>
-      <c r="L145" s="2"/>
-      <c r="M145" s="2"/>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-      <c r="P145" s="2"/>
-      <c r="Q145" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J145" t="s">
+        <v>97</v>
+      </c>
+      <c r="K145" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E146" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="F146" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="G146" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="H146" t="s">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J146" t="s">
-        <v>97</v>
-      </c>
-      <c r="K146" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J146" s="2">
+        <v>1</v>
+      </c>
+      <c r="K146" s="2">
+        <v>1</v>
+      </c>
+      <c r="L146" s="2"/>
+      <c r="M146" s="2"/>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" s="2"/>
+      <c r="Q146" s="2"/>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
@@ -7168,38 +7177,73 @@
         <v>213</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E147" t="s">
+        <v>97</v>
+      </c>
+      <c r="F147" t="s">
+        <v>97</v>
+      </c>
+      <c r="G147" t="s">
+        <v>97</v>
+      </c>
+      <c r="H147" t="s">
+        <v>97</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J147" t="s">
+        <v>97</v>
+      </c>
+      <c r="K147" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A148" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E148" t="s">
         <v>67</v>
       </c>
-      <c r="F147" t="s">
+      <c r="F148" t="s">
         <v>67</v>
       </c>
-      <c r="G147" t="s">
+      <c r="G148" t="s">
         <v>67</v>
       </c>
-      <c r="H147" t="s">
+      <c r="H148" t="s">
         <v>68</v>
       </c>
-      <c r="I147" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J147" s="2">
+      <c r="I148" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J148" s="2">
         <v>1</v>
       </c>
-      <c r="K147" s="2">
+      <c r="K148" s="2">
         <v>1</v>
       </c>
-      <c r="L147" s="2"/>
-      <c r="M147" s="2"/>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
-      <c r="P147" s="2"/>
-      <c r="Q147" s="2"/>
+      <c r="L148" s="2"/>
+      <c r="M148" s="2"/>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" s="2"/>
+      <c r="Q148" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90526B38-DBC8-1346-9672-72F65125A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CE0322-EBD4-A341-97FE-9C9E9B313549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="469">
   <si>
     <t>category</t>
   </si>
@@ -1409,6 +1409,24 @@
   </si>
   <si>
     <t>Aghoramoorthy_sahasranaama_stotram_naamaavali_1_and_2</t>
+  </si>
+  <si>
+    <t>N008</t>
+  </si>
+  <si>
+    <t>N009</t>
+  </si>
+  <si>
+    <t>Aghoramoorthy_stotram_stavam_ashtakam</t>
+  </si>
+  <si>
+    <t>Aghoramoorthy_stotram_stavam_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Atharva_shikhopanishad</t>
+  </si>
+  <si>
+    <t>Shri_Atharva_shikhopanishad.pdf</t>
   </si>
 </sst>
 </file>
@@ -1780,7 +1798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q148"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5718,66 +5736,72 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>125</v>
+        <v>463</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E106" t="s">
-        <v>97</v>
+        <v>465</v>
       </c>
       <c r="F106" t="s">
-        <v>97</v>
+        <v>465</v>
+      </c>
+      <c r="G106" t="s">
+        <v>465</v>
+      </c>
+      <c r="H106" t="s">
+        <v>466</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J106" t="s">
-        <v>97</v>
-      </c>
-      <c r="K106" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J106">
+        <v>8</v>
+      </c>
+      <c r="K106">
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>185</v>
+        <v>464</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E107" t="s">
-        <v>186</v>
+        <v>467</v>
       </c>
       <c r="F107" t="s">
-        <v>186</v>
+        <v>467</v>
       </c>
       <c r="G107" t="s">
-        <v>186</v>
+        <v>467</v>
       </c>
       <c r="H107" t="s">
-        <v>187</v>
+        <v>468</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
@@ -5788,31 +5812,25 @@
         <v>152</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E108" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F108" t="s">
-        <v>188</v>
-      </c>
-      <c r="G108" t="s">
-        <v>188</v>
-      </c>
-      <c r="H108" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J108">
-        <v>2</v>
-      </c>
-      <c r="K108">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J108" t="s">
+        <v>97</v>
+      </c>
+      <c r="K108" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -5823,31 +5841,31 @@
         <v>152</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E109" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F109" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G109" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H109" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K109">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
@@ -5858,101 +5876,101 @@
         <v>152</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E110" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F110" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G110" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H110" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K110">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E111" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="F111" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="G111" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="H111" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J111" t="s">
-        <v>97</v>
-      </c>
-      <c r="K111" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J111">
+        <v>3</v>
+      </c>
+      <c r="K111">
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E112" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="F112" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="G112" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="H112" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J112" s="2">
-        <v>1</v>
-      </c>
-      <c r="K112" s="2">
-        <v>1</v>
+      <c r="J112">
+        <v>4</v>
+      </c>
+      <c r="K112">
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -5963,31 +5981,31 @@
         <v>209</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E113" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="F113" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G113" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="H113" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J113">
-        <v>2</v>
-      </c>
-      <c r="K113">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J113" t="s">
+        <v>97</v>
+      </c>
+      <c r="K113" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -5998,31 +6016,31 @@
         <v>209</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E114" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F114" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G114" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H114" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J114">
-        <v>3</v>
-      </c>
-      <c r="K114">
-        <v>3</v>
+      <c r="J114" s="2">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -6033,31 +6051,31 @@
         <v>209</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E115" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F115" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G115" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H115" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K115">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -6068,31 +6086,31 @@
         <v>209</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H116" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K116">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -6103,31 +6121,31 @@
         <v>209</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F117" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G117" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H117" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J117">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K117">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -6138,31 +6156,31 @@
         <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F118" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G118" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H118" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K118">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -6173,31 +6191,31 @@
         <v>209</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E119" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F119" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G119" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H119" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K119">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6208,31 +6226,31 @@
         <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="F120" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="G120" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="H120" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J120">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K120">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6243,31 +6261,31 @@
         <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F121" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G121" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H121" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J121">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K121">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6278,31 +6296,31 @@
         <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="F122" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="G122" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="H122" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K122">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6313,31 +6331,31 @@
         <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F123" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G123" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H123" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K123">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6348,31 +6366,31 @@
         <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F124" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G124" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H124" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K124">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6383,101 +6401,101 @@
         <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F125" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G125" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H125" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K125">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="F126" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="G126" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="H126" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J126" t="s">
-        <v>97</v>
-      </c>
-      <c r="K126" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J126">
+        <v>13</v>
+      </c>
+      <c r="K126">
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="F127" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="G127" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="H127" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J127" s="2">
-        <v>1</v>
-      </c>
-      <c r="K127" s="2">
-        <v>1</v>
+      <c r="J127">
+        <v>14</v>
+      </c>
+      <c r="K127">
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6488,31 +6506,31 @@
         <v>210</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E128" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="F128" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="G128" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="H128" t="s">
-        <v>339</v>
+        <v>97</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J128">
-        <v>2</v>
-      </c>
-      <c r="K128">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J128" t="s">
+        <v>97</v>
+      </c>
+      <c r="K128" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
@@ -6523,31 +6541,31 @@
         <v>210</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E129" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F129" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G129" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H129" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J129">
-        <v>3</v>
-      </c>
-      <c r="K129">
-        <v>3</v>
+      <c r="J129" s="2">
+        <v>1</v>
+      </c>
+      <c r="K129" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
@@ -6558,31 +6576,31 @@
         <v>210</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E130" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F130" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G130" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H130" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
@@ -6593,31 +6611,31 @@
         <v>210</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E131" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F131" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G131" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H131" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K131">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
@@ -6628,31 +6646,31 @@
         <v>210</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F132" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G132" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H132" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J132">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K132">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
@@ -6663,31 +6681,31 @@
         <v>210</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E133" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F133" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G133" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H133" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J133">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K133">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
@@ -6698,31 +6716,31 @@
         <v>210</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E134" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F134" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G134" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H134" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K134">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
@@ -6733,31 +6751,31 @@
         <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F135" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G135" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H135" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J135">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K135">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.2">
@@ -6768,31 +6786,31 @@
         <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="F136" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="G136" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="H136" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J136">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K136">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.2">
@@ -6803,31 +6821,31 @@
         <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F137" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G137" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H137" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J137">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K137">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.2">
@@ -6838,31 +6856,31 @@
         <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F138" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="G138" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="H138" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J138">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K138">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.2">
@@ -6873,31 +6891,31 @@
         <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F139" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G139" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H139" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K139">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.2">
@@ -6908,108 +6926,102 @@
         <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F140" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G140" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H140" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J140">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K140">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E141" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="F141" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="G141" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="H141" t="s">
-        <v>97</v>
+        <v>349</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J141" t="s">
-        <v>97</v>
-      </c>
-      <c r="K141" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J141">
+        <v>13</v>
+      </c>
+      <c r="K141">
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="F142" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="G142" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="H142" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J142" s="2">
-        <v>1</v>
-      </c>
-      <c r="K142" s="2">
-        <v>1</v>
-      </c>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" s="2"/>
-      <c r="Q142" s="2"/>
+      <c r="J142">
+        <v>14</v>
+      </c>
+      <c r="K142">
+        <v>14</v>
+      </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
@@ -7019,38 +7031,32 @@
         <v>211</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E143" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="F143" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="G143" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H143" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J143" s="2">
-        <v>2</v>
-      </c>
-      <c r="K143" s="2">
-        <v>2</v>
-      </c>
-      <c r="L143" s="2"/>
-      <c r="M143" s="2"/>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
-      <c r="P143" s="2"/>
-      <c r="Q143" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J143" t="s">
+        <v>97</v>
+      </c>
+      <c r="K143" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
@@ -7060,31 +7066,31 @@
         <v>211</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E144" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="G144" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="H144" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J144" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K144" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -7095,72 +7101,78 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>128</v>
+        <v>219</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E145" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F145" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G145" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H145" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J145" t="s">
-        <v>97</v>
-      </c>
-      <c r="K145" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J145" s="2">
+        <v>2</v>
+      </c>
+      <c r="K145" s="2">
+        <v>2</v>
+      </c>
+      <c r="L145" s="2"/>
+      <c r="M145" s="2"/>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" s="2"/>
+      <c r="Q145" s="2"/>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E146" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F146" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G146" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H146" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J146" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K146" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -7171,16 +7183,16 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E147" t="s">
         <v>97</v>
@@ -7206,28 +7218,28 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E148" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F148" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="G148" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="H148" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>70</v>
@@ -7245,6 +7257,82 @@
       <c r="P148" s="2"/>
       <c r="Q148" s="2"/>
     </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A149" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E149" t="s">
+        <v>97</v>
+      </c>
+      <c r="F149" t="s">
+        <v>97</v>
+      </c>
+      <c r="G149" t="s">
+        <v>97</v>
+      </c>
+      <c r="H149" t="s">
+        <v>97</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J149" t="s">
+        <v>97</v>
+      </c>
+      <c r="K149" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A150" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E150" t="s">
+        <v>67</v>
+      </c>
+      <c r="F150" t="s">
+        <v>67</v>
+      </c>
+      <c r="G150" t="s">
+        <v>67</v>
+      </c>
+      <c r="H150" t="s">
+        <v>68</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J150" s="2">
+        <v>1</v>
+      </c>
+      <c r="K150" s="2">
+        <v>1</v>
+      </c>
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+      <c r="P150" s="2"/>
+      <c r="Q150" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CE0322-EBD4-A341-97FE-9C9E9B313549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8FDB4-84EE-D24D-8192-337AEE73039B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="481">
   <si>
     <t>category</t>
   </si>
@@ -1427,6 +1427,42 @@
   </si>
   <si>
     <t>Shri_Atharva_shikhopanishad.pdf</t>
+  </si>
+  <si>
+    <t>N010</t>
+  </si>
+  <si>
+    <t>N011</t>
+  </si>
+  <si>
+    <t>N012</t>
+  </si>
+  <si>
+    <t>N013</t>
+  </si>
+  <si>
+    <t>Shrimad_anaadhi_kalpeshwara_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shrimad_anaadhi_siddha_linga_stavam.pdf</t>
+  </si>
+  <si>
+    <t>Shrimad_anaahateshwara_sammohana_kavacham.pdf</t>
+  </si>
+  <si>
+    <t>Anyaapadesha_shatakam_Neelakanta_deekshitar.pdf</t>
+  </si>
+  <si>
+    <t>Shrimad_anaadhi_kalpeshwara_stotram</t>
+  </si>
+  <si>
+    <t>Shrimad_anaadhi_siddha_linga_stavam</t>
+  </si>
+  <si>
+    <t>Shrimad_anaahateshwara_sammohana_kavacham</t>
+  </si>
+  <si>
+    <t>Anyaapadesha_shatakam_Neelakanta_deekshitar</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q150"/>
+  <dimension ref="A1:Q154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5806,136 +5842,142 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>125</v>
+        <v>469</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" t="s">
-        <v>97</v>
+        <v>477</v>
       </c>
       <c r="F108" t="s">
-        <v>97</v>
+        <v>477</v>
+      </c>
+      <c r="G108" t="s">
+        <v>477</v>
+      </c>
+      <c r="H108" t="s">
+        <v>473</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J108" t="s">
-        <v>97</v>
-      </c>
-      <c r="K108" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J108">
+        <v>10</v>
+      </c>
+      <c r="K108">
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>185</v>
+        <v>470</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E109" t="s">
-        <v>186</v>
+        <v>478</v>
       </c>
       <c r="F109" t="s">
-        <v>186</v>
+        <v>478</v>
       </c>
       <c r="G109" t="s">
-        <v>186</v>
+        <v>478</v>
       </c>
       <c r="H109" t="s">
-        <v>187</v>
+        <v>474</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K109">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>190</v>
+        <v>471</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E110" t="s">
-        <v>188</v>
+        <v>479</v>
       </c>
       <c r="F110" t="s">
-        <v>188</v>
+        <v>479</v>
       </c>
       <c r="G110" t="s">
-        <v>188</v>
+        <v>479</v>
       </c>
       <c r="H110" t="s">
-        <v>189</v>
+        <v>475</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J110">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>191</v>
+        <v>472</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E111" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="F111" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="G111" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="H111" t="s">
-        <v>194</v>
+        <v>476</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J111">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5946,171 +5988,165 @@
         <v>152</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E112" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="F112" t="s">
-        <v>195</v>
-      </c>
-      <c r="G112" t="s">
-        <v>195</v>
-      </c>
-      <c r="H112" t="s">
-        <v>196</v>
+        <v>97</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J112">
-        <v>4</v>
-      </c>
-      <c r="K112">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J112" t="s">
+        <v>97</v>
+      </c>
+      <c r="K112" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E113" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="F113" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="G113" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="H113" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J113" t="s">
-        <v>97</v>
-      </c>
-      <c r="K113" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E114" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
       <c r="F114" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
       <c r="G114" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
       <c r="H114" t="s">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J114" s="2">
-        <v>1</v>
-      </c>
-      <c r="K114" s="2">
-        <v>1</v>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E115" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="F115" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="G115" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="H115" t="s">
-        <v>293</v>
+        <v>194</v>
       </c>
       <c r="I115" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E116" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="F116" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="G116" t="s">
-        <v>306</v>
+        <v>195</v>
       </c>
       <c r="H116" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K116">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -6121,31 +6157,31 @@
         <v>209</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E117" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="F117" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="G117" t="s">
-        <v>307</v>
+        <v>97</v>
       </c>
       <c r="H117" t="s">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J117">
-        <v>4</v>
-      </c>
-      <c r="K117">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J117" t="s">
+        <v>97</v>
+      </c>
+      <c r="K117" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -6156,31 +6192,31 @@
         <v>209</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E118" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F118" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G118" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="H118" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J118">
-        <v>5</v>
-      </c>
-      <c r="K118">
-        <v>5</v>
+      <c r="J118" s="2">
+        <v>1</v>
+      </c>
+      <c r="K118" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -6191,31 +6227,31 @@
         <v>209</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E119" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F119" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G119" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H119" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K119">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6226,31 +6262,31 @@
         <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F120" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G120" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H120" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J120">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K120">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6261,31 +6297,31 @@
         <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F121" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G121" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H121" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J121">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K121">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6296,31 +6332,31 @@
         <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="F122" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="G122" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="H122" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K122">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6331,31 +6367,31 @@
         <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F123" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G123" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H123" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K123">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6366,31 +6402,31 @@
         <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F124" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G124" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H124" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K124">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6401,31 +6437,31 @@
         <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F125" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G125" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H125" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J125">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K125">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6436,31 +6472,31 @@
         <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="F126" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="G126" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="H126" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J126">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K126">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6471,174 +6507,174 @@
         <v>209</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F127" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G127" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H127" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K127">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>130</v>
+        <v>288</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E128" t="s">
-        <v>97</v>
+        <v>313</v>
       </c>
       <c r="F128" t="s">
-        <v>97</v>
+        <v>313</v>
       </c>
       <c r="G128" t="s">
-        <v>97</v>
+        <v>313</v>
       </c>
       <c r="H128" t="s">
-        <v>97</v>
+        <v>301</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J128" t="s">
-        <v>97</v>
-      </c>
-      <c r="K128" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="J128">
+        <v>11</v>
+      </c>
+      <c r="K128">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E129" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="F129" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="G129" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="H129" t="s">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J129" s="2">
-        <v>1</v>
-      </c>
-      <c r="K129" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J129">
+        <v>12</v>
+      </c>
+      <c r="K129">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="F130" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="G130" t="s">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="H130" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K130">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="F131" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="G131" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="H131" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K131">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>113</v>
       </c>
@@ -6646,34 +6682,34 @@
         <v>210</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>327</v>
+        <v>130</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>354</v>
+        <v>97</v>
       </c>
       <c r="F132" t="s">
-        <v>354</v>
+        <v>97</v>
       </c>
       <c r="G132" t="s">
-        <v>354</v>
+        <v>97</v>
       </c>
       <c r="H132" t="s">
-        <v>341</v>
+        <v>97</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J132">
-        <v>4</v>
-      </c>
-      <c r="K132">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="J132" t="s">
+        <v>97</v>
+      </c>
+      <c r="K132" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>113</v>
       </c>
@@ -6681,34 +6717,34 @@
         <v>210</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>328</v>
+        <v>254</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E133" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F133" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G133" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H133" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J133">
-        <v>5</v>
-      </c>
-      <c r="K133">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J133" s="2">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>113</v>
       </c>
@@ -6716,34 +6752,34 @@
         <v>210</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E134" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F134" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G134" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H134" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K134">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>113</v>
       </c>
@@ -6751,34 +6787,34 @@
         <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F135" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G135" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H135" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J135">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K135">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>113</v>
       </c>
@@ -6786,34 +6822,34 @@
         <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F136" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G136" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H136" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J136">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K136">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>113</v>
       </c>
@@ -6821,34 +6857,34 @@
         <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F137" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G137" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H137" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J137">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K137">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>113</v>
       </c>
@@ -6856,34 +6892,34 @@
         <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="F138" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="G138" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="H138" t="s">
-        <v>258</v>
+        <v>343</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J138">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K138">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>113</v>
       </c>
@@ -6891,34 +6927,34 @@
         <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F139" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G139" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H139" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K139">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>113</v>
       </c>
@@ -6926,34 +6962,34 @@
         <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F140" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G140" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H140" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J140">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K140">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>113</v>
       </c>
@@ -6961,34 +6997,34 @@
         <v>210</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E141" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F141" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G141" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H141" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J141">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K141">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>113</v>
       </c>
@@ -6996,203 +7032,185 @@
         <v>210</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>363</v>
+        <v>257</v>
       </c>
       <c r="F142" t="s">
-        <v>363</v>
+        <v>257</v>
       </c>
       <c r="G142" t="s">
-        <v>363</v>
+        <v>257</v>
       </c>
       <c r="H142" t="s">
-        <v>350</v>
+        <v>258</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K142">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>97</v>
+        <v>360</v>
       </c>
       <c r="F143" t="s">
-        <v>97</v>
+        <v>360</v>
       </c>
       <c r="G143" t="s">
-        <v>97</v>
+        <v>360</v>
       </c>
       <c r="H143" t="s">
-        <v>97</v>
+        <v>347</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J143" t="s">
-        <v>97</v>
-      </c>
-      <c r="K143" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="J143">
+        <v>11</v>
+      </c>
+      <c r="K143">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>218</v>
+        <v>335</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E144" t="s">
-        <v>177</v>
+        <v>361</v>
       </c>
       <c r="F144" t="s">
-        <v>177</v>
+        <v>361</v>
       </c>
       <c r="G144" t="s">
-        <v>177</v>
+        <v>361</v>
       </c>
       <c r="H144" t="s">
-        <v>178</v>
+        <v>348</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="2">
-        <v>1</v>
-      </c>
-      <c r="K144" s="2">
-        <v>1</v>
-      </c>
-      <c r="L144" s="2"/>
-      <c r="M144" s="2"/>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
-      <c r="P144" s="2"/>
-      <c r="Q144" s="2"/>
+      <c r="J144">
+        <v>12</v>
+      </c>
+      <c r="K144">
+        <v>12</v>
+      </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>219</v>
+        <v>336</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="F145" t="s">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="G145" t="s">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="H145" t="s">
-        <v>176</v>
+        <v>349</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J145" s="2">
-        <v>2</v>
-      </c>
-      <c r="K145" s="2">
-        <v>2</v>
-      </c>
-      <c r="L145" s="2"/>
-      <c r="M145" s="2"/>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
-      <c r="P145" s="2"/>
-      <c r="Q145" s="2"/>
+      <c r="J145">
+        <v>13</v>
+      </c>
+      <c r="K145">
+        <v>13</v>
+      </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="F146" t="s">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="G146" t="s">
-        <v>222</v>
+        <v>363</v>
       </c>
       <c r="H146" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J146" s="2">
-        <v>3</v>
-      </c>
-      <c r="K146" s="2">
-        <v>3</v>
-      </c>
-      <c r="L146" s="2"/>
-      <c r="M146" s="2"/>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-      <c r="P146" s="2"/>
-      <c r="Q146" s="2"/>
+      <c r="J146">
+        <v>14</v>
+      </c>
+      <c r="K146">
+        <v>14</v>
+      </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E147" t="s">
         <v>97</v>
@@ -7218,28 +7236,28 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E148" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="F148" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="G148" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="H148" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>70</v>
@@ -7259,72 +7277,78 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E149" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F149" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G149" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H149" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J149" t="s">
-        <v>97</v>
-      </c>
-      <c r="K149" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J149" s="2">
+        <v>2</v>
+      </c>
+      <c r="K149" s="2">
+        <v>2</v>
+      </c>
+      <c r="L149" s="2"/>
+      <c r="M149" s="2"/>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
+      <c r="P149" s="2"/>
+      <c r="Q149" s="2"/>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E150" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="F150" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="G150" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="H150" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J150" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K150" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -7333,6 +7357,158 @@
       <c r="P150" s="2"/>
       <c r="Q150" s="2"/>
     </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A151" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E151" t="s">
+        <v>97</v>
+      </c>
+      <c r="F151" t="s">
+        <v>97</v>
+      </c>
+      <c r="G151" t="s">
+        <v>97</v>
+      </c>
+      <c r="H151" t="s">
+        <v>97</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J151" t="s">
+        <v>97</v>
+      </c>
+      <c r="K151" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A152" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E152" t="s">
+        <v>216</v>
+      </c>
+      <c r="F152" t="s">
+        <v>216</v>
+      </c>
+      <c r="G152" t="s">
+        <v>216</v>
+      </c>
+      <c r="H152" t="s">
+        <v>217</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J152" s="2">
+        <v>1</v>
+      </c>
+      <c r="K152" s="2">
+        <v>1</v>
+      </c>
+      <c r="L152" s="2"/>
+      <c r="M152" s="2"/>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" s="2"/>
+      <c r="Q152" s="2"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A153" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E153" t="s">
+        <v>97</v>
+      </c>
+      <c r="F153" t="s">
+        <v>97</v>
+      </c>
+      <c r="G153" t="s">
+        <v>97</v>
+      </c>
+      <c r="H153" t="s">
+        <v>97</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J153" t="s">
+        <v>97</v>
+      </c>
+      <c r="K153" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A154" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E154" t="s">
+        <v>67</v>
+      </c>
+      <c r="F154" t="s">
+        <v>67</v>
+      </c>
+      <c r="G154" t="s">
+        <v>67</v>
+      </c>
+      <c r="H154" t="s">
+        <v>68</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J154" s="2">
+        <v>1</v>
+      </c>
+      <c r="K154" s="2">
+        <v>1</v>
+      </c>
+      <c r="L154" s="2"/>
+      <c r="M154" s="2"/>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" s="2"/>
+      <c r="Q154" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8FDB4-84EE-D24D-8192-337AEE73039B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081C2FAB-F2B0-BA45-8ECE-3C00057DC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="490">
   <si>
     <t>category</t>
   </si>
@@ -1381,9 +1381,6 @@
     <t>Shri_Agastesha_lingaashtakam.pdf</t>
   </si>
   <si>
-    <t>Shri_Ahoramoorthy_kavacham.pdf</t>
-  </si>
-  <si>
     <t>Shrimad_akhilaanda_devi_jambhukeshwara_stuti_dringeri.pdf</t>
   </si>
   <si>
@@ -1396,9 +1393,6 @@
     <t>Shri_Agastesha_lingaashtakam</t>
   </si>
   <si>
-    <t>Shri_Ahoramoorthy_kavacham</t>
-  </si>
-  <si>
     <t>Shrimad_akhilaanda_devi_jambhukeshwara_stuti_dringeri</t>
   </si>
   <si>
@@ -1463,6 +1457,39 @@
   </si>
   <si>
     <t>Anyaapadesha_shatakam_Neelakanta_deekshitar</t>
+  </si>
+  <si>
+    <t>Shri_Aghoramoorthy_kavacham</t>
+  </si>
+  <si>
+    <t>Shri_Aghoramoorthy_kavacham.pdf</t>
+  </si>
+  <si>
+    <t>N014</t>
+  </si>
+  <si>
+    <t>N015</t>
+  </si>
+  <si>
+    <t>N016</t>
+  </si>
+  <si>
+    <t>Amaranaatha_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Aparaadha_ashtakam_Shiva_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atma_vaibhava_nirupanam.pdf</t>
+  </si>
+  <si>
+    <t>Amaranaatha_ashtakam</t>
+  </si>
+  <si>
+    <t>Aparaadha_ashtakam_Shiva_ashtakam</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atma_vaibhava_nirupanam</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q154"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -5574,13 +5601,13 @@
         <v>145</v>
       </c>
       <c r="E100" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F100" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G100" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H100" t="s">
         <v>450</v>
@@ -5609,13 +5636,13 @@
         <v>145</v>
       </c>
       <c r="E101" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F101" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G101" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H101" t="s">
         <v>451</v>
@@ -5644,13 +5671,13 @@
         <v>145</v>
       </c>
       <c r="E102" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F102" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G102" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H102" t="s">
         <v>452</v>
@@ -5679,16 +5706,16 @@
         <v>145</v>
       </c>
       <c r="E103" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="F103" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="G103" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="H103" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>70</v>
@@ -5714,16 +5741,16 @@
         <v>145</v>
       </c>
       <c r="E104" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F104" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G104" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H104" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>70</v>
@@ -5743,22 +5770,22 @@
         <v>263</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E105" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F105" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G105" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H105" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>70</v>
@@ -5778,22 +5805,22 @@
         <v>263</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E106" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F106" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G106" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H106" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>70</v>
@@ -5813,22 +5840,22 @@
         <v>263</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E107" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F107" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G107" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H107" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>70</v>
@@ -5848,22 +5875,22 @@
         <v>263</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E108" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F108" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G108" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H108" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>70</v>
@@ -5883,22 +5910,22 @@
         <v>263</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E109" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F109" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G109" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H109" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>70</v>
@@ -5918,22 +5945,22 @@
         <v>263</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E110" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F110" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G110" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H110" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>70</v>
@@ -5953,22 +5980,22 @@
         <v>263</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>145</v>
       </c>
       <c r="E111" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F111" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G111" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H111" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>70</v>
@@ -5982,101 +6009,107 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>125</v>
+        <v>481</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" t="s">
-        <v>97</v>
+        <v>487</v>
       </c>
       <c r="F112" t="s">
-        <v>97</v>
+        <v>487</v>
+      </c>
+      <c r="G112" t="s">
+        <v>487</v>
+      </c>
+      <c r="H112" t="s">
+        <v>484</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J112" t="s">
-        <v>97</v>
-      </c>
-      <c r="K112" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J112">
+        <v>14</v>
+      </c>
+      <c r="K112">
+        <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>185</v>
+        <v>482</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E113" t="s">
-        <v>186</v>
+        <v>488</v>
       </c>
       <c r="F113" t="s">
-        <v>186</v>
+        <v>488</v>
       </c>
       <c r="G113" t="s">
-        <v>186</v>
+        <v>488</v>
       </c>
       <c r="H113" t="s">
-        <v>187</v>
+        <v>485</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K113">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>190</v>
+        <v>483</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E114" t="s">
-        <v>188</v>
+        <v>489</v>
       </c>
       <c r="F114" t="s">
-        <v>188</v>
+        <v>489</v>
       </c>
       <c r="G114" t="s">
-        <v>188</v>
+        <v>489</v>
       </c>
       <c r="H114" t="s">
-        <v>189</v>
+        <v>486</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J114">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K114">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -6087,31 +6120,25 @@
         <v>152</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E115" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F115" t="s">
-        <v>193</v>
-      </c>
-      <c r="G115" t="s">
-        <v>193</v>
-      </c>
-      <c r="H115" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J115">
-        <v>3</v>
-      </c>
-      <c r="K115">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J115" t="s">
+        <v>97</v>
+      </c>
+      <c r="K115" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -6122,136 +6149,136 @@
         <v>152</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E116" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F116" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G116" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H116" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K116">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E117" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="F117" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="G117" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H117" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J117" t="s">
-        <v>97</v>
-      </c>
-      <c r="K117" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J117">
+        <v>2</v>
+      </c>
+      <c r="K117">
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E118" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="F118" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="G118" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="H118" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J118" s="2">
-        <v>1</v>
-      </c>
-      <c r="K118" s="2">
-        <v>1</v>
+      <c r="J118">
+        <v>3</v>
+      </c>
+      <c r="K118">
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="F119" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="G119" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="H119" t="s">
-        <v>293</v>
+        <v>196</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K119">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6262,31 +6289,31 @@
         <v>209</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>280</v>
+        <v>126</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="G120" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="H120" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J120">
-        <v>3</v>
-      </c>
-      <c r="K120">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J120" t="s">
+        <v>97</v>
+      </c>
+      <c r="K120" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6297,31 +6324,31 @@
         <v>209</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E121" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F121" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G121" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H121" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J121">
-        <v>4</v>
-      </c>
-      <c r="K121">
-        <v>4</v>
+      <c r="J121" s="2">
+        <v>1</v>
+      </c>
+      <c r="K121" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6332,31 +6359,31 @@
         <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F122" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G122" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H122" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J122">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K122">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6367,31 +6394,31 @@
         <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F123" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G123" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H123" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J123">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K123">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6402,31 +6429,31 @@
         <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F124" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G124" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H124" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K124">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6437,31 +6464,31 @@
         <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H125" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J125">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K125">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6472,31 +6499,31 @@
         <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="F126" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="G126" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="H126" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J126">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K126">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6507,31 +6534,31 @@
         <v>209</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F127" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G127" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H127" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K127">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6542,31 +6569,31 @@
         <v>209</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E128" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F128" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G128" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H128" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J128">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K128">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -6577,31 +6604,31 @@
         <v>209</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E129" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="F129" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="G129" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H129" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J129">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K129">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
@@ -6612,31 +6639,31 @@
         <v>209</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F130" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G130" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H130" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K130">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
@@ -6647,136 +6674,136 @@
         <v>209</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F131" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G131" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H131" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K131">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>130</v>
+        <v>289</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="F132" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="G132" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="H132" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J132" t="s">
-        <v>97</v>
-      </c>
-      <c r="K132" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J132">
+        <v>12</v>
+      </c>
+      <c r="K132">
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E133" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="F133" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="G133" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="H133" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J133" s="2">
-        <v>1</v>
-      </c>
-      <c r="K133" s="2">
-        <v>1</v>
+      <c r="J133">
+        <v>13</v>
+      </c>
+      <c r="K133">
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E134" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="F134" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="G134" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="H134" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K134">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
@@ -6787,31 +6814,31 @@
         <v>210</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>326</v>
+        <v>130</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E135" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="F135" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="G135" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="H135" t="s">
-        <v>340</v>
+        <v>97</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J135">
-        <v>3</v>
-      </c>
-      <c r="K135">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J135" t="s">
+        <v>97</v>
+      </c>
+      <c r="K135" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
@@ -6822,31 +6849,31 @@
         <v>210</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>327</v>
+        <v>254</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F136" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G136" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H136" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J136">
-        <v>4</v>
-      </c>
-      <c r="K136">
-        <v>4</v>
+      <c r="J136" s="2">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
@@ -6857,31 +6884,31 @@
         <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F137" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G137" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H137" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J137">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K137">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
@@ -6892,31 +6919,31 @@
         <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F138" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G138" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H138" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J138">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K138">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
@@ -6927,31 +6954,31 @@
         <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F139" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G139" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H139" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K139">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
@@ -6962,31 +6989,31 @@
         <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F140" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G140" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H140" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J140">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K140">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
@@ -6997,31 +7024,31 @@
         <v>210</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E141" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F141" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G141" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H141" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J141">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K141">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -7032,31 +7059,31 @@
         <v>210</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="F142" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="G142" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="H142" t="s">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K142">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
@@ -7067,31 +7094,31 @@
         <v>210</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F143" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G143" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H143" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J143">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K143">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
@@ -7102,31 +7129,31 @@
         <v>210</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G144" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H144" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J144">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K144">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
@@ -7137,31 +7164,31 @@
         <v>210</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="F145" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="G145" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="H145" t="s">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J145">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K145">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
@@ -7172,149 +7199,137 @@
         <v>210</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F146" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G146" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H146" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J146">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K146">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E147" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="F147" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="G147" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="H147" t="s">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J147" t="s">
-        <v>97</v>
-      </c>
-      <c r="K147" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J147">
+        <v>12</v>
+      </c>
+      <c r="K147">
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>218</v>
+        <v>336</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E148" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="F148" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="G148" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="H148" t="s">
-        <v>178</v>
+        <v>349</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J148" s="2">
-        <v>1</v>
-      </c>
-      <c r="K148" s="2">
-        <v>1</v>
-      </c>
-      <c r="L148" s="2"/>
-      <c r="M148" s="2"/>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
-      <c r="P148" s="2"/>
-      <c r="Q148" s="2"/>
+      <c r="J148">
+        <v>13</v>
+      </c>
+      <c r="K148">
+        <v>13</v>
+      </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E149" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="F149" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="G149" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="H149" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J149" s="2">
-        <v>2</v>
-      </c>
-      <c r="K149" s="2">
-        <v>2</v>
-      </c>
-      <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
-      <c r="P149" s="2"/>
-      <c r="Q149" s="2"/>
+      <c r="J149">
+        <v>14</v>
+      </c>
+      <c r="K149">
+        <v>14</v>
+      </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
@@ -7324,107 +7339,107 @@
         <v>211</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E150" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="F150" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="G150" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="H150" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J150" s="2">
-        <v>3</v>
-      </c>
-      <c r="K150" s="2">
-        <v>3</v>
-      </c>
-      <c r="L150" s="2"/>
-      <c r="M150" s="2"/>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
-      <c r="P150" s="2"/>
-      <c r="Q150" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J150" t="s">
+        <v>97</v>
+      </c>
+      <c r="K150" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E151" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G151" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H151" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J151" t="s">
-        <v>97</v>
-      </c>
-      <c r="K151" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J151" s="2">
+        <v>1</v>
+      </c>
+      <c r="K151" s="2">
+        <v>1</v>
+      </c>
+      <c r="L151" s="2"/>
+      <c r="M151" s="2"/>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" s="2"/>
+      <c r="Q151" s="2"/>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E152" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="F152" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="G152" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="H152" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -7435,79 +7450,196 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E153" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F153" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G153" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="H153" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J153" t="s">
-        <v>97</v>
-      </c>
-      <c r="K153" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J153" s="2">
+        <v>3</v>
+      </c>
+      <c r="K153" s="2">
+        <v>3</v>
+      </c>
+      <c r="L153" s="2"/>
+      <c r="M153" s="2"/>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" s="2"/>
+      <c r="Q153" s="2"/>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E154" t="s">
+        <v>97</v>
+      </c>
+      <c r="F154" t="s">
+        <v>97</v>
+      </c>
+      <c r="G154" t="s">
+        <v>97</v>
+      </c>
+      <c r="H154" t="s">
+        <v>97</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J154" t="s">
+        <v>97</v>
+      </c>
+      <c r="K154" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A155" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E155" t="s">
+        <v>216</v>
+      </c>
+      <c r="F155" t="s">
+        <v>216</v>
+      </c>
+      <c r="G155" t="s">
+        <v>216</v>
+      </c>
+      <c r="H155" t="s">
+        <v>217</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J155" s="2">
+        <v>1</v>
+      </c>
+      <c r="K155" s="2">
+        <v>1</v>
+      </c>
+      <c r="L155" s="2"/>
+      <c r="M155" s="2"/>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
+      <c r="P155" s="2"/>
+      <c r="Q155" s="2"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A156" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B156" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C156" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E156" t="s">
+        <v>97</v>
+      </c>
+      <c r="F156" t="s">
+        <v>97</v>
+      </c>
+      <c r="G156" t="s">
+        <v>97</v>
+      </c>
+      <c r="H156" t="s">
+        <v>97</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J156" t="s">
+        <v>97</v>
+      </c>
+      <c r="K156" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A157" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D157" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E157" t="s">
         <v>67</v>
       </c>
-      <c r="F154" t="s">
+      <c r="F157" t="s">
         <v>67</v>
       </c>
-      <c r="G154" t="s">
+      <c r="G157" t="s">
         <v>67</v>
       </c>
-      <c r="H154" t="s">
+      <c r="H157" t="s">
         <v>68</v>
       </c>
-      <c r="I154" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J154" s="2">
+      <c r="I157" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J157" s="2">
         <v>1</v>
       </c>
-      <c r="K154" s="2">
+      <c r="K157" s="2">
         <v>1</v>
       </c>
-      <c r="L154" s="2"/>
-      <c r="M154" s="2"/>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
-      <c r="P154" s="2"/>
-      <c r="Q154" s="2"/>
+      <c r="L157" s="2"/>
+      <c r="M157" s="2"/>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" s="2"/>
+      <c r="Q157" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081C2FAB-F2B0-BA45-8ECE-3C00057DC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FC13E5-3456-3742-BF7F-10D455C96214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="496">
   <si>
     <t>category</t>
   </si>
@@ -1490,6 +1490,24 @@
   </si>
   <si>
     <t>Rubhu_proktha_Atma_vaibhava_nirupanam</t>
+  </si>
+  <si>
+    <t>N017</t>
+  </si>
+  <si>
+    <t>N018</t>
+  </si>
+  <si>
+    <t>Atma_shatkam_Nirvaana_shatkam_shankaracharya.pdf</t>
+  </si>
+  <si>
+    <t>Atma_shatkam_Nirvaana_shatkam_shankaracharya</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atmagynaana_nirupanam</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atmagynaana_nirupanam.pdf</t>
   </si>
 </sst>
 </file>
@@ -1861,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q157"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -6114,66 +6132,72 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>125</v>
+        <v>490</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E115" t="s">
-        <v>97</v>
+        <v>493</v>
       </c>
       <c r="F115" t="s">
-        <v>97</v>
+        <v>493</v>
+      </c>
+      <c r="G115" t="s">
+        <v>493</v>
+      </c>
+      <c r="H115" t="s">
+        <v>492</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J115" t="s">
-        <v>97</v>
-      </c>
-      <c r="K115" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J115">
+        <v>17</v>
+      </c>
+      <c r="K115">
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>185</v>
+        <v>491</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E116" t="s">
-        <v>186</v>
+        <v>494</v>
       </c>
       <c r="F116" t="s">
-        <v>186</v>
+        <v>494</v>
       </c>
       <c r="G116" t="s">
-        <v>186</v>
+        <v>494</v>
       </c>
       <c r="H116" t="s">
-        <v>187</v>
+        <v>495</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J116">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K116">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -6184,31 +6208,25 @@
         <v>152</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E117" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F117" t="s">
-        <v>188</v>
-      </c>
-      <c r="G117" t="s">
-        <v>188</v>
-      </c>
-      <c r="H117" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J117">
-        <v>2</v>
-      </c>
-      <c r="K117">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J117" t="s">
+        <v>97</v>
+      </c>
+      <c r="K117" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -6219,31 +6237,31 @@
         <v>152</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E118" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F118" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G118" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H118" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -6254,101 +6272,101 @@
         <v>152</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F119" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G119" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H119" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K119">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E120" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="F120" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="G120" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="H120" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J120" t="s">
-        <v>97</v>
-      </c>
-      <c r="K120" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J120">
+        <v>3</v>
+      </c>
+      <c r="K120">
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E121" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="F121" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="G121" t="s">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="H121" t="s">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J121" s="2">
-        <v>1</v>
-      </c>
-      <c r="K121" s="2">
-        <v>1</v>
+      <c r="J121">
+        <v>4</v>
+      </c>
+      <c r="K121">
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -6359,31 +6377,31 @@
         <v>209</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>279</v>
+        <v>126</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E122" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="F122" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="G122" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="H122" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J122">
-        <v>2</v>
-      </c>
-      <c r="K122">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J122" t="s">
+        <v>97</v>
+      </c>
+      <c r="K122" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -6394,31 +6412,31 @@
         <v>209</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E123" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F123" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G123" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H123" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J123">
-        <v>3</v>
-      </c>
-      <c r="K123">
-        <v>3</v>
+      <c r="J123" s="2">
+        <v>1</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -6429,31 +6447,31 @@
         <v>209</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E124" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F124" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G124" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H124" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K124">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6464,31 +6482,31 @@
         <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H125" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J125">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K125">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6499,31 +6517,31 @@
         <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G126" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H126" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J126">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K126">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6534,31 +6552,31 @@
         <v>209</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H127" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K127">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6569,31 +6587,31 @@
         <v>209</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E128" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G128" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H128" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J128">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K128">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -6604,31 +6622,31 @@
         <v>209</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E129" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="F129" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="G129" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="H129" t="s">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K129">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
@@ -6639,31 +6657,31 @@
         <v>209</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H130" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K130">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
@@ -6674,31 +6692,31 @@
         <v>209</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="F131" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="G131" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="H131" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K131">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
@@ -6709,31 +6727,31 @@
         <v>209</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E132" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F132" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G132" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H132" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J132">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K132">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
@@ -6744,31 +6762,31 @@
         <v>209</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E133" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F133" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G133" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H133" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J133">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K133">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
@@ -6779,101 +6797,101 @@
         <v>209</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E134" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F134" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G134" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H134" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K134">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E135" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="F135" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="G135" t="s">
-        <v>97</v>
+        <v>315</v>
       </c>
       <c r="H135" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J135" t="s">
-        <v>97</v>
-      </c>
-      <c r="K135" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J135">
+        <v>13</v>
+      </c>
+      <c r="K135">
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E136" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="F136" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="G136" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="H136" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J136" s="2">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2">
-        <v>1</v>
+      <c r="J136">
+        <v>14</v>
+      </c>
+      <c r="K136">
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
@@ -6884,31 +6902,31 @@
         <v>210</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>325</v>
+        <v>130</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E137" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="F137" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="G137" t="s">
-        <v>352</v>
+        <v>97</v>
       </c>
       <c r="H137" t="s">
-        <v>339</v>
+        <v>97</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J137">
-        <v>2</v>
-      </c>
-      <c r="K137">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J137" t="s">
+        <v>97</v>
+      </c>
+      <c r="K137" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
@@ -6919,31 +6937,31 @@
         <v>210</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E138" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F138" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G138" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H138" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J138">
-        <v>3</v>
-      </c>
-      <c r="K138">
-        <v>3</v>
+      <c r="J138" s="2">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
@@ -6954,31 +6972,31 @@
         <v>210</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E139" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F139" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G139" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H139" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K139">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
@@ -6989,31 +7007,31 @@
         <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F140" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G140" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H140" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="I140" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K140">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
@@ -7024,31 +7042,31 @@
         <v>210</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E141" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F141" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G141" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H141" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J141">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K141">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -7059,31 +7077,31 @@
         <v>210</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G142" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H142" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K142">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
@@ -7094,31 +7112,31 @@
         <v>210</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F143" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G143" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H143" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J143">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K143">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
@@ -7129,31 +7147,31 @@
         <v>210</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E144" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F144" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G144" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H144" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J144">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K144">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
@@ -7164,31 +7182,31 @@
         <v>210</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="F145" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="G145" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="H145" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J145">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K145">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
@@ -7199,31 +7217,31 @@
         <v>210</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F146" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G146" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H146" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J146">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K146">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
@@ -7234,31 +7252,31 @@
         <v>210</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E147" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F147" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="G147" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="H147" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J147">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K147">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
@@ -7269,31 +7287,31 @@
         <v>210</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E148" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F148" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G148" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H148" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J148">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K148">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
@@ -7304,108 +7322,102 @@
         <v>210</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E149" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F149" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G149" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H149" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J149">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K149">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E150" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="F150" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="G150" t="s">
-        <v>97</v>
+        <v>362</v>
       </c>
       <c r="H150" t="s">
-        <v>97</v>
+        <v>349</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J150" t="s">
-        <v>97</v>
-      </c>
-      <c r="K150" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J150">
+        <v>13</v>
+      </c>
+      <c r="K150">
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E151" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="F151" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="G151" t="s">
-        <v>177</v>
+        <v>363</v>
       </c>
       <c r="H151" t="s">
-        <v>178</v>
+        <v>350</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J151" s="2">
-        <v>1</v>
-      </c>
-      <c r="K151" s="2">
-        <v>1</v>
-      </c>
-      <c r="L151" s="2"/>
-      <c r="M151" s="2"/>
-      <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
-      <c r="P151" s="2"/>
-      <c r="Q151" s="2"/>
+      <c r="J151">
+        <v>14</v>
+      </c>
+      <c r="K151">
+        <v>14</v>
+      </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
@@ -7415,38 +7427,32 @@
         <v>211</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E152" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="F152" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="G152" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H152" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J152" s="2">
-        <v>2</v>
-      </c>
-      <c r="K152" s="2">
-        <v>2</v>
-      </c>
-      <c r="L152" s="2"/>
-      <c r="M152" s="2"/>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
-      <c r="P152" s="2"/>
-      <c r="Q152" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J152" t="s">
+        <v>97</v>
+      </c>
+      <c r="K152" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
@@ -7456,31 +7462,31 @@
         <v>211</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E153" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="F153" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="G153" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="H153" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J153" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K153" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -7491,72 +7497,78 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>128</v>
+        <v>219</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E154" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F154" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G154" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H154" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J154" t="s">
-        <v>97</v>
-      </c>
-      <c r="K154" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J154" s="2">
+        <v>2</v>
+      </c>
+      <c r="K154" s="2">
+        <v>2</v>
+      </c>
+      <c r="L154" s="2"/>
+      <c r="M154" s="2"/>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" s="2"/>
+      <c r="Q154" s="2"/>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E155" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F155" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G155" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H155" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I155" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J155" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K155" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -7567,16 +7579,16 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E156" t="s">
         <v>97</v>
@@ -7602,28 +7614,28 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E157" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F157" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="G157" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="H157" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>70</v>
@@ -7641,6 +7653,82 @@
       <c r="P157" s="2"/>
       <c r="Q157" s="2"/>
     </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A158" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E158" t="s">
+        <v>97</v>
+      </c>
+      <c r="F158" t="s">
+        <v>97</v>
+      </c>
+      <c r="G158" t="s">
+        <v>97</v>
+      </c>
+      <c r="H158" t="s">
+        <v>97</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J158" t="s">
+        <v>97</v>
+      </c>
+      <c r="K158" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A159" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E159" t="s">
+        <v>67</v>
+      </c>
+      <c r="F159" t="s">
+        <v>67</v>
+      </c>
+      <c r="G159" t="s">
+        <v>67</v>
+      </c>
+      <c r="H159" t="s">
+        <v>68</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J159" s="2">
+        <v>1</v>
+      </c>
+      <c r="K159" s="2">
+        <v>1</v>
+      </c>
+      <c r="L159" s="2"/>
+      <c r="M159" s="2"/>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" s="2"/>
+      <c r="Q159" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FC13E5-3456-3742-BF7F-10D455C96214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A764C25D-672C-AA44-A746-88DF7661310A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="505">
   <si>
     <t>category</t>
   </si>
@@ -1508,6 +1508,33 @@
   </si>
   <si>
     <t>Rubhu_proktha_Atmagynaana_nirupanam.pdf</t>
+  </si>
+  <si>
+    <t>N019</t>
+  </si>
+  <si>
+    <t>N020</t>
+  </si>
+  <si>
+    <t>N021</t>
+  </si>
+  <si>
+    <t>Atma_arpana_stuthi_appaiya_deekshitar.pdf</t>
+  </si>
+  <si>
+    <t>Atmaa_veereshwar_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atma_aananda_nirupanam.pdf</t>
+  </si>
+  <si>
+    <t>Atma_arpana_stuthi_appaiya_deekshitar</t>
+  </si>
+  <si>
+    <t>Atmaa_veereshwar_stotram</t>
+  </si>
+  <si>
+    <t>Rubhu_proktha_Atma_aananda_nirupanam</t>
   </si>
 </sst>
 </file>
@@ -1879,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -6202,101 +6229,107 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>125</v>
+        <v>496</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
-        <v>97</v>
+        <v>502</v>
       </c>
       <c r="F117" t="s">
-        <v>97</v>
+        <v>502</v>
+      </c>
+      <c r="G117" t="s">
+        <v>502</v>
+      </c>
+      <c r="H117" t="s">
+        <v>499</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J117" t="s">
-        <v>97</v>
-      </c>
-      <c r="K117" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J117">
+        <v>19</v>
+      </c>
+      <c r="K117">
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>185</v>
+        <v>497</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>186</v>
+        <v>503</v>
       </c>
       <c r="F118" t="s">
-        <v>186</v>
+        <v>503</v>
       </c>
       <c r="G118" t="s">
-        <v>186</v>
+        <v>503</v>
       </c>
       <c r="H118" t="s">
-        <v>187</v>
+        <v>500</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J118">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>190</v>
+        <v>498</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E119" t="s">
-        <v>188</v>
+        <v>504</v>
       </c>
       <c r="F119" t="s">
-        <v>188</v>
+        <v>504</v>
       </c>
       <c r="G119" t="s">
-        <v>188</v>
+        <v>504</v>
       </c>
       <c r="H119" t="s">
-        <v>189</v>
+        <v>501</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J119">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K119">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -6307,31 +6340,25 @@
         <v>152</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E120" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>193</v>
-      </c>
-      <c r="G120" t="s">
-        <v>193</v>
-      </c>
-      <c r="H120" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J120">
-        <v>3</v>
-      </c>
-      <c r="K120">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J120" t="s">
+        <v>97</v>
+      </c>
+      <c r="K120" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -6342,136 +6369,136 @@
         <v>152</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E121" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F121" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G121" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H121" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J121">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K121">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E122" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="F122" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="G122" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H122" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J122" t="s">
-        <v>97</v>
-      </c>
-      <c r="K122" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E123" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="F123" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="G123" t="s">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="H123" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J123" s="2">
-        <v>1</v>
-      </c>
-      <c r="K123" s="2">
-        <v>1</v>
+      <c r="J123">
+        <v>3</v>
+      </c>
+      <c r="K123">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E124" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="F124" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="G124" t="s">
-        <v>305</v>
+        <v>195</v>
       </c>
       <c r="H124" t="s">
-        <v>293</v>
+        <v>196</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K124">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -6482,31 +6509,31 @@
         <v>209</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>280</v>
+        <v>126</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E125" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="F125" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="G125" t="s">
-        <v>306</v>
+        <v>97</v>
       </c>
       <c r="H125" t="s">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J125">
-        <v>3</v>
-      </c>
-      <c r="K125">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J125" t="s">
+        <v>97</v>
+      </c>
+      <c r="K125" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -6517,31 +6544,31 @@
         <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E126" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F126" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G126" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H126" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I126" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J126">
-        <v>4</v>
-      </c>
-      <c r="K126">
-        <v>4</v>
+      <c r="J126" s="2">
+        <v>1</v>
+      </c>
+      <c r="K126" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -6552,31 +6579,31 @@
         <v>209</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E127" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F127" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G127" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H127" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K127">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -6587,31 +6614,31 @@
         <v>209</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E128" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F128" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G128" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H128" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I128" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J128">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K128">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -6622,31 +6649,31 @@
         <v>209</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E129" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F129" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G129" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H129" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J129">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K129">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
@@ -6657,31 +6684,31 @@
         <v>209</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E130" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F130" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G130" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H130" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J130">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K130">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
@@ -6692,31 +6719,31 @@
         <v>209</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E131" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="F131" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="G131" t="s">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="H131" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J131">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K131">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
@@ -6727,31 +6754,31 @@
         <v>209</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E132" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F132" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G132" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H132" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I132" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J132">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K132">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
@@ -6762,31 +6789,31 @@
         <v>209</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F133" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G133" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H133" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J133">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K133">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
@@ -6797,31 +6824,31 @@
         <v>209</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E134" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="F134" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="G134" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="H134" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="I134" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J134">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K134">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
@@ -6832,31 +6859,31 @@
         <v>209</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E135" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F135" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G135" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="H135" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J135">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K135">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
@@ -6867,136 +6894,136 @@
         <v>209</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>147</v>
       </c>
       <c r="E136" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F136" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G136" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H136" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J136">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K136">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>130</v>
+        <v>289</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E137" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="F137" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="G137" t="s">
-        <v>97</v>
+        <v>314</v>
       </c>
       <c r="H137" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J137" t="s">
-        <v>97</v>
-      </c>
-      <c r="K137" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J137">
+        <v>12</v>
+      </c>
+      <c r="K137">
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E138" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="F138" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="G138" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="H138" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="I138" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J138" s="2">
-        <v>1</v>
-      </c>
-      <c r="K138" s="2">
-        <v>1</v>
+      <c r="J138">
+        <v>13</v>
+      </c>
+      <c r="K138">
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E139" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="F139" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="G139" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="H139" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="I139" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K139">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
@@ -7007,31 +7034,31 @@
         <v>210</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>326</v>
+        <v>130</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E140" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="F140" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="G140" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c r="H140" t="s">
-        <v>340</v>
+        <v>97</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J140">
-        <v>3</v>
-      </c>
-      <c r="K140">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J140" t="s">
+        <v>97</v>
+      </c>
+      <c r="K140" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
@@ -7042,31 +7069,31 @@
         <v>210</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>327</v>
+        <v>254</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E141" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F141" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G141" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H141" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I141" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J141">
-        <v>4</v>
-      </c>
-      <c r="K141">
-        <v>4</v>
+      <c r="J141" s="2">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -7077,31 +7104,31 @@
         <v>210</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E142" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F142" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G142" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H142" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J142">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K142">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
@@ -7112,31 +7139,31 @@
         <v>210</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F143" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G143" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H143" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K143">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
@@ -7147,31 +7174,31 @@
         <v>210</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E144" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F144" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G144" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H144" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J144">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K144">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
@@ -7182,31 +7209,31 @@
         <v>210</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F145" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G145" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H145" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J145">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K145">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
@@ -7217,31 +7244,31 @@
         <v>210</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F146" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G146" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H146" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J146">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K146">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
@@ -7252,31 +7279,31 @@
         <v>210</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E147" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="F147" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="G147" t="s">
-        <v>257</v>
+        <v>357</v>
       </c>
       <c r="H147" t="s">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J147">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K147">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
@@ -7287,31 +7314,31 @@
         <v>210</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E148" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F148" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G148" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H148" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J148">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K148">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
@@ -7322,31 +7349,31 @@
         <v>210</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E149" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F149" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G149" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H149" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I149" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J149">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K149">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
@@ -7357,31 +7384,31 @@
         <v>210</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E150" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="F150" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="G150" t="s">
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="H150" t="s">
-        <v>349</v>
+        <v>258</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J150">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K150">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.2">
@@ -7392,149 +7419,137 @@
         <v>210</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>148</v>
       </c>
       <c r="E151" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F151" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G151" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H151" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J151">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K151">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E152" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="F152" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="G152" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="H152" t="s">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J152" t="s">
-        <v>97</v>
-      </c>
-      <c r="K152" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J152">
+        <v>12</v>
+      </c>
+      <c r="K152">
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>218</v>
+        <v>336</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E153" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="F153" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="G153" t="s">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="H153" t="s">
-        <v>178</v>
+        <v>349</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J153" s="2">
-        <v>1</v>
-      </c>
-      <c r="K153" s="2">
-        <v>1</v>
-      </c>
-      <c r="L153" s="2"/>
-      <c r="M153" s="2"/>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
-      <c r="P153" s="2"/>
-      <c r="Q153" s="2"/>
+      <c r="J153">
+        <v>13</v>
+      </c>
+      <c r="K153">
+        <v>13</v>
+      </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E154" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="F154" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="G154" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="H154" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="I154" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J154" s="2">
-        <v>2</v>
-      </c>
-      <c r="K154" s="2">
-        <v>2</v>
-      </c>
-      <c r="L154" s="2"/>
-      <c r="M154" s="2"/>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
-      <c r="P154" s="2"/>
-      <c r="Q154" s="2"/>
+      <c r="J154">
+        <v>14</v>
+      </c>
+      <c r="K154">
+        <v>14</v>
+      </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
@@ -7544,107 +7559,107 @@
         <v>211</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E155" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="F155" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="G155" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="H155" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J155" s="2">
-        <v>3</v>
-      </c>
-      <c r="K155" s="2">
-        <v>3</v>
-      </c>
-      <c r="L155" s="2"/>
-      <c r="M155" s="2"/>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" s="2"/>
-      <c r="Q155" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J155" t="s">
+        <v>97</v>
+      </c>
+      <c r="K155" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E156" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F156" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G156" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H156" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J156" t="s">
-        <v>97</v>
-      </c>
-      <c r="K156" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J156" s="2">
+        <v>1</v>
+      </c>
+      <c r="K156" s="2">
+        <v>1</v>
+      </c>
+      <c r="L156" s="2"/>
+      <c r="M156" s="2"/>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" s="2"/>
+      <c r="Q156" s="2"/>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E157" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="F157" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="G157" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="H157" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J157" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K157" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -7655,79 +7670,196 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E158" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F158" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G158" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="H158" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J158" t="s">
-        <v>97</v>
-      </c>
-      <c r="K158" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J158" s="2">
+        <v>3</v>
+      </c>
+      <c r="K158" s="2">
+        <v>3</v>
+      </c>
+      <c r="L158" s="2"/>
+      <c r="M158" s="2"/>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" s="2"/>
+      <c r="Q158" s="2"/>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E159" t="s">
+        <v>97</v>
+      </c>
+      <c r="F159" t="s">
+        <v>97</v>
+      </c>
+      <c r="G159" t="s">
+        <v>97</v>
+      </c>
+      <c r="H159" t="s">
+        <v>97</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J159" t="s">
+        <v>97</v>
+      </c>
+      <c r="K159" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A160" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E160" t="s">
+        <v>216</v>
+      </c>
+      <c r="F160" t="s">
+        <v>216</v>
+      </c>
+      <c r="G160" t="s">
+        <v>216</v>
+      </c>
+      <c r="H160" t="s">
+        <v>217</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J160" s="2">
+        <v>1</v>
+      </c>
+      <c r="K160" s="2">
+        <v>1</v>
+      </c>
+      <c r="L160" s="2"/>
+      <c r="M160" s="2"/>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" s="2"/>
+      <c r="Q160" s="2"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A161" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B161" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C161" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E161" t="s">
+        <v>97</v>
+      </c>
+      <c r="F161" t="s">
+        <v>97</v>
+      </c>
+      <c r="G161" t="s">
+        <v>97</v>
+      </c>
+      <c r="H161" t="s">
+        <v>97</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J161" t="s">
+        <v>97</v>
+      </c>
+      <c r="K161" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A162" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D162" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E162" t="s">
         <v>67</v>
       </c>
-      <c r="F159" t="s">
+      <c r="F162" t="s">
         <v>67</v>
       </c>
-      <c r="G159" t="s">
+      <c r="G162" t="s">
         <v>67</v>
       </c>
-      <c r="H159" t="s">
+      <c r="H162" t="s">
         <v>68</v>
       </c>
-      <c r="I159" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J159" s="2">
+      <c r="I162" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J162" s="2">
         <v>1</v>
       </c>
-      <c r="K159" s="2">
+      <c r="K162" s="2">
         <v>1</v>
       </c>
-      <c r="L159" s="2"/>
-      <c r="M159" s="2"/>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
-      <c r="P159" s="2"/>
-      <c r="Q159" s="2"/>
+      <c r="L162" s="2"/>
+      <c r="M162" s="2"/>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
+      <c r="P162" s="2"/>
+      <c r="Q162" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
